--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$378</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$382</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$194</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$378</f>
+              <f>'資金明細'!$R$2:$R$382</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-12 22:39（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 01:45（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$191,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$194,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$J$2:$J$191,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$J$2:$J$194,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$J$2:$J$191,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$J$2:$J$194,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$J$2:$J$191,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$J$2:$J$194,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$191,"&lt;&gt;未平倉",交易明細!$L$2:$L$191,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$194,"&lt;&gt;未平倉",交易明細!$L$2:$L$194,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做多",交易明細!$B$2:$B$191,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$B$2:$B$194,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$191,交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$191,"做多",交易明細!$J$2:$J$191,"&lt;&gt;未平倉",交易明細!$L$2:$L$191,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉",交易明細!$L$2:$L$194,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做空",交易明細!$B$2:$B$191,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$B$2:$B$194,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$191,交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$191,"做空",交易明細!$J$2:$J$191,"&lt;&gt;未平倉",交易明細!$L$2:$L$191,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉",交易明細!$L$2:$L$194,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,24 +1085,47 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1168,7 +1191,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R378</f>
+        <f>資金明細!R382</f>
         <v/>
       </c>
     </row>
@@ -1206,7 +1229,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$378)</f>
+        <f>MAX(資金明細!$R$2:$R$382)</f>
         <v/>
       </c>
     </row>
@@ -1225,7 +1248,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$378)</f>
+        <f>MIN(資金明細!$R$2:$R$382)</f>
         <v/>
       </c>
     </row>
@@ -1245,7 +1268,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$378)</f>
+        <f>MIN(資金明細!$X$2:$X$382)</f>
         <v/>
       </c>
     </row>
@@ -1264,7 +1287,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$378,"進場",資金明細!$N$2:$N$378,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$382,"進場",資金明細!$N$2:$N$382,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1283,7 +1306,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$378,"進場",資金明細!$N$2:$N$378,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$382,"進場",資金明細!$N$2:$N$382,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1294,7 +1317,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$378,"出場",資金明細!$N$2:$N$378,"已下單",資金明細!$K$2:$K$378,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$382,"出場",資金明細!$N$2:$N$382,"已下單",資金明細!$K$2:$K$382,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1328,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$191),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$194),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1314,7 +1337,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$378,"出場",資金明細!$N$2:$N$378,"已下單",資金明細!$K$2:$K$378,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$382,"出場",資金明細!$N$2:$N$382,"已下單",資金明細!$K$2:$K$382,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1330,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$378,"出場",資金明細!$N$2:$N$378,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$382,"出場",資金明細!$N$2:$N$382,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1346,7 +1369,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$378)</f>
+        <f>MAX(資金明細!$U$2:$U$382)</f>
         <v/>
       </c>
     </row>
@@ -1362,7 +1385,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$378)</f>
+        <f>MAX(資金明細!$S$2:$S$382)</f>
         <v/>
       </c>
     </row>
@@ -1373,7 +1396,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V378</f>
+        <f>B5*資金明細!V382</f>
         <v/>
       </c>
     </row>
@@ -1384,7 +1407,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N355="已下單",資金明細!O355*交易明細!L179,0)+IF(資金明細!N357="已下單",資金明細!O357*交易明細!L181,0)+IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N378="已下單",資金明細!O378*交易明細!L191,0)</f>
+        <f>IF(資金明細!N355="已下單",資金明細!O355*交易明細!L179,0)+IF(資金明細!N357="已下單",資金明細!O357*交易明細!L181,0)+IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N380="已下單",資金明細!O380*交易明細!L192,0)+IF(資金明細!N381="已下單",資金明細!O381*交易明細!L193,0)+IF(資金明細!N382="已下單",資金明細!O382*交易明細!L194,0)</f>
         <v/>
       </c>
     </row>
@@ -1395,7 +1418,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$378)</f>
+        <f>MAX(資金明細!$Y$2:$Y$382)</f>
         <v/>
       </c>
     </row>
@@ -1417,7 +1440,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$378,MATCH(1,資金明細!$Z$2:$Z$378,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$382,MATCH(1,資金明細!$Z$2:$Z$382,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1428,7 +1451,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$378,"進場",資金明細!$N$2:$N$378,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$382,"進場",資金明細!$N$2:$N$382,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1493,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z378"/>
+  <dimension ref="A1:Z382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -37929,11 +37952,7 @@
         <v>0.0731405</v>
       </c>
       <c r="J378" s="17" t="n"/>
-      <c r="K378" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K378" s="2" t="n"/>
       <c r="L378" s="5" t="n"/>
       <c r="M378" s="16">
         <f>資金模擬!$B$5*V377</f>
@@ -37988,9 +38007,394 @@
         <v/>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="B379" s="7" t="n">
+        <v>46277.95833333334</v>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G379" s="17" t="n">
+        <v>0.07699</v>
+      </c>
+      <c r="H379" s="17" t="n">
+        <v>0.0792997</v>
+      </c>
+      <c r="I379" s="17" t="n">
+        <v>0.0731405</v>
+      </c>
+      <c r="J379" s="17" t="n">
+        <v>0.0731405</v>
+      </c>
+      <c r="K379" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L379" s="5">
+        <f>交易明細!K191</f>
+        <v/>
+      </c>
+      <c r="M379" s="16">
+        <f>M378</f>
+        <v/>
+      </c>
+      <c r="N379" s="2">
+        <f>N378</f>
+        <v/>
+      </c>
+      <c r="O379" s="16">
+        <f>O378</f>
+        <v/>
+      </c>
+      <c r="P379" s="4">
+        <f>交易明細!L191</f>
+        <v/>
+      </c>
+      <c r="Q379" s="10">
+        <f>IF(N379="已下單",O379*P379,0)</f>
+        <v/>
+      </c>
+      <c r="R379" s="10">
+        <f>R378+Q379</f>
+        <v/>
+      </c>
+      <c r="S379" s="16">
+        <f>S378-IF(N379="已下單",M379,0)</f>
+        <v/>
+      </c>
+      <c r="T379" s="16">
+        <f>R379-S379</f>
+        <v/>
+      </c>
+      <c r="U379" s="2">
+        <f>U378-IF(N379="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V379" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R379,0),MAX(V378,FLOOR(MAX(R379,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W379" s="10">
+        <f>MAX(W378,R379)</f>
+        <v/>
+      </c>
+      <c r="X379" s="4">
+        <f>IF(W379&gt;0,R379/W379-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y379" s="16">
+        <f>IF(R379&gt;0,S379*資金模擬!$B$7/R379,0)</f>
+        <v/>
+      </c>
+      <c r="Z379" s="2">
+        <f>IF(OR(Z378=1,R379&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B380" s="7" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G380" s="17" t="n">
+        <v>0.13578</v>
+      </c>
+      <c r="H380" s="17" t="n">
+        <v>0.1398534</v>
+      </c>
+      <c r="I380" s="17" t="n">
+        <v>0.128991</v>
+      </c>
+      <c r="J380" s="17" t="n"/>
+      <c r="K380" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L380" s="5" t="n"/>
+      <c r="M380" s="16">
+        <f>資金模擬!$B$5*V379</f>
+        <v/>
+      </c>
+      <c r="N380" s="2">
+        <f>IF(Z379=1,"已停止",IF(T379&gt;=M380,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O380" s="16">
+        <f>IF(N380="已下單",M380*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P380" s="4" t="n"/>
+      <c r="Q380" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R380" s="10">
+        <f>R379+Q380</f>
+        <v/>
+      </c>
+      <c r="S380" s="16">
+        <f>S379+IF(N380="已下單",M380,0)</f>
+        <v/>
+      </c>
+      <c r="T380" s="16">
+        <f>R380-S380</f>
+        <v/>
+      </c>
+      <c r="U380" s="2">
+        <f>U379+IF(N380="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V380" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R380,0),MAX(V379,FLOOR(MAX(R380,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W380" s="10">
+        <f>MAX(W379,R380)</f>
+        <v/>
+      </c>
+      <c r="X380" s="4">
+        <f>IF(W380&gt;0,R380/W380-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y380" s="16">
+        <f>IF(R380&gt;0,S380*資金模擬!$B$7/R380,0)</f>
+        <v/>
+      </c>
+      <c r="Z380" s="2">
+        <f>IF(OR(Z379=1,R380&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="B381" s="7" t="n">
+        <v>46278.04166666666</v>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>MARSCOIN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G381" s="17" t="n">
+        <v>0.11779</v>
+      </c>
+      <c r="H381" s="17" t="n">
+        <v>0.1142563</v>
+      </c>
+      <c r="I381" s="17" t="n">
+        <v>0.1236795</v>
+      </c>
+      <c r="J381" s="17" t="n"/>
+      <c r="K381" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L381" s="5" t="n"/>
+      <c r="M381" s="16">
+        <f>資金模擬!$B$5*V380</f>
+        <v/>
+      </c>
+      <c r="N381" s="2">
+        <f>IF(Z380=1,"已停止",IF(T380&gt;=M381,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O381" s="16">
+        <f>IF(N381="已下單",M381*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P381" s="4" t="n"/>
+      <c r="Q381" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R381" s="10">
+        <f>R380+Q381</f>
+        <v/>
+      </c>
+      <c r="S381" s="16">
+        <f>S380+IF(N381="已下單",M381,0)</f>
+        <v/>
+      </c>
+      <c r="T381" s="16">
+        <f>R381-S381</f>
+        <v/>
+      </c>
+      <c r="U381" s="2">
+        <f>U380+IF(N381="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V381" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R381,0),MAX(V380,FLOOR(MAX(R381,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W381" s="10">
+        <f>MAX(W380,R381)</f>
+        <v/>
+      </c>
+      <c r="X381" s="4">
+        <f>IF(W381&gt;0,R381/W381-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y381" s="16">
+        <f>IF(R381&gt;0,S381*資金模擬!$B$7/R381,0)</f>
+        <v/>
+      </c>
+      <c r="Z381" s="2">
+        <f>IF(OR(Z380=1,R381&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="B382" s="7" t="n">
+        <v>46278.04166666666</v>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G382" s="17" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="H382" s="17" t="n">
+        <v>0.593446</v>
+      </c>
+      <c r="I382" s="17" t="n">
+        <v>0.64239</v>
+      </c>
+      <c r="J382" s="17" t="n"/>
+      <c r="K382" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L382" s="5" t="n"/>
+      <c r="M382" s="16">
+        <f>資金模擬!$B$5*V381</f>
+        <v/>
+      </c>
+      <c r="N382" s="2">
+        <f>IF(Z381=1,"已停止",IF(T381&gt;=M382,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O382" s="16">
+        <f>IF(N382="已下單",M382*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P382" s="4" t="n"/>
+      <c r="Q382" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R382" s="10">
+        <f>R381+Q382</f>
+        <v/>
+      </c>
+      <c r="S382" s="16">
+        <f>S381+IF(N382="已下單",M382,0)</f>
+        <v/>
+      </c>
+      <c r="T382" s="16">
+        <f>R382-S382</f>
+        <v/>
+      </c>
+      <c r="U382" s="2">
+        <f>U381+IF(N382="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V382" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R382,0),MAX(V381,FLOOR(MAX(R382,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W382" s="10">
+        <f>MAX(W381,R382)</f>
+        <v/>
+      </c>
+      <c r="X382" s="4">
+        <f>IF(W382&gt;0,R382/W382-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y382" s="16">
+        <f>IF(R382&gt;0,S382*資金模擬!$B$7/R382,0)</f>
+        <v/>
+      </c>
+      <c r="Z382" s="2">
+        <f>IF(OR(Z381=1,R382&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z378"/>
-  <conditionalFormatting sqref="K2:K378">
+  <autoFilter ref="A1:Z382"/>
+  <conditionalFormatting sqref="K2:K382">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -37998,7 +38402,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N378">
+  <conditionalFormatting sqref="N2:N382">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -38006,7 +38410,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q378">
+  <conditionalFormatting sqref="Q2:Q382">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -38071,7 +38475,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-12 22:39（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-13 01:45（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -38275,7 +38679,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$191),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$194),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -38440,7 +38844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC191"/>
+  <dimension ref="A1:AC194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -55626,10 +56030,10 @@
         <v>0.14889</v>
       </c>
       <c r="H179" s="7" t="n">
-        <v>46277.91666666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="I179" s="17" t="n">
-        <v>0.1414</v>
+        <v>0.1427</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
@@ -55668,7 +56072,7 @@
         <v>0.02679830747531731</v>
       </c>
       <c r="T179" s="4" t="n">
-        <v>0.01198871650211553</v>
+        <v>0.01410437235543016</v>
       </c>
       <c r="U179" s="16" t="n">
         <v>1.201993217794421</v>
@@ -55822,10 +56226,10 @@
         <v>0.00371385</v>
       </c>
       <c r="H181" s="7" t="n">
-        <v>46277.91666666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="I181" s="17" t="n">
-        <v>0.003596</v>
+        <v>0.003672</v>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
@@ -55864,7 +56268,7 @@
         <v>0.006502685891998872</v>
       </c>
       <c r="T181" s="4" t="n">
-        <v>0.030534351145038</v>
+        <v>0.04523607577042688</v>
       </c>
       <c r="U181" s="16" t="n">
         <v>1.224382173297189</v>
@@ -56114,10 +56518,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46277.91666666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5737</v>
+        <v>0.5696</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -56790,14 +57194,14 @@
         <v>0.0731405</v>
       </c>
       <c r="H191" s="7" t="n">
-        <v>46277.91666666666</v>
+        <v>46277.95833333334</v>
       </c>
       <c r="I191" s="17" t="n">
-        <v>0.07488</v>
+        <v>0.0731405</v>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K191" s="5">
@@ -56808,11 +57212,7 @@
         <f>IF(C191="做多",I191/E191-1,1-I191/E191)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M191" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M191" s="2" t="inlineStr"/>
       <c r="N191" s="4" t="n">
         <v>0.03342281879194631</v>
       </c>
@@ -56832,7 +57232,7 @@
         <v>0.007793219898688086</v>
       </c>
       <c r="T191" s="4" t="n">
-        <v>0.03104299259644117</v>
+        <v>0.05</v>
       </c>
       <c r="U191" s="16" t="n">
         <v>0.8291217446110898</v>
@@ -56863,9 +57263,309 @@
         <v/>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="n">
+        <v>46278</v>
+      </c>
+      <c r="E192" s="17" t="n">
+        <v>0.13578</v>
+      </c>
+      <c r="F192" s="17" t="n">
+        <v>0.1398534</v>
+      </c>
+      <c r="G192" s="17" t="n">
+        <v>0.128991</v>
+      </c>
+      <c r="H192" s="7" t="n">
+        <v>46278.04166666666</v>
+      </c>
+      <c r="I192" s="17" t="n">
+        <v>0.13284</v>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K192" s="5">
+        <f>(H192-D192)*24</f>
+        <v/>
+      </c>
+      <c r="L192" s="4">
+        <f>IF(C192="做多",I192/E192-1,1-I192/E192)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N192" s="4" t="n">
+        <v>0.02630385487528364</v>
+      </c>
+      <c r="O192" s="4" t="n">
+        <v>0.0656380056310801</v>
+      </c>
+      <c r="P192" s="4" t="n">
+        <v>0.03692389934705442</v>
+      </c>
+      <c r="Q192" s="19" t="n">
+        <v>2052353</v>
+      </c>
+      <c r="R192" s="19" t="n">
+        <v>3011155.14336</v>
+      </c>
+      <c r="S192" s="4" t="n">
+        <v>0.01119457946678448</v>
+      </c>
+      <c r="T192" s="4" t="n">
+        <v>0.0364560318161733</v>
+      </c>
+      <c r="U192" s="16" t="n">
+        <v>0.4313868219392165</v>
+      </c>
+      <c r="V192" s="16" t="n">
+        <v>0.8737270875763784</v>
+      </c>
+      <c r="W192" s="4" t="n">
+        <v>0.2422826234139808</v>
+      </c>
+      <c r="X192" s="4" t="n">
+        <v>-0.03256145350908435</v>
+      </c>
+      <c r="Y192" s="4" t="n">
+        <v>-0.001068111135219985</v>
+      </c>
+      <c r="Z192" s="4" t="n">
+        <v>0.001094822274368523</v>
+      </c>
+      <c r="AA192" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB192" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC192" s="4">
+        <f>(AB192+2*參數!$B$7)/(AA192+AB192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>MARSCOIN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="n">
+        <v>46278.04166666666</v>
+      </c>
+      <c r="E193" s="17" t="n">
+        <v>0.11779</v>
+      </c>
+      <c r="F193" s="17" t="n">
+        <v>0.1142563</v>
+      </c>
+      <c r="G193" s="17" t="n">
+        <v>0.1236795</v>
+      </c>
+      <c r="H193" s="7" t="n">
+        <v>46278.04166666666</v>
+      </c>
+      <c r="I193" s="17" t="n">
+        <v>0.11779</v>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K193" s="5">
+        <f>(H193-D193)*24</f>
+        <v/>
+      </c>
+      <c r="L193" s="4">
+        <f>IF(C193="做多",I193/E193-1,1-I193/E193)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N193" s="4" t="n">
+        <v>-0.02636799470986939</v>
+      </c>
+      <c r="O193" s="4" t="n">
+        <v>0.03725001851709079</v>
+      </c>
+      <c r="P193" s="4" t="n">
+        <v>-0.003574072115892779</v>
+      </c>
+      <c r="Q193" s="19" t="n">
+        <v>-5714544</v>
+      </c>
+      <c r="R193" s="19" t="n">
+        <v>1817018.29532</v>
+      </c>
+      <c r="S193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" s="16" t="n">
+        <v>2.875093831728709</v>
+      </c>
+      <c r="V193" s="16" t="n">
+        <v>0.7025495750708207</v>
+      </c>
+      <c r="W193" s="4" t="n">
+        <v>0.02972362073964741</v>
+      </c>
+      <c r="X193" s="4" t="n">
+        <v>0.07215439149271363</v>
+      </c>
+      <c r="Y193" s="4" t="n">
+        <v>0.0002275557026621966</v>
+      </c>
+      <c r="Z193" s="4" t="n">
+        <v>-0.0008473267143092045</v>
+      </c>
+      <c r="AA193" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB193" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC193" s="4">
+        <f>(AB193+2*參數!$B$7)/(AA193+AB193)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="n">
+        <v>46278.04166666666</v>
+      </c>
+      <c r="E194" s="17" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="F194" s="17" t="n">
+        <v>0.593446</v>
+      </c>
+      <c r="G194" s="17" t="n">
+        <v>0.64239</v>
+      </c>
+      <c r="H194" s="7" t="n">
+        <v>46278.04166666666</v>
+      </c>
+      <c r="I194" s="17" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K194" s="5">
+        <f>(H194-D194)*24</f>
+        <v/>
+      </c>
+      <c r="L194" s="4">
+        <f>IF(C194="做多",I194/E194-1,1-I194/E194)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N194" s="4" t="n">
+        <v>-0.02595128164305049</v>
+      </c>
+      <c r="O194" s="4" t="n">
+        <v>0.03563079245954242</v>
+      </c>
+      <c r="P194" s="4" t="n">
+        <v>-0.007985731079492409</v>
+      </c>
+      <c r="Q194" s="19" t="n">
+        <v>-482055</v>
+      </c>
+      <c r="R194" s="19" t="n">
+        <v>2443822.4458</v>
+      </c>
+      <c r="S194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" s="16" t="n">
+        <v>0.7277946313631973</v>
+      </c>
+      <c r="V194" s="16" t="n">
+        <v>0.9458128078817738</v>
+      </c>
+      <c r="W194" s="4" t="n">
+        <v>0.07782699986283459</v>
+      </c>
+      <c r="X194" s="4" t="n">
+        <v>-0.005588428665351586</v>
+      </c>
+      <c r="Y194" s="4" t="n">
+        <v>0.0002275557026621966</v>
+      </c>
+      <c r="Z194" s="4" t="n">
+        <v>-0.0008473267143092045</v>
+      </c>
+      <c r="AA194" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB194" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC194" s="4">
+        <f>(AB194+2*參數!$B$7)/(AA194+AB194)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC191"/>
-  <conditionalFormatting sqref="J2:J191">
+  <autoFilter ref="A1:AC194"/>
+  <conditionalFormatting sqref="J2:J194">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -56972,27 +57672,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A2,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A2,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$191,$A2,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A2,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A2,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -57000,19 +57700,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A2,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A2,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A2,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A2,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57023,27 +57723,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A3,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A3,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$191,$A3,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A3,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A3,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -57051,19 +57751,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A3,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A3,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A3,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A3,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57074,27 +57774,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A4,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A4,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$191,$A4,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A4,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A4,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -57102,19 +57802,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A4,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A4,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A4,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A4,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57125,27 +57825,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A5,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A5,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$191,$A5,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A5,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A5,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -57153,19 +57853,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A5,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A5,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A5,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A5,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57176,27 +57876,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A6,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A6,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$191,$A6,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A6,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A6,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -57204,19 +57904,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A6,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A6,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A6,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A6,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57227,27 +57927,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A7,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A7,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$191,$A7,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A7,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A7,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -57255,19 +57955,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A7,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A7,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A7,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A7,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57278,27 +57978,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A8,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A8,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$191,$A8,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A8,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A8,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -57306,19 +58006,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A8,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A8,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A8,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A8,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57329,27 +58029,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A9,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A9,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$191,$A9,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A9,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A9,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -57357,19 +58057,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A9,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A9,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A9,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A9,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57380,27 +58080,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A10,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A10,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$191,$A10,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A10,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A10,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -57408,19 +58108,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A10,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A10,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A10,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A10,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57431,27 +58131,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A11,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A11,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$191,$A11,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A11,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A11,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -57459,50 +58159,50 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A11,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A11,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A11,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A11,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NEAR_USDT_PERP</t>
+          <t>牛来_USDT_PERP</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A12,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A12,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$191,$A12,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A12,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A12,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -57510,50 +58210,50 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A12,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A12,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A12,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A12,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RAY_USDT_PERP</t>
+          <t>NEAR_USDT_PERP</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A13,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A13,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$191,$A13,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A13,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A13,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -57561,50 +58261,50 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A13,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A13,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A13,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A13,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>牛来_USDT_PERP</t>
+          <t>RAY_USDT_PERP</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A14,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A14,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$191,$A14,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A14,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A14,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -57612,19 +58312,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A14,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A14,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A14,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A14,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57635,27 +58335,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A15,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A15,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$191,$A15,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A15,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A15,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -57663,19 +58363,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A15,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A15,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A15,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A15,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57686,27 +58386,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A16,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A16,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$191,$A16,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A16,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A16,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -57714,19 +58414,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A16,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A16,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A16,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A16,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57737,27 +58437,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A17,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A17,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$191,$A17,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A17,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A17,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -57765,19 +58465,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A17,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A17,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A17,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A17,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57788,27 +58488,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A18,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A18,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$191,$A18,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A18,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A18,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -57816,19 +58516,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A18,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A18,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A18,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A18,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57839,27 +58539,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A19,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A19,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$191,$A19,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A19,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A19,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -57867,19 +58567,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A19,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A19,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A19,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A19,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57890,27 +58590,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A20,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A20,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$191,$A20,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A20,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A20,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -57918,19 +58618,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A20,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A20,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A20,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A20,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57941,27 +58641,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A21,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A21,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$191,$A21,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A21,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A21,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -57969,19 +58669,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A21,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A21,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A21,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A21,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57992,27 +58692,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A22,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A22,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$191,$A22,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A22,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A22,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -58020,19 +58720,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A22,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A22,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A22,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A22,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58043,27 +58743,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A23,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A23,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$191,$A23,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A23,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A23,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -58071,19 +58771,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A23,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A23,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A23,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A23,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58094,27 +58794,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A24,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A24,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$191,$A24,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A24,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A24,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -58122,19 +58822,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A24,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A24,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A24,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A24,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58145,27 +58845,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A25,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A25,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$191,$A25,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A25,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A25,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -58173,19 +58873,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A25,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A25,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A25,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A25,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58196,27 +58896,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A26,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A26,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$191,$A26,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A26,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A26,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -58224,19 +58924,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A26,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A26,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A26,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A26,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58247,27 +58947,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A27,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A27,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$191,$A27,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A27,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A27,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -58275,19 +58975,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A27,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A27,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A27,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A27,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58298,27 +58998,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A28,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A28,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$191,$A28,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A28,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A28,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -58326,19 +59026,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A28,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A28,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A28,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A28,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58349,27 +59049,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A29,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A29,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$191,$A29,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A29,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A29,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -58377,19 +59077,19 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A29,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A29,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A29,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A29,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58400,27 +59100,27 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A30,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A30,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$191,$A30,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A30,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A30,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -58428,19 +59128,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A30,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A30,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A30,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A30,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58451,27 +59151,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A31,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A31,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$191,$A31,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A31,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A31,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -58479,19 +59179,19 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A31,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A31,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A31,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A31,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58502,27 +59202,27 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A32,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A32,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$191,$A32,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A32,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A32,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -58530,19 +59230,19 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A32,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A32,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A32,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A32,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58553,27 +59253,27 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A33,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A33,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$191,$A33,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A33,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A33,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -58581,19 +59281,19 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A33,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A33,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A33,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A33,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58604,27 +59304,27 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A34,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A34,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$191,$A34,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A34,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A34,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -58632,19 +59332,19 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A34,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A34,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A34,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A34,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58655,27 +59355,27 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A35,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A35,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$191,$A35,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A35,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A35,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -58683,19 +59383,19 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A35,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A35,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A35,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A35,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58706,27 +59406,27 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A36,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A36,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$191,$A36,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A36,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A36,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -58734,19 +59434,19 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A36,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A36,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A36,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A36,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58757,27 +59457,27 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A37,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A37,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$191,$A37,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A37,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A37,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -58785,19 +59485,19 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A37,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A37,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A37,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A37,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58808,27 +59508,27 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A38,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A38,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$191,$A38,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A38,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A38,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -58836,19 +59536,19 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A38,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A38,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A38,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A38,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58859,27 +59559,27 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A39,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A39,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$191,$A39,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A39,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A39,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -58887,19 +59587,19 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A39,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A39,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A39,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A39,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58910,27 +59610,27 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A40,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A40,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$191,$A40,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A40,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A40,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -58938,19 +59638,19 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A40,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A40,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A40,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A40,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58961,27 +59661,27 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A41,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A41,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$191,$A41,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A41,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A41,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -58989,19 +59689,19 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A41,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A41,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A41,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A41,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -59012,27 +59712,27 @@
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A42,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A42,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$191,$A42,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A42,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A42,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -59040,19 +59740,19 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A42,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A42,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A42,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A42,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -59063,27 +59763,27 @@
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A43,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A43,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$191,$A43,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A43,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A43,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -59091,19 +59791,19 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A43,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A43,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A43,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A43,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -59114,27 +59814,27 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A44,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A44,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$191,$A44,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A44,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A44,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -59142,19 +59842,19 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A44,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A44,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A44,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A44,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -59165,27 +59865,27 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A45,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A45,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$191,$A45,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A45,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A45,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -59193,19 +59893,19 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A45,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A45,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A45,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A45,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -59216,27 +59916,27 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A46,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A46,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$191,$A46,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A46,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A46,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -59244,19 +59944,19 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A46,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A46,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A46,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A46,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -59267,27 +59967,27 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A47,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A47,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$191,$A47,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A47,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A47,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -59295,19 +59995,19 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A47,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A47,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A47,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A47,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -59318,27 +60018,27 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A48,交易明細!$C$2:$C$191,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$C$2:$C$194,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A48,交易明細!$C$2:$C$191,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$C$2:$C$194,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$191,$A48,交易明細!$J$2:$J$191,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A48,交易明細!$J$2:$J$191,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A48,交易明細!$J$2:$J$191,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -59346,19 +60046,19 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A48,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$191,交易明細!$B$2:$B$191,$A48,交易明細!$J$2:$J$191,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$191,交易明細!$B$2:$B$191,$A48,交易明細!$J$2:$J$191,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$191,$A48,交易明細!$J$2:$J$191,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63192,11 +63892,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C210" s="2" t="inlineStr"/>
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="17" t="n"/>
       <c r="F210" s="17" t="n"/>
@@ -63574,7 +64270,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr"/>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D231" s="2" t="n"/>
       <c r="E231" s="17" t="n"/>
       <c r="F231" s="17" t="n"/>
@@ -64744,7 +65444,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C296" s="2" t="inlineStr"/>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D296" s="2" t="n"/>
       <c r="E296" s="17" t="n"/>
       <c r="F296" s="17" t="n"/>
@@ -67394,7 +68098,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr"/>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="17" t="n"/>
       <c r="F443" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$382</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$194</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$382</f>
+              <f>'資金明細'!$R$2:$R$401</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 01:45（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 16:19（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$194,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$203,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$J$2:$J$194,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$J$2:$J$203,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$J$2:$J$194,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$J$2:$J$203,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$J$2:$J$194,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$J$2:$J$203,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$194,"&lt;&gt;未平倉",交易明細!$L$2:$L$194,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$203,"&lt;&gt;未平倉",交易明細!$L$2:$L$203,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$B$2:$B$194,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$B$2:$B$203,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$194,"做多",交易明細!$J$2:$J$194,"&lt;&gt;未平倉",交易明細!$L$2:$L$194,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉",交易明細!$L$2:$L$203,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$B$2:$B$194,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$B$2:$B$203,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$194,"做空",交易明細!$J$2:$J$194,"&lt;&gt;未平倉",交易明細!$L$2:$L$194,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉",交易明細!$L$2:$L$203,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,47 +1085,70 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1191,7 +1214,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R382</f>
+        <f>資金明細!R401</f>
         <v/>
       </c>
     </row>
@@ -1229,7 +1252,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$382)</f>
+        <f>MAX(資金明細!$R$2:$R$401)</f>
         <v/>
       </c>
     </row>
@@ -1248,7 +1271,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$382)</f>
+        <f>MIN(資金明細!$R$2:$R$401)</f>
         <v/>
       </c>
     </row>
@@ -1268,7 +1291,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$382)</f>
+        <f>MIN(資金明細!$X$2:$X$401)</f>
         <v/>
       </c>
     </row>
@@ -1287,7 +1310,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$382,"進場",資金明細!$N$2:$N$382,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$401,"進場",資金明細!$N$2:$N$401,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1306,7 +1329,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$382,"進場",資金明細!$N$2:$N$382,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$401,"進場",資金明細!$N$2:$N$401,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1317,7 +1340,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$382,"出場",資金明細!$N$2:$N$382,"已下單",資金明細!$K$2:$K$382,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$401,"出場",資金明細!$N$2:$N$401,"已下單",資金明細!$K$2:$K$401,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1328,7 +1351,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$194),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$203),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1337,7 +1360,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$382,"出場",資金明細!$N$2:$N$382,"已下單",資金明細!$K$2:$K$382,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$401,"出場",資金明細!$N$2:$N$401,"已下單",資金明細!$K$2:$K$401,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1353,7 +1376,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$382,"出場",資金明細!$N$2:$N$382,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$401,"出場",資金明細!$N$2:$N$401,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1369,7 +1392,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$382)</f>
+        <f>MAX(資金明細!$U$2:$U$401)</f>
         <v/>
       </c>
     </row>
@@ -1385,7 +1408,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$382)</f>
+        <f>MAX(資金明細!$S$2:$S$401)</f>
         <v/>
       </c>
     </row>
@@ -1396,7 +1419,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V382</f>
+        <f>B5*資金明細!V401</f>
         <v/>
       </c>
     </row>
@@ -1407,7 +1430,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N355="已下單",資金明細!O355*交易明細!L179,0)+IF(資金明細!N357="已下單",資金明細!O357*交易明細!L181,0)+IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N380="已下單",資金明細!O380*交易明細!L192,0)+IF(資金明細!N381="已下單",資金明細!O381*交易明細!L193,0)+IF(資金明細!N382="已下單",資金明細!O382*交易明細!L194,0)</f>
+        <f>IF(資金明細!N355="已下單",資金明細!O355*交易明細!L179,0)+IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N396="已下單",資金明細!O396*交易明細!L201,0)+IF(資金明細!N400="已下單",資金明細!O400*交易明細!L202,0)+IF(資金明細!N401="已下單",資金明細!O401*交易明細!L203,0)</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1441,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$382)</f>
+        <f>MAX(資金明細!$Y$2:$Y$401)</f>
         <v/>
       </c>
     </row>
@@ -1440,7 +1463,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$382,MATCH(1,資金明細!$Z$2:$Z$382,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$401,MATCH(1,資金明細!$Z$2:$Z$401,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1451,7 +1474,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$382,"進場",資金明細!$N$2:$N$382,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$401,"進場",資金明細!$N$2:$N$401,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1516,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z382"/>
+  <dimension ref="A1:Z401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -35911,11 +35934,7 @@
         <v>0.00371385</v>
       </c>
       <c r="J357" s="17" t="n"/>
-      <c r="K357" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K357" s="2" t="n"/>
       <c r="L357" s="5" t="n"/>
       <c r="M357" s="16">
         <f>資金模擬!$B$5*V356</f>
@@ -38145,11 +38164,7 @@
         <v>0.128991</v>
       </c>
       <c r="J380" s="17" t="n"/>
-      <c r="K380" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K380" s="2" t="n"/>
       <c r="L380" s="5" t="n"/>
       <c r="M380" s="16">
         <f>資金模擬!$B$5*V379</f>
@@ -38239,11 +38254,7 @@
         <v>0.1236795</v>
       </c>
       <c r="J381" s="17" t="n"/>
-      <c r="K381" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K381" s="2" t="n"/>
       <c r="L381" s="5" t="n"/>
       <c r="M381" s="16">
         <f>資金模擬!$B$5*V380</f>
@@ -38333,11 +38344,7 @@
         <v>0.64239</v>
       </c>
       <c r="J382" s="17" t="n"/>
-      <c r="K382" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K382" s="2" t="n"/>
       <c r="L382" s="5" t="n"/>
       <c r="M382" s="16">
         <f>資金模擬!$B$5*V381</f>
@@ -38392,9 +38399,1861 @@
         <v/>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="B383" s="7" t="n">
+        <v>46278.08333333334</v>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>PUMP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G383" s="17" t="n">
+        <v>0.003537</v>
+      </c>
+      <c r="H383" s="17" t="n">
+        <v>0.00343089</v>
+      </c>
+      <c r="I383" s="17" t="n">
+        <v>0.00371385</v>
+      </c>
+      <c r="J383" s="17" t="n">
+        <v>0.00371385</v>
+      </c>
+      <c r="K383" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L383" s="5">
+        <f>交易明細!K181</f>
+        <v/>
+      </c>
+      <c r="M383" s="16">
+        <f>M357</f>
+        <v/>
+      </c>
+      <c r="N383" s="2">
+        <f>N357</f>
+        <v/>
+      </c>
+      <c r="O383" s="16">
+        <f>O357</f>
+        <v/>
+      </c>
+      <c r="P383" s="4">
+        <f>交易明細!L181</f>
+        <v/>
+      </c>
+      <c r="Q383" s="10">
+        <f>IF(N383="已下單",O383*P383,0)</f>
+        <v/>
+      </c>
+      <c r="R383" s="10">
+        <f>R382+Q383</f>
+        <v/>
+      </c>
+      <c r="S383" s="16">
+        <f>S382-IF(N383="已下單",M383,0)</f>
+        <v/>
+      </c>
+      <c r="T383" s="16">
+        <f>R383-S383</f>
+        <v/>
+      </c>
+      <c r="U383" s="2">
+        <f>U382-IF(N383="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V383" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R383,0),MAX(V382,FLOOR(MAX(R383,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W383" s="10">
+        <f>MAX(W382,R383)</f>
+        <v/>
+      </c>
+      <c r="X383" s="4">
+        <f>IF(W383&gt;0,R383/W383-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y383" s="16">
+        <f>IF(R383&gt;0,S383*資金模擬!$B$7/R383,0)</f>
+        <v/>
+      </c>
+      <c r="Z383" s="2">
+        <f>IF(OR(Z382=1,R383&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="B384" s="7" t="n">
+        <v>46278.08333333334</v>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G384" s="17" t="n">
+        <v>0.13578</v>
+      </c>
+      <c r="H384" s="17" t="n">
+        <v>0.1398534</v>
+      </c>
+      <c r="I384" s="17" t="n">
+        <v>0.128991</v>
+      </c>
+      <c r="J384" s="17" t="n">
+        <v>0.128991</v>
+      </c>
+      <c r="K384" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L384" s="5">
+        <f>交易明細!K192</f>
+        <v/>
+      </c>
+      <c r="M384" s="16">
+        <f>M380</f>
+        <v/>
+      </c>
+      <c r="N384" s="2">
+        <f>N380</f>
+        <v/>
+      </c>
+      <c r="O384" s="16">
+        <f>O380</f>
+        <v/>
+      </c>
+      <c r="P384" s="4">
+        <f>交易明細!L192</f>
+        <v/>
+      </c>
+      <c r="Q384" s="10">
+        <f>IF(N384="已下單",O384*P384,0)</f>
+        <v/>
+      </c>
+      <c r="R384" s="10">
+        <f>R383+Q384</f>
+        <v/>
+      </c>
+      <c r="S384" s="16">
+        <f>S383-IF(N384="已下單",M384,0)</f>
+        <v/>
+      </c>
+      <c r="T384" s="16">
+        <f>R384-S384</f>
+        <v/>
+      </c>
+      <c r="U384" s="2">
+        <f>U383-IF(N384="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V384" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R384,0),MAX(V383,FLOOR(MAX(R384,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W384" s="10">
+        <f>MAX(W383,R384)</f>
+        <v/>
+      </c>
+      <c r="X384" s="4">
+        <f>IF(W384&gt;0,R384/W384-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y384" s="16">
+        <f>IF(R384&gt;0,S384*資金模擬!$B$7/R384,0)</f>
+        <v/>
+      </c>
+      <c r="Z384" s="2">
+        <f>IF(OR(Z383=1,R384&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="B385" s="7" t="n">
+        <v>46278.08333333334</v>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G385" s="17" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="H385" s="17" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="I385" s="17" t="n">
+        <v>1.3414</v>
+      </c>
+      <c r="J385" s="17" t="n"/>
+      <c r="K385" s="2" t="n"/>
+      <c r="L385" s="5" t="n"/>
+      <c r="M385" s="16">
+        <f>資金模擬!$B$5*V384</f>
+        <v/>
+      </c>
+      <c r="N385" s="2">
+        <f>IF(Z384=1,"已停止",IF(T384&gt;=M385,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O385" s="16">
+        <f>IF(N385="已下單",M385*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P385" s="4" t="n"/>
+      <c r="Q385" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R385" s="10">
+        <f>R384+Q385</f>
+        <v/>
+      </c>
+      <c r="S385" s="16">
+        <f>S384+IF(N385="已下單",M385,0)</f>
+        <v/>
+      </c>
+      <c r="T385" s="16">
+        <f>R385-S385</f>
+        <v/>
+      </c>
+      <c r="U385" s="2">
+        <f>U384+IF(N385="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V385" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R385,0),MAX(V384,FLOOR(MAX(R385,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W385" s="10">
+        <f>MAX(W384,R385)</f>
+        <v/>
+      </c>
+      <c r="X385" s="4">
+        <f>IF(W385&gt;0,R385/W385-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y385" s="16">
+        <f>IF(R385&gt;0,S385*資金模擬!$B$7/R385,0)</f>
+        <v/>
+      </c>
+      <c r="Z385" s="2">
+        <f>IF(OR(Z384=1,R385&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="B386" s="7" t="n">
+        <v>46278.08333333334</v>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G386" s="17" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="H386" s="17" t="n">
+        <v>0.2396707</v>
+      </c>
+      <c r="I386" s="17" t="n">
+        <v>0.2210555</v>
+      </c>
+      <c r="J386" s="17" t="n"/>
+      <c r="K386" s="2" t="n"/>
+      <c r="L386" s="5" t="n"/>
+      <c r="M386" s="16">
+        <f>資金模擬!$B$5*V385</f>
+        <v/>
+      </c>
+      <c r="N386" s="2">
+        <f>IF(Z385=1,"已停止",IF(T385&gt;=M386,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O386" s="16">
+        <f>IF(N386="已下單",M386*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P386" s="4" t="n"/>
+      <c r="Q386" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R386" s="10">
+        <f>R385+Q386</f>
+        <v/>
+      </c>
+      <c r="S386" s="16">
+        <f>S385+IF(N386="已下單",M386,0)</f>
+        <v/>
+      </c>
+      <c r="T386" s="16">
+        <f>R386-S386</f>
+        <v/>
+      </c>
+      <c r="U386" s="2">
+        <f>U385+IF(N386="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V386" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R386,0),MAX(V385,FLOOR(MAX(R386,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W386" s="10">
+        <f>MAX(W385,R386)</f>
+        <v/>
+      </c>
+      <c r="X386" s="4">
+        <f>IF(W386&gt;0,R386/W386-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y386" s="16">
+        <f>IF(R386&gt;0,S386*資金模擬!$B$7/R386,0)</f>
+        <v/>
+      </c>
+      <c r="Z386" s="2">
+        <f>IF(OR(Z385=1,R386&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="B387" s="7" t="n">
+        <v>46278.125</v>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G387" s="17" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="H387" s="17" t="n">
+        <v>0.593446</v>
+      </c>
+      <c r="I387" s="17" t="n">
+        <v>0.64239</v>
+      </c>
+      <c r="J387" s="17" t="n">
+        <v>0.593446</v>
+      </c>
+      <c r="K387" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L387" s="5">
+        <f>交易明細!K194</f>
+        <v/>
+      </c>
+      <c r="M387" s="16">
+        <f>M382</f>
+        <v/>
+      </c>
+      <c r="N387" s="2">
+        <f>N382</f>
+        <v/>
+      </c>
+      <c r="O387" s="16">
+        <f>O382</f>
+        <v/>
+      </c>
+      <c r="P387" s="4">
+        <f>交易明細!L194</f>
+        <v/>
+      </c>
+      <c r="Q387" s="10">
+        <f>IF(N387="已下單",O387*P387,0)</f>
+        <v/>
+      </c>
+      <c r="R387" s="10">
+        <f>R386+Q387</f>
+        <v/>
+      </c>
+      <c r="S387" s="16">
+        <f>S386-IF(N387="已下單",M387,0)</f>
+        <v/>
+      </c>
+      <c r="T387" s="16">
+        <f>R387-S387</f>
+        <v/>
+      </c>
+      <c r="U387" s="2">
+        <f>U386-IF(N387="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V387" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R387,0),MAX(V386,FLOOR(MAX(R387,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W387" s="10">
+        <f>MAX(W386,R387)</f>
+        <v/>
+      </c>
+      <c r="X387" s="4">
+        <f>IF(W387&gt;0,R387/W387-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y387" s="16">
+        <f>IF(R387&gt;0,S387*資金模擬!$B$7/R387,0)</f>
+        <v/>
+      </c>
+      <c r="Z387" s="2">
+        <f>IF(OR(Z386=1,R387&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="B388" s="7" t="n">
+        <v>46278.125</v>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G388" s="17" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="H388" s="17" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="I388" s="17" t="n">
+        <v>1.3414</v>
+      </c>
+      <c r="J388" s="17" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="K388" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L388" s="5">
+        <f>交易明細!K195</f>
+        <v/>
+      </c>
+      <c r="M388" s="16">
+        <f>M385</f>
+        <v/>
+      </c>
+      <c r="N388" s="2">
+        <f>N385</f>
+        <v/>
+      </c>
+      <c r="O388" s="16">
+        <f>O385</f>
+        <v/>
+      </c>
+      <c r="P388" s="4">
+        <f>交易明細!L195</f>
+        <v/>
+      </c>
+      <c r="Q388" s="10">
+        <f>IF(N388="已下單",O388*P388,0)</f>
+        <v/>
+      </c>
+      <c r="R388" s="10">
+        <f>R387+Q388</f>
+        <v/>
+      </c>
+      <c r="S388" s="16">
+        <f>S387-IF(N388="已下單",M388,0)</f>
+        <v/>
+      </c>
+      <c r="T388" s="16">
+        <f>R388-S388</f>
+        <v/>
+      </c>
+      <c r="U388" s="2">
+        <f>U387-IF(N388="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V388" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R388,0),MAX(V387,FLOOR(MAX(R388,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W388" s="10">
+        <f>MAX(W387,R388)</f>
+        <v/>
+      </c>
+      <c r="X388" s="4">
+        <f>IF(W388&gt;0,R388/W388-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y388" s="16">
+        <f>IF(R388&gt;0,S388*資金模擬!$B$7/R388,0)</f>
+        <v/>
+      </c>
+      <c r="Z388" s="2">
+        <f>IF(OR(Z387=1,R388&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="B389" s="7" t="n">
+        <v>46278.20833333334</v>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>VVV_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G389" s="17" t="n">
+        <v>23.956</v>
+      </c>
+      <c r="H389" s="17" t="n">
+        <v>24.67468</v>
+      </c>
+      <c r="I389" s="17" t="n">
+        <v>22.7582</v>
+      </c>
+      <c r="J389" s="17" t="n"/>
+      <c r="K389" s="2" t="n"/>
+      <c r="L389" s="5" t="n"/>
+      <c r="M389" s="16">
+        <f>資金模擬!$B$5*V388</f>
+        <v/>
+      </c>
+      <c r="N389" s="2">
+        <f>IF(Z388=1,"已停止",IF(T388&gt;=M389,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O389" s="16">
+        <f>IF(N389="已下單",M389*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P389" s="4" t="n"/>
+      <c r="Q389" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R389" s="10">
+        <f>R388+Q389</f>
+        <v/>
+      </c>
+      <c r="S389" s="16">
+        <f>S388+IF(N389="已下單",M389,0)</f>
+        <v/>
+      </c>
+      <c r="T389" s="16">
+        <f>R389-S389</f>
+        <v/>
+      </c>
+      <c r="U389" s="2">
+        <f>U388+IF(N389="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V389" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R389,0),MAX(V388,FLOOR(MAX(R389,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W389" s="10">
+        <f>MAX(W388,R389)</f>
+        <v/>
+      </c>
+      <c r="X389" s="4">
+        <f>IF(W389&gt;0,R389/W389-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y389" s="16">
+        <f>IF(R389&gt;0,S389*資金模擬!$B$7/R389,0)</f>
+        <v/>
+      </c>
+      <c r="Z389" s="2">
+        <f>IF(OR(Z388=1,R389&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="B390" s="7" t="n">
+        <v>46278.29166666666</v>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>VVV_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G390" s="17" t="n">
+        <v>23.956</v>
+      </c>
+      <c r="H390" s="17" t="n">
+        <v>24.67468</v>
+      </c>
+      <c r="I390" s="17" t="n">
+        <v>22.7582</v>
+      </c>
+      <c r="J390" s="17" t="n">
+        <v>24.67468</v>
+      </c>
+      <c r="K390" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L390" s="5">
+        <f>交易明細!K197</f>
+        <v/>
+      </c>
+      <c r="M390" s="16">
+        <f>M389</f>
+        <v/>
+      </c>
+      <c r="N390" s="2">
+        <f>N389</f>
+        <v/>
+      </c>
+      <c r="O390" s="16">
+        <f>O389</f>
+        <v/>
+      </c>
+      <c r="P390" s="4">
+        <f>交易明細!L197</f>
+        <v/>
+      </c>
+      <c r="Q390" s="10">
+        <f>IF(N390="已下單",O390*P390,0)</f>
+        <v/>
+      </c>
+      <c r="R390" s="10">
+        <f>R389+Q390</f>
+        <v/>
+      </c>
+      <c r="S390" s="16">
+        <f>S389-IF(N390="已下單",M390,0)</f>
+        <v/>
+      </c>
+      <c r="T390" s="16">
+        <f>R390-S390</f>
+        <v/>
+      </c>
+      <c r="U390" s="2">
+        <f>U389-IF(N390="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V390" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R390,0),MAX(V389,FLOOR(MAX(R390,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W390" s="10">
+        <f>MAX(W389,R390)</f>
+        <v/>
+      </c>
+      <c r="X390" s="4">
+        <f>IF(W390&gt;0,R390/W390-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y390" s="16">
+        <f>IF(R390&gt;0,S390*資金模擬!$B$7/R390,0)</f>
+        <v/>
+      </c>
+      <c r="Z390" s="2">
+        <f>IF(OR(Z389=1,R390&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="B391" s="7" t="n">
+        <v>46278.45833333334</v>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>MARSCOIN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G391" s="17" t="n">
+        <v>0.11779</v>
+      </c>
+      <c r="H391" s="17" t="n">
+        <v>0.1142563</v>
+      </c>
+      <c r="I391" s="17" t="n">
+        <v>0.1236795</v>
+      </c>
+      <c r="J391" s="17" t="n">
+        <v>0.1236795</v>
+      </c>
+      <c r="K391" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L391" s="5">
+        <f>交易明細!K193</f>
+        <v/>
+      </c>
+      <c r="M391" s="16">
+        <f>M381</f>
+        <v/>
+      </c>
+      <c r="N391" s="2">
+        <f>N381</f>
+        <v/>
+      </c>
+      <c r="O391" s="16">
+        <f>O381</f>
+        <v/>
+      </c>
+      <c r="P391" s="4">
+        <f>交易明細!L193</f>
+        <v/>
+      </c>
+      <c r="Q391" s="10">
+        <f>IF(N391="已下單",O391*P391,0)</f>
+        <v/>
+      </c>
+      <c r="R391" s="10">
+        <f>R390+Q391</f>
+        <v/>
+      </c>
+      <c r="S391" s="16">
+        <f>S390-IF(N391="已下單",M391,0)</f>
+        <v/>
+      </c>
+      <c r="T391" s="16">
+        <f>R391-S391</f>
+        <v/>
+      </c>
+      <c r="U391" s="2">
+        <f>U390-IF(N391="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V391" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R391,0),MAX(V390,FLOOR(MAX(R391,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W391" s="10">
+        <f>MAX(W390,R391)</f>
+        <v/>
+      </c>
+      <c r="X391" s="4">
+        <f>IF(W391&gt;0,R391/W391-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y391" s="16">
+        <f>IF(R391&gt;0,S391*資金模擬!$B$7/R391,0)</f>
+        <v/>
+      </c>
+      <c r="Z391" s="2">
+        <f>IF(OR(Z390=1,R391&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="B392" s="7" t="n">
+        <v>46278.45833333334</v>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>AKE_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G392" s="17" t="n">
+        <v>0.0164847</v>
+      </c>
+      <c r="H392" s="17" t="n">
+        <v>0.016979241</v>
+      </c>
+      <c r="I392" s="17" t="n">
+        <v>0.015660465</v>
+      </c>
+      <c r="J392" s="17" t="n"/>
+      <c r="K392" s="2" t="n"/>
+      <c r="L392" s="5" t="n"/>
+      <c r="M392" s="16">
+        <f>資金模擬!$B$5*V391</f>
+        <v/>
+      </c>
+      <c r="N392" s="2">
+        <f>IF(Z391=1,"已停止",IF(T391&gt;=M392,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O392" s="16">
+        <f>IF(N392="已下單",M392*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P392" s="4" t="n"/>
+      <c r="Q392" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R392" s="10">
+        <f>R391+Q392</f>
+        <v/>
+      </c>
+      <c r="S392" s="16">
+        <f>S391+IF(N392="已下單",M392,0)</f>
+        <v/>
+      </c>
+      <c r="T392" s="16">
+        <f>R392-S392</f>
+        <v/>
+      </c>
+      <c r="U392" s="2">
+        <f>U391+IF(N392="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V392" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R392,0),MAX(V391,FLOOR(MAX(R392,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W392" s="10">
+        <f>MAX(W391,R392)</f>
+        <v/>
+      </c>
+      <c r="X392" s="4">
+        <f>IF(W392&gt;0,R392/W392-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y392" s="16">
+        <f>IF(R392&gt;0,S392*資金模擬!$B$7/R392,0)</f>
+        <v/>
+      </c>
+      <c r="Z392" s="2">
+        <f>IF(OR(Z391=1,R392&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="B393" s="7" t="n">
+        <v>46278.45833333334</v>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G393" s="17" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="H393" s="17" t="n">
+        <v>0.5724939999999999</v>
+      </c>
+      <c r="I393" s="17" t="n">
+        <v>0.61971</v>
+      </c>
+      <c r="J393" s="17" t="n"/>
+      <c r="K393" s="2" t="n"/>
+      <c r="L393" s="5" t="n"/>
+      <c r="M393" s="16">
+        <f>資金模擬!$B$5*V392</f>
+        <v/>
+      </c>
+      <c r="N393" s="2">
+        <f>IF(Z392=1,"已停止",IF(T392&gt;=M393,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O393" s="16">
+        <f>IF(N393="已下單",M393*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P393" s="4" t="n"/>
+      <c r="Q393" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R393" s="10">
+        <f>R392+Q393</f>
+        <v/>
+      </c>
+      <c r="S393" s="16">
+        <f>S392+IF(N393="已下單",M393,0)</f>
+        <v/>
+      </c>
+      <c r="T393" s="16">
+        <f>R393-S393</f>
+        <v/>
+      </c>
+      <c r="U393" s="2">
+        <f>U392+IF(N393="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V393" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R393,0),MAX(V392,FLOOR(MAX(R393,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W393" s="10">
+        <f>MAX(W392,R393)</f>
+        <v/>
+      </c>
+      <c r="X393" s="4">
+        <f>IF(W393&gt;0,R393/W393-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y393" s="16">
+        <f>IF(R393&gt;0,S393*資金模擬!$B$7/R393,0)</f>
+        <v/>
+      </c>
+      <c r="Z393" s="2">
+        <f>IF(OR(Z392=1,R393&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B394" s="7" t="n">
+        <v>46278.5</v>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G394" s="17" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="H394" s="17" t="n">
+        <v>0.2396707</v>
+      </c>
+      <c r="I394" s="17" t="n">
+        <v>0.2210555</v>
+      </c>
+      <c r="J394" s="17" t="n">
+        <v>0.2396707</v>
+      </c>
+      <c r="K394" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L394" s="5">
+        <f>交易明細!K196</f>
+        <v/>
+      </c>
+      <c r="M394" s="16">
+        <f>M386</f>
+        <v/>
+      </c>
+      <c r="N394" s="2">
+        <f>N386</f>
+        <v/>
+      </c>
+      <c r="O394" s="16">
+        <f>O386</f>
+        <v/>
+      </c>
+      <c r="P394" s="4">
+        <f>交易明細!L196</f>
+        <v/>
+      </c>
+      <c r="Q394" s="10">
+        <f>IF(N394="已下單",O394*P394,0)</f>
+        <v/>
+      </c>
+      <c r="R394" s="10">
+        <f>R393+Q394</f>
+        <v/>
+      </c>
+      <c r="S394" s="16">
+        <f>S393-IF(N394="已下單",M394,0)</f>
+        <v/>
+      </c>
+      <c r="T394" s="16">
+        <f>R394-S394</f>
+        <v/>
+      </c>
+      <c r="U394" s="2">
+        <f>U393-IF(N394="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V394" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R394,0),MAX(V393,FLOOR(MAX(R394,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W394" s="10">
+        <f>MAX(W393,R394)</f>
+        <v/>
+      </c>
+      <c r="X394" s="4">
+        <f>IF(W394&gt;0,R394/W394-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y394" s="16">
+        <f>IF(R394&gt;0,S394*資金模擬!$B$7/R394,0)</f>
+        <v/>
+      </c>
+      <c r="Z394" s="2">
+        <f>IF(OR(Z393=1,R394&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="B395" s="7" t="n">
+        <v>46278.5</v>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>MARSCOIN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G395" s="17" t="n">
+        <v>0.11416</v>
+      </c>
+      <c r="H395" s="17" t="n">
+        <v>0.1107352</v>
+      </c>
+      <c r="I395" s="17" t="n">
+        <v>0.119868</v>
+      </c>
+      <c r="J395" s="17" t="n"/>
+      <c r="K395" s="2" t="n"/>
+      <c r="L395" s="5" t="n"/>
+      <c r="M395" s="16">
+        <f>資金模擬!$B$5*V394</f>
+        <v/>
+      </c>
+      <c r="N395" s="2">
+        <f>IF(Z394=1,"已停止",IF(T394&gt;=M395,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O395" s="16">
+        <f>IF(N395="已下單",M395*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P395" s="4" t="n"/>
+      <c r="Q395" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R395" s="10">
+        <f>R394+Q395</f>
+        <v/>
+      </c>
+      <c r="S395" s="16">
+        <f>S394+IF(N395="已下單",M395,0)</f>
+        <v/>
+      </c>
+      <c r="T395" s="16">
+        <f>R395-S395</f>
+        <v/>
+      </c>
+      <c r="U395" s="2">
+        <f>U394+IF(N395="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V395" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R395,0),MAX(V394,FLOOR(MAX(R395,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W395" s="10">
+        <f>MAX(W394,R395)</f>
+        <v/>
+      </c>
+      <c r="X395" s="4">
+        <f>IF(W395&gt;0,R395/W395-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y395" s="16">
+        <f>IF(R395&gt;0,S395*資金模擬!$B$7/R395,0)</f>
+        <v/>
+      </c>
+      <c r="Z395" s="2">
+        <f>IF(OR(Z394=1,R395&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="B396" s="7" t="n">
+        <v>46278.5</v>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G396" s="17" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="H396" s="17" t="n">
+        <v>1.22317</v>
+      </c>
+      <c r="I396" s="17" t="n">
+        <v>1.32405</v>
+      </c>
+      <c r="J396" s="17" t="n"/>
+      <c r="K396" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L396" s="5" t="n"/>
+      <c r="M396" s="16">
+        <f>資金模擬!$B$5*V395</f>
+        <v/>
+      </c>
+      <c r="N396" s="2">
+        <f>IF(Z395=1,"已停止",IF(T395&gt;=M396,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O396" s="16">
+        <f>IF(N396="已下單",M396*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P396" s="4" t="n"/>
+      <c r="Q396" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R396" s="10">
+        <f>R395+Q396</f>
+        <v/>
+      </c>
+      <c r="S396" s="16">
+        <f>S395+IF(N396="已下單",M396,0)</f>
+        <v/>
+      </c>
+      <c r="T396" s="16">
+        <f>R396-S396</f>
+        <v/>
+      </c>
+      <c r="U396" s="2">
+        <f>U395+IF(N396="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V396" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R396,0),MAX(V395,FLOOR(MAX(R396,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W396" s="10">
+        <f>MAX(W395,R396)</f>
+        <v/>
+      </c>
+      <c r="X396" s="4">
+        <f>IF(W396&gt;0,R396/W396-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y396" s="16">
+        <f>IF(R396&gt;0,S396*資金模擬!$B$7/R396,0)</f>
+        <v/>
+      </c>
+      <c r="Z396" s="2">
+        <f>IF(OR(Z395=1,R396&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="B397" s="7" t="n">
+        <v>46278.58333333334</v>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>AKE_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G397" s="17" t="n">
+        <v>0.0164847</v>
+      </c>
+      <c r="H397" s="17" t="n">
+        <v>0.016979241</v>
+      </c>
+      <c r="I397" s="17" t="n">
+        <v>0.015660465</v>
+      </c>
+      <c r="J397" s="17" t="n">
+        <v>0.015660465</v>
+      </c>
+      <c r="K397" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L397" s="5">
+        <f>交易明細!K198</f>
+        <v/>
+      </c>
+      <c r="M397" s="16">
+        <f>M392</f>
+        <v/>
+      </c>
+      <c r="N397" s="2">
+        <f>N392</f>
+        <v/>
+      </c>
+      <c r="O397" s="16">
+        <f>O392</f>
+        <v/>
+      </c>
+      <c r="P397" s="4">
+        <f>交易明細!L198</f>
+        <v/>
+      </c>
+      <c r="Q397" s="10">
+        <f>IF(N397="已下單",O397*P397,0)</f>
+        <v/>
+      </c>
+      <c r="R397" s="10">
+        <f>R396+Q397</f>
+        <v/>
+      </c>
+      <c r="S397" s="16">
+        <f>S396-IF(N397="已下單",M397,0)</f>
+        <v/>
+      </c>
+      <c r="T397" s="16">
+        <f>R397-S397</f>
+        <v/>
+      </c>
+      <c r="U397" s="2">
+        <f>U396-IF(N397="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V397" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R397,0),MAX(V396,FLOOR(MAX(R397,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W397" s="10">
+        <f>MAX(W396,R397)</f>
+        <v/>
+      </c>
+      <c r="X397" s="4">
+        <f>IF(W397&gt;0,R397/W397-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y397" s="16">
+        <f>IF(R397&gt;0,S397*資金模擬!$B$7/R397,0)</f>
+        <v/>
+      </c>
+      <c r="Z397" s="2">
+        <f>IF(OR(Z396=1,R397&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="B398" s="7" t="n">
+        <v>46278.625</v>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G398" s="17" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="H398" s="17" t="n">
+        <v>0.5724939999999999</v>
+      </c>
+      <c r="I398" s="17" t="n">
+        <v>0.61971</v>
+      </c>
+      <c r="J398" s="17" t="n">
+        <v>0.5724939999999999</v>
+      </c>
+      <c r="K398" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L398" s="5">
+        <f>交易明細!K199</f>
+        <v/>
+      </c>
+      <c r="M398" s="16">
+        <f>M393</f>
+        <v/>
+      </c>
+      <c r="N398" s="2">
+        <f>N393</f>
+        <v/>
+      </c>
+      <c r="O398" s="16">
+        <f>O393</f>
+        <v/>
+      </c>
+      <c r="P398" s="4">
+        <f>交易明細!L199</f>
+        <v/>
+      </c>
+      <c r="Q398" s="10">
+        <f>IF(N398="已下單",O398*P398,0)</f>
+        <v/>
+      </c>
+      <c r="R398" s="10">
+        <f>R397+Q398</f>
+        <v/>
+      </c>
+      <c r="S398" s="16">
+        <f>S397-IF(N398="已下單",M398,0)</f>
+        <v/>
+      </c>
+      <c r="T398" s="16">
+        <f>R398-S398</f>
+        <v/>
+      </c>
+      <c r="U398" s="2">
+        <f>U397-IF(N398="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V398" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R398,0),MAX(V397,FLOOR(MAX(R398,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W398" s="10">
+        <f>MAX(W397,R398)</f>
+        <v/>
+      </c>
+      <c r="X398" s="4">
+        <f>IF(W398&gt;0,R398/W398-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y398" s="16">
+        <f>IF(R398&gt;0,S398*資金模擬!$B$7/R398,0)</f>
+        <v/>
+      </c>
+      <c r="Z398" s="2">
+        <f>IF(OR(Z397=1,R398&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="B399" s="7" t="n">
+        <v>46278.625</v>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>MARSCOIN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G399" s="17" t="n">
+        <v>0.11416</v>
+      </c>
+      <c r="H399" s="17" t="n">
+        <v>0.1107352</v>
+      </c>
+      <c r="I399" s="17" t="n">
+        <v>0.119868</v>
+      </c>
+      <c r="J399" s="17" t="n">
+        <v>0.119868</v>
+      </c>
+      <c r="K399" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L399" s="5">
+        <f>交易明細!K200</f>
+        <v/>
+      </c>
+      <c r="M399" s="16">
+        <f>M395</f>
+        <v/>
+      </c>
+      <c r="N399" s="2">
+        <f>N395</f>
+        <v/>
+      </c>
+      <c r="O399" s="16">
+        <f>O395</f>
+        <v/>
+      </c>
+      <c r="P399" s="4">
+        <f>交易明細!L200</f>
+        <v/>
+      </c>
+      <c r="Q399" s="10">
+        <f>IF(N399="已下單",O399*P399,0)</f>
+        <v/>
+      </c>
+      <c r="R399" s="10">
+        <f>R398+Q399</f>
+        <v/>
+      </c>
+      <c r="S399" s="16">
+        <f>S398-IF(N399="已下單",M399,0)</f>
+        <v/>
+      </c>
+      <c r="T399" s="16">
+        <f>R399-S399</f>
+        <v/>
+      </c>
+      <c r="U399" s="2">
+        <f>U398-IF(N399="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V399" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R399,0),MAX(V398,FLOOR(MAX(R399,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W399" s="10">
+        <f>MAX(W398,R399)</f>
+        <v/>
+      </c>
+      <c r="X399" s="4">
+        <f>IF(W399&gt;0,R399/W399-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y399" s="16">
+        <f>IF(R399&gt;0,S399*資金模擬!$B$7/R399,0)</f>
+        <v/>
+      </c>
+      <c r="Z399" s="2">
+        <f>IF(OR(Z398=1,R399&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n">
+        <v>398</v>
+      </c>
+      <c r="B400" s="7" t="n">
+        <v>46278.625</v>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>PUMP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G400" s="17" t="n">
+        <v>0.003747</v>
+      </c>
+      <c r="H400" s="17" t="n">
+        <v>0.00363459</v>
+      </c>
+      <c r="I400" s="17" t="n">
+        <v>0.00393435</v>
+      </c>
+      <c r="J400" s="17" t="n"/>
+      <c r="K400" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L400" s="5" t="n"/>
+      <c r="M400" s="16">
+        <f>資金模擬!$B$5*V399</f>
+        <v/>
+      </c>
+      <c r="N400" s="2">
+        <f>IF(Z399=1,"已停止",IF(T399&gt;=M400,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O400" s="16">
+        <f>IF(N400="已下單",M400*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P400" s="4" t="n"/>
+      <c r="Q400" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R400" s="10">
+        <f>R399+Q400</f>
+        <v/>
+      </c>
+      <c r="S400" s="16">
+        <f>S399+IF(N400="已下單",M400,0)</f>
+        <v/>
+      </c>
+      <c r="T400" s="16">
+        <f>R400-S400</f>
+        <v/>
+      </c>
+      <c r="U400" s="2">
+        <f>U399+IF(N400="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V400" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R400,0),MAX(V399,FLOOR(MAX(R400,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W400" s="10">
+        <f>MAX(W399,R400)</f>
+        <v/>
+      </c>
+      <c r="X400" s="4">
+        <f>IF(W400&gt;0,R400/W400-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y400" s="16">
+        <f>IF(R400&gt;0,S400*資金模擬!$B$7/R400,0)</f>
+        <v/>
+      </c>
+      <c r="Z400" s="2">
+        <f>IF(OR(Z399=1,R400&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B401" s="7" t="n">
+        <v>46278.625</v>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G401" s="17" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="H401" s="17" t="n">
+        <v>0.2177068</v>
+      </c>
+      <c r="I401" s="17" t="n">
+        <v>0.235662</v>
+      </c>
+      <c r="J401" s="17" t="n"/>
+      <c r="K401" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L401" s="5" t="n"/>
+      <c r="M401" s="16">
+        <f>資金模擬!$B$5*V400</f>
+        <v/>
+      </c>
+      <c r="N401" s="2">
+        <f>IF(Z400=1,"已停止",IF(T400&gt;=M401,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O401" s="16">
+        <f>IF(N401="已下單",M401*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P401" s="4" t="n"/>
+      <c r="Q401" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R401" s="10">
+        <f>R400+Q401</f>
+        <v/>
+      </c>
+      <c r="S401" s="16">
+        <f>S400+IF(N401="已下單",M401,0)</f>
+        <v/>
+      </c>
+      <c r="T401" s="16">
+        <f>R401-S401</f>
+        <v/>
+      </c>
+      <c r="U401" s="2">
+        <f>U400+IF(N401="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V401" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R401,0),MAX(V400,FLOOR(MAX(R401,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W401" s="10">
+        <f>MAX(W400,R401)</f>
+        <v/>
+      </c>
+      <c r="X401" s="4">
+        <f>IF(W401&gt;0,R401/W401-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y401" s="16">
+        <f>IF(R401&gt;0,S401*資金模擬!$B$7/R401,0)</f>
+        <v/>
+      </c>
+      <c r="Z401" s="2">
+        <f>IF(OR(Z400=1,R401&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z382"/>
-  <conditionalFormatting sqref="K2:K382">
+  <autoFilter ref="A1:Z401"/>
+  <conditionalFormatting sqref="K2:K401">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -38402,7 +40261,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N382">
+  <conditionalFormatting sqref="N2:N401">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -38410,7 +40269,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q382">
+  <conditionalFormatting sqref="Q2:Q401">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -38475,7 +40334,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-13 01:45（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-13 16:19（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -38679,7 +40538,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$194),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$203),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -38844,7 +40703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC194"/>
+  <dimension ref="A1:AC203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -56030,10 +57889,10 @@
         <v>0.14889</v>
       </c>
       <c r="H179" s="7" t="n">
-        <v>46278.04166666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="I179" s="17" t="n">
-        <v>0.1427</v>
+        <v>0.1393</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
@@ -56226,14 +58085,14 @@
         <v>0.00371385</v>
       </c>
       <c r="H181" s="7" t="n">
-        <v>46278.04166666666</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="I181" s="17" t="n">
-        <v>0.003672</v>
+        <v>0.00371385</v>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K181" s="5">
@@ -56244,11 +58103,7 @@
         <f>IF(C181="做多",I181/E181-1,1-I181/E181)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M181" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M181" s="2" t="inlineStr"/>
       <c r="N181" s="4" t="n">
         <v>-0.04224207961007309</v>
       </c>
@@ -56268,7 +58123,7 @@
         <v>0.006502685891998872</v>
       </c>
       <c r="T181" s="4" t="n">
-        <v>0.04523607577042688</v>
+        <v>0.05</v>
       </c>
       <c r="U181" s="16" t="n">
         <v>1.224382173297189</v>
@@ -56518,10 +58373,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46278.04166666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5696</v>
+        <v>0.5628</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -56557,7 +58412,7 @@
         <v>1281726.24259</v>
       </c>
       <c r="S184" s="4" t="n">
-        <v>0.01194239550403942</v>
+        <v>0.01615735862311207</v>
       </c>
       <c r="T184" s="4" t="n">
         <v>0.02388479100807861</v>
@@ -57290,14 +59145,14 @@
         <v>0.128991</v>
       </c>
       <c r="H192" s="7" t="n">
-        <v>46278.04166666666</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="I192" s="17" t="n">
-        <v>0.13284</v>
+        <v>0.128991</v>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K192" s="5">
@@ -57308,11 +59163,7 @@
         <f>IF(C192="做多",I192/E192-1,1-I192/E192)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M192" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M192" s="2" t="inlineStr"/>
       <c r="N192" s="4" t="n">
         <v>0.02630385487528364</v>
       </c>
@@ -57332,7 +59183,7 @@
         <v>0.01119457946678448</v>
       </c>
       <c r="T192" s="4" t="n">
-        <v>0.0364560318161733</v>
+        <v>0.05</v>
       </c>
       <c r="U192" s="16" t="n">
         <v>0.4313868219392165</v>
@@ -57390,14 +59241,14 @@
         <v>0.1236795</v>
       </c>
       <c r="H193" s="7" t="n">
-        <v>46278.04166666666</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="I193" s="17" t="n">
-        <v>0.11779</v>
+        <v>0.1236795</v>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K193" s="5">
@@ -57408,11 +59259,7 @@
         <f>IF(C193="做多",I193/E193-1,1-I193/E193)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M193" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M193" s="2" t="inlineStr"/>
       <c r="N193" s="4" t="n">
         <v>-0.02636799470986939</v>
       </c>
@@ -57429,10 +59276,10 @@
         <v>1817018.29532</v>
       </c>
       <c r="S193" s="4" t="n">
-        <v>0</v>
+        <v>0.02385601494184575</v>
       </c>
       <c r="T193" s="4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="U193" s="16" t="n">
         <v>2.875093831728709</v>
@@ -57490,14 +59337,14 @@
         <v>0.64239</v>
       </c>
       <c r="H194" s="7" t="n">
-        <v>46278.04166666666</v>
+        <v>46278.125</v>
       </c>
       <c r="I194" s="17" t="n">
-        <v>0.6118</v>
+        <v>0.593446</v>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K194" s="5">
@@ -57508,11 +59355,7 @@
         <f>IF(C194="做多",I194/E194-1,1-I194/E194)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M194" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M194" s="2" t="inlineStr"/>
       <c r="N194" s="4" t="n">
         <v>-0.02595128164305049</v>
       </c>
@@ -57529,10 +59372,10 @@
         <v>2443822.4458</v>
       </c>
       <c r="S194" s="4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T194" s="4" t="n">
-        <v>0</v>
+        <v>0.003269042170644054</v>
       </c>
       <c r="U194" s="16" t="n">
         <v>0.7277946313631973</v>
@@ -57563,9 +59406,885 @@
         <v/>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="n">
+        <v>46278.08333333334</v>
+      </c>
+      <c r="E195" s="17" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="F195" s="17" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="G195" s="17" t="n">
+        <v>1.3414</v>
+      </c>
+      <c r="H195" s="7" t="n">
+        <v>46278.125</v>
+      </c>
+      <c r="I195" s="17" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K195" s="5">
+        <f>(H195-D195)*24</f>
+        <v/>
+      </c>
+      <c r="L195" s="4">
+        <f>IF(C195="做多",I195/E195-1,1-I195/E195)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="4" t="n">
+        <v>0.06485671191553544</v>
+      </c>
+      <c r="O195" s="4" t="n">
+        <v>0.0402440441641955</v>
+      </c>
+      <c r="P195" s="4" t="n">
+        <v>0.05724233461869632</v>
+      </c>
+      <c r="Q195" s="19" t="n">
+        <v>358363.9</v>
+      </c>
+      <c r="R195" s="19" t="n">
+        <v>2323206.5163</v>
+      </c>
+      <c r="S195" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T195" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" s="16" t="n">
+        <v>1.628344958438214</v>
+      </c>
+      <c r="V195" s="16" t="n">
+        <v>0.9374999999999999</v>
+      </c>
+      <c r="W195" s="4" t="n">
+        <v>0.1756477719309932</v>
+      </c>
+      <c r="X195" s="4" t="n">
+        <v>0.1489015459723351</v>
+      </c>
+      <c r="Y195" s="4" t="n">
+        <v>-0.001973460448671305</v>
+      </c>
+      <c r="Z195" s="4" t="n">
+        <v>-0.001188114198741208</v>
+      </c>
+      <c r="AA195" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB195" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC195" s="4">
+        <f>(AB195+2*參數!$B$7)/(AA195+AB195)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="n">
+        <v>46278.08333333334</v>
+      </c>
+      <c r="E196" s="17" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="F196" s="17" t="n">
+        <v>0.2396707</v>
+      </c>
+      <c r="G196" s="17" t="n">
+        <v>0.2210555</v>
+      </c>
+      <c r="H196" s="7" t="n">
+        <v>46278.5</v>
+      </c>
+      <c r="I196" s="17" t="n">
+        <v>0.2396707</v>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K196" s="5">
+        <f>(H196-D196)*24</f>
+        <v/>
+      </c>
+      <c r="L196" s="4">
+        <f>IF(C196="做多",I196/E196-1,1-I196/E196)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="4" t="n">
+        <v>0.02110760049148674</v>
+      </c>
+      <c r="O196" s="4" t="n">
+        <v>0.03676124996549265</v>
+      </c>
+      <c r="P196" s="4" t="n">
+        <v>0.02226947425764747</v>
+      </c>
+      <c r="Q196" s="19" t="n">
+        <v>1450242</v>
+      </c>
+      <c r="R196" s="19" t="n">
+        <v>3111990.00034</v>
+      </c>
+      <c r="S196" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T196" s="4" t="n">
+        <v>0.0336928961278955</v>
+      </c>
+      <c r="U196" s="16" t="n">
+        <v>0.3783995304245745</v>
+      </c>
+      <c r="V196" s="16" t="n">
+        <v>0.8534201954397415</v>
+      </c>
+      <c r="W196" s="4" t="n">
+        <v>-0.06779246814453488</v>
+      </c>
+      <c r="X196" s="4" t="n">
+        <v>-0.02652386729699197</v>
+      </c>
+      <c r="Y196" s="4" t="n">
+        <v>-0.001973460448671305</v>
+      </c>
+      <c r="Z196" s="4" t="n">
+        <v>-0.001188114198741208</v>
+      </c>
+      <c r="AA196" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB196" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC196" s="4">
+        <f>(AB196+2*參數!$B$7)/(AA196+AB196)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>VVV_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="n">
+        <v>46278.20833333334</v>
+      </c>
+      <c r="E197" s="17" t="n">
+        <v>23.956</v>
+      </c>
+      <c r="F197" s="17" t="n">
+        <v>24.67468</v>
+      </c>
+      <c r="G197" s="17" t="n">
+        <v>22.7582</v>
+      </c>
+      <c r="H197" s="7" t="n">
+        <v>46278.29166666666</v>
+      </c>
+      <c r="I197" s="17" t="n">
+        <v>24.67468</v>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K197" s="5">
+        <f>(H197-D197)*24</f>
+        <v/>
+      </c>
+      <c r="L197" s="4">
+        <f>IF(C197="做多",I197/E197-1,1-I197/E197)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="4" t="n">
+        <v>0.02319224362533623</v>
+      </c>
+      <c r="O197" s="4" t="n">
+        <v>0.02012515049149717</v>
+      </c>
+      <c r="P197" s="4" t="n">
+        <v>0.02280781152601419</v>
+      </c>
+      <c r="Q197" s="19" t="n">
+        <v>19198.86</v>
+      </c>
+      <c r="R197" s="19" t="n">
+        <v>2454827.49017</v>
+      </c>
+      <c r="S197" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T197" s="4" t="n">
+        <v>0.004550008348639056</v>
+      </c>
+      <c r="U197" s="16" t="n">
+        <v>2.355414085223603</v>
+      </c>
+      <c r="V197" s="16" t="n">
+        <v>0.732620320855615</v>
+      </c>
+      <c r="W197" s="4" t="n">
+        <v>-0.01346377333222426</v>
+      </c>
+      <c r="X197" s="4" t="n">
+        <v>-0.00897695776279317</v>
+      </c>
+      <c r="Y197" s="4" t="n">
+        <v>0.00058507526195406</v>
+      </c>
+      <c r="Z197" s="4" t="n">
+        <v>-0.001610280944836395</v>
+      </c>
+      <c r="AA197" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB197" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC197" s="4">
+        <f>(AB197+2*參數!$B$7)/(AA197+AB197)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>AKE_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="n">
+        <v>46278.45833333334</v>
+      </c>
+      <c r="E198" s="17" t="n">
+        <v>0.0164847</v>
+      </c>
+      <c r="F198" s="17" t="n">
+        <v>0.016979241</v>
+      </c>
+      <c r="G198" s="17" t="n">
+        <v>0.015660465</v>
+      </c>
+      <c r="H198" s="7" t="n">
+        <v>46278.58333333334</v>
+      </c>
+      <c r="I198" s="17" t="n">
+        <v>0.015660465</v>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="K198" s="5">
+        <f>(H198-D198)*24</f>
+        <v/>
+      </c>
+      <c r="L198" s="4">
+        <f>IF(C198="做多",I198/E198-1,1-I198/E198)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="4" t="n">
+        <v>0.03530852567122023</v>
+      </c>
+      <c r="O198" s="4" t="n">
+        <v>0.03066412929037533</v>
+      </c>
+      <c r="P198" s="4" t="n">
+        <v>0.05175916860704954</v>
+      </c>
+      <c r="Q198" s="19" t="n">
+        <v>16627395</v>
+      </c>
+      <c r="R198" s="19" t="n">
+        <v>1279492.2116761</v>
+      </c>
+      <c r="S198" s="4" t="n">
+        <v>0.006266416737944702</v>
+      </c>
+      <c r="T198" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U198" s="16" t="n">
+        <v>1.16641888456675</v>
+      </c>
+      <c r="V198" s="16" t="n">
+        <v>0.9319167389418938</v>
+      </c>
+      <c r="W198" s="4" t="n">
+        <v>0.08557267091363707</v>
+      </c>
+      <c r="X198" s="4" t="n">
+        <v>0.1904029462738304</v>
+      </c>
+      <c r="Y198" s="4" t="n">
+        <v>-0.0002807767553076879</v>
+      </c>
+      <c r="Z198" s="4" t="n">
+        <v>6.931272133070543e-05</v>
+      </c>
+      <c r="AA198" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB198" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC198" s="4">
+        <f>(AB198+2*參數!$B$7)/(AA198+AB198)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="n">
+        <v>46278.45833333334</v>
+      </c>
+      <c r="E199" s="17" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="F199" s="17" t="n">
+        <v>0.5724939999999999</v>
+      </c>
+      <c r="G199" s="17" t="n">
+        <v>0.61971</v>
+      </c>
+      <c r="H199" s="7" t="n">
+        <v>46278.625</v>
+      </c>
+      <c r="I199" s="17" t="n">
+        <v>0.5724939999999999</v>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K199" s="5">
+        <f>(H199-D199)*24</f>
+        <v/>
+      </c>
+      <c r="L199" s="4">
+        <f>IF(C199="做多",I199/E199-1,1-I199/E199)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="4" t="n">
+        <v>-0.0218760357971497</v>
+      </c>
+      <c r="O199" s="4" t="n">
+        <v>0.03203661733508664</v>
+      </c>
+      <c r="P199" s="4" t="n">
+        <v>-0.04098014364174085</v>
+      </c>
+      <c r="Q199" s="19" t="n">
+        <v>-538336</v>
+      </c>
+      <c r="R199" s="19" t="n">
+        <v>1769968.569</v>
+      </c>
+      <c r="S199" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T199" s="4" t="n">
+        <v>0.01745171128431044</v>
+      </c>
+      <c r="U199" s="16" t="n">
+        <v>0.684186904308496</v>
+      </c>
+      <c r="V199" s="16" t="n">
+        <v>0.9259259259259283</v>
+      </c>
+      <c r="W199" s="4" t="n">
+        <v>0.08181092648108945</v>
+      </c>
+      <c r="X199" s="4" t="n">
+        <v>0.008733624454148603</v>
+      </c>
+      <c r="Y199" s="4" t="n">
+        <v>0.0002807767553076879</v>
+      </c>
+      <c r="Z199" s="4" t="n">
+        <v>-6.931272133070543e-05</v>
+      </c>
+      <c r="AA199" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB199" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC199" s="4">
+        <f>(AB199+2*參數!$B$7)/(AA199+AB199)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>MARSCOIN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="n">
+        <v>46278.5</v>
+      </c>
+      <c r="E200" s="17" t="n">
+        <v>0.11416</v>
+      </c>
+      <c r="F200" s="17" t="n">
+        <v>0.1107352</v>
+      </c>
+      <c r="G200" s="17" t="n">
+        <v>0.119868</v>
+      </c>
+      <c r="H200" s="7" t="n">
+        <v>46278.625</v>
+      </c>
+      <c r="I200" s="17" t="n">
+        <v>0.119868</v>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="K200" s="5">
+        <f>(H200-D200)*24</f>
+        <v/>
+      </c>
+      <c r="L200" s="4">
+        <f>IF(C200="做多",I200/E200-1,1-I200/E200)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="4" t="n">
+        <v>-0.02718363868768636</v>
+      </c>
+      <c r="O200" s="4" t="n">
+        <v>0.03723116438279655</v>
+      </c>
+      <c r="P200" s="4" t="n">
+        <v>-0.04411025890076015</v>
+      </c>
+      <c r="Q200" s="19" t="n">
+        <v>-2353397</v>
+      </c>
+      <c r="R200" s="19" t="n">
+        <v>1260378.77313</v>
+      </c>
+      <c r="S200" s="4" t="n">
+        <v>0.01673090399439381</v>
+      </c>
+      <c r="T200" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U200" s="16" t="n">
+        <v>0.6845291252500373</v>
+      </c>
+      <c r="V200" s="16" t="n">
+        <v>0.7480314960629915</v>
+      </c>
+      <c r="W200" s="4" t="n">
+        <v>0.04624492356842758</v>
+      </c>
+      <c r="X200" s="4" t="n">
+        <v>-0.008658773634917738</v>
+      </c>
+      <c r="Y200" s="4" t="n">
+        <v>0.001314973745824233</v>
+      </c>
+      <c r="Z200" s="4" t="n">
+        <v>0.001197595179174393</v>
+      </c>
+      <c r="AA200" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB200" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC200" s="4">
+        <f>(AB200+2*參數!$B$7)/(AA200+AB200)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="n">
+        <v>46278.5</v>
+      </c>
+      <c r="E201" s="17" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="F201" s="17" t="n">
+        <v>1.22317</v>
+      </c>
+      <c r="G201" s="17" t="n">
+        <v>1.32405</v>
+      </c>
+      <c r="H201" s="7" t="n">
+        <v>46278.66666666666</v>
+      </c>
+      <c r="I201" s="17" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K201" s="5">
+        <f>(H201-D201)*24</f>
+        <v/>
+      </c>
+      <c r="L201" s="4">
+        <f>IF(C201="做多",I201/E201-1,1-I201/E201)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N201" s="4" t="n">
+        <v>-0.03149001536098317</v>
+      </c>
+      <c r="O201" s="4" t="n">
+        <v>0.04700685788213382</v>
+      </c>
+      <c r="P201" s="4" t="n">
+        <v>-0.05684367988032912</v>
+      </c>
+      <c r="Q201" s="19" t="n">
+        <v>-166098.5</v>
+      </c>
+      <c r="R201" s="19" t="n">
+        <v>1633132.5949</v>
+      </c>
+      <c r="S201" s="4" t="n">
+        <v>0.009516256938937206</v>
+      </c>
+      <c r="T201" s="4" t="n">
+        <v>0.04203013481364004</v>
+      </c>
+      <c r="U201" s="16" t="n">
+        <v>2.452428134930138</v>
+      </c>
+      <c r="V201" s="16" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="W201" s="4" t="n">
+        <v>-0.03967416397335244</v>
+      </c>
+      <c r="X201" s="4" t="n">
+        <v>0.1181818181818182</v>
+      </c>
+      <c r="Y201" s="4" t="n">
+        <v>0.001314973745824233</v>
+      </c>
+      <c r="Z201" s="4" t="n">
+        <v>0.001197595179174393</v>
+      </c>
+      <c r="AA201" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB201" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC201" s="4">
+        <f>(AB201+2*參數!$B$7)/(AA201+AB201)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>PUMP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="n">
+        <v>46278.625</v>
+      </c>
+      <c r="E202" s="17" t="n">
+        <v>0.003747</v>
+      </c>
+      <c r="F202" s="17" t="n">
+        <v>0.00363459</v>
+      </c>
+      <c r="G202" s="17" t="n">
+        <v>0.00393435</v>
+      </c>
+      <c r="H202" s="7" t="n">
+        <v>46278.66666666666</v>
+      </c>
+      <c r="I202" s="17" t="n">
+        <v>0.003718</v>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K202" s="5">
+        <f>(H202-D202)*24</f>
+        <v/>
+      </c>
+      <c r="L202" s="4">
+        <f>IF(C202="做多",I202/E202-1,1-I202/E202)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N202" s="4" t="n">
+        <v>-0.02371026576341839</v>
+      </c>
+      <c r="O202" s="4" t="n">
+        <v>0.02110602954508002</v>
+      </c>
+      <c r="P202" s="4" t="n">
+        <v>-0.00349720090953809</v>
+      </c>
+      <c r="Q202" s="19" t="n">
+        <v>-41085587</v>
+      </c>
+      <c r="R202" s="19" t="n">
+        <v>2666544.507709</v>
+      </c>
+      <c r="S202" s="4" t="n">
+        <v>0.009607686148919159</v>
+      </c>
+      <c r="T202" s="4" t="n">
+        <v>0.004536962903656239</v>
+      </c>
+      <c r="U202" s="16" t="n">
+        <v>0.823158869101001</v>
+      </c>
+      <c r="V202" s="16" t="n">
+        <v>0.8260869565217388</v>
+      </c>
+      <c r="W202" s="4" t="n">
+        <v>0.04097422890181679</v>
+      </c>
+      <c r="X202" s="4" t="n">
+        <v>-0.05668358714043986</v>
+      </c>
+      <c r="Y202" s="4" t="n">
+        <v>0.002569852498747971</v>
+      </c>
+      <c r="Z202" s="4" t="n">
+        <v>0.00197611890247551</v>
+      </c>
+      <c r="AA202" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB202" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC202" s="4">
+        <f>(AB202+2*參數!$B$7)/(AA202+AB202)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="n">
+        <v>46278.625</v>
+      </c>
+      <c r="E203" s="17" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="F203" s="17" t="n">
+        <v>0.2177068</v>
+      </c>
+      <c r="G203" s="17" t="n">
+        <v>0.235662</v>
+      </c>
+      <c r="H203" s="7" t="n">
+        <v>46278.66666666666</v>
+      </c>
+      <c r="I203" s="17" t="n">
+        <v>0.22431</v>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K203" s="5">
+        <f>(H203-D203)*24</f>
+        <v/>
+      </c>
+      <c r="L203" s="4">
+        <f>IF(C203="做多",I203/E203-1,1-I203/E203)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N203" s="4" t="n">
+        <v>-0.02383437717466952</v>
+      </c>
+      <c r="O203" s="4" t="n">
+        <v>0.0296493558421459</v>
+      </c>
+      <c r="P203" s="4" t="n">
+        <v>-0.0325257397552865</v>
+      </c>
+      <c r="Q203" s="19" t="n">
+        <v>-987624</v>
+      </c>
+      <c r="R203" s="19" t="n">
+        <v>1943593.26169</v>
+      </c>
+      <c r="S203" s="4" t="n">
+        <v>0.01327749064337913</v>
+      </c>
+      <c r="T203" s="4" t="n">
+        <v>0.005123863838887965</v>
+      </c>
+      <c r="U203" s="16" t="n">
+        <v>1.125300022122543</v>
+      </c>
+      <c r="V203" s="16" t="n">
+        <v>0.8199999999999997</v>
+      </c>
+      <c r="W203" s="4" t="n">
+        <v>0.07342117474540155</v>
+      </c>
+      <c r="X203" s="4" t="n">
+        <v>-0.009263422969691515</v>
+      </c>
+      <c r="Y203" s="4" t="n">
+        <v>0.002569852498747971</v>
+      </c>
+      <c r="Z203" s="4" t="n">
+        <v>0.00197611890247551</v>
+      </c>
+      <c r="AA203" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB203" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC203" s="4">
+        <f>(AB203+2*參數!$B$7)/(AA203+AB203)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC194"/>
-  <conditionalFormatting sqref="J2:J194">
+  <autoFilter ref="A1:AC203"/>
+  <conditionalFormatting sqref="J2:J203">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -57586,7 +60305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -57672,27 +60391,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -57700,50 +60419,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A2,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PUMP_USDT_PERP</t>
+          <t>USELESS_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -57751,50 +60470,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A3,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>USELESS_USDT_PERP</t>
+          <t>PUMP_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -57802,19 +60521,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A4,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -57825,27 +60544,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -57853,50 +60572,50 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A5,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BULLA_USDT_PERP</t>
+          <t>MARSCOIN_USDT_PERP</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -57904,50 +60623,50 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A6,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HEMI_USDT_PERP</t>
+          <t>BULLA_USDT_PERP</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -57955,50 +60674,50 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A7,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LIT_USDT_PERP</t>
+          <t>HEMI_USDT_PERP</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -58006,50 +60725,50 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A8,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MARSCOIN_USDT_PERP</t>
+          <t>LIT_USDT_PERP</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -58057,19 +60776,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A9,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58080,27 +60799,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -58108,19 +60827,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A10,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58131,27 +60850,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -58159,19 +60878,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A11,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58182,27 +60901,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -58210,19 +60929,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A12,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58233,27 +60952,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -58261,19 +60980,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A13,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58284,27 +61003,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -58312,50 +61031,50 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A14,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>UNI_USDT_PERP</t>
+          <t>VVV_USDT_PERP</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -58363,50 +61082,50 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A15,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DASH_USDT_PERP</t>
+          <t>UNI_USDT_PERP</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -58414,50 +61133,50 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A16,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>VVV_USDT_PERP</t>
+          <t>DASH_USDT_PERP</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -58465,19 +61184,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A17,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58488,27 +61207,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -58516,19 +61235,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A18,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58539,27 +61258,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -58567,19 +61286,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A19,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58590,27 +61309,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -58618,19 +61337,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A20,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58641,27 +61360,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -58669,19 +61388,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A21,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58692,27 +61411,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -58720,19 +61439,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A22,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58743,27 +61462,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -58771,19 +61490,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A23,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58794,27 +61513,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -58822,19 +61541,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A24,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58845,27 +61564,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -58873,19 +61592,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A25,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58896,27 +61615,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -58924,19 +61643,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A26,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58947,27 +61666,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -58975,19 +61694,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A27,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -58998,27 +61717,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -59026,19 +61745,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A28,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -59049,27 +61768,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -59077,50 +61796,50 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A29,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SKYAI_USDT_PERP</t>
+          <t>RIVER_USDT_PERP</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -59128,50 +61847,50 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A30,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>XMR_USDT_PERP</t>
+          <t>SKYAI_USDT_PERP</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -59179,50 +61898,50 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A31,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>CRV_USDT_PERP</t>
+          <t>XMR_USDT_PERP</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -59230,50 +61949,50 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A32,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MAGMA_USDT_PERP</t>
+          <t>CRV_USDT_PERP</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -59281,50 +62000,50 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A33,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TRUMP_USDT_PERP</t>
+          <t>MAGMA_USDT_PERP</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -59332,50 +62051,50 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A34,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CHIP_USDT_PERP</t>
+          <t>TRUMP_USDT_PERP</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -59383,50 +62102,50 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A35,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PENGU_USDT_PERP</t>
+          <t>CHIP_USDT_PERP</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -59434,50 +62153,50 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A36,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FARTCOIN_USDT_PERP</t>
+          <t>PENGU_USDT_PERP</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -59485,50 +62204,50 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A37,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TRIA_USDT_PERP</t>
+          <t>FARTCOIN_USDT_PERP</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -59536,50 +62255,50 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A38,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ZEN_USDT_PERP</t>
+          <t>TRIA_USDT_PERP</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -59587,50 +62306,50 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A39,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TAO_USDT_PERP</t>
+          <t>ZEN_USDT_PERP</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -59638,50 +62357,50 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A40,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>KAS_USDT_PERP</t>
+          <t>TAO_USDT_PERP</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -59689,50 +62408,50 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A41,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CASHCAT_USDT_PERP</t>
+          <t>KAS_USDT_PERP</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -59740,50 +62459,50 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A42,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>INJ_USDT_PERP</t>
+          <t>CASHCAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -59791,50 +62510,50 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A43,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ICP_USDT_PERP</t>
+          <t>INJ_USDT_PERP</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -59842,50 +62561,50 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A44,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FF_USDT_PERP</t>
+          <t>ICP_USDT_PERP</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -59893,50 +62612,50 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A45,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>KAT_USDT_PERP</t>
+          <t>FF_USDT_PERP</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -59944,50 +62663,50 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A46,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MET_USDT_PERP</t>
+          <t>KAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -59995,50 +62714,50 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A47,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LAB_USDT_PERP</t>
+          <t>MET_USDT_PERP</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$C$2:$C$194,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$C$2:$C$203,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$C$2:$C$194,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$C$2:$C$203,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -60046,24 +62765,75 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$194,交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$194,交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$194,$A48,交易明細!$J$2:$J$194,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B49" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49)</f>
+        <v/>
+      </c>
+      <c r="C49" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$C$2:$C$203,"做多")</f>
+        <v/>
+      </c>
+      <c r="D49" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$C$2:$C$203,"做空")</f>
+        <v/>
+      </c>
+      <c r="E49" s="2">
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F49" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G49" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"止損")</f>
+        <v/>
+      </c>
+      <c r="H49" s="4">
+        <f>IFERROR(F49/E49,0)</f>
+        <v/>
+      </c>
+      <c r="I49" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J49" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K49" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L49" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L48"/>
+  <autoFilter ref="A1:L49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -64270,11 +67040,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C231" s="2" t="inlineStr"/>
       <c r="D231" s="2" t="n"/>
       <c r="E231" s="17" t="n"/>
       <c r="F231" s="17" t="n"/>
@@ -65444,11 +68210,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C296" s="2" t="inlineStr"/>
       <c r="D296" s="2" t="n"/>
       <c r="E296" s="17" t="n"/>
       <c r="F296" s="17" t="n"/>
@@ -65902,7 +68664,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C321" s="2" t="inlineStr"/>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D321" s="2" t="n"/>
       <c r="E321" s="17" t="n"/>
       <c r="F321" s="17" t="n"/>
@@ -67252,7 +70018,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr"/>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="17" t="n"/>
       <c r="F396" s="17" t="n"/>
@@ -68098,11 +70868,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C443" s="2" t="inlineStr"/>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="17" t="n"/>
       <c r="F443" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$401</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$405</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$401</f>
+              <f>'資金明細'!$R$2:$R$405</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 16:19（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 17:04（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$203,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$206,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$J$2:$J$203,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$J$2:$J$206,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$J$2:$J$203,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$J$2:$J$206,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$J$2:$J$203,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$J$2:$J$206,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$203,"&lt;&gt;未平倉",交易明細!$L$2:$L$203,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$206,"&lt;&gt;未平倉",交易明細!$L$2:$L$206,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$B$2:$B$203,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$B$2:$B$206,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$203,"做多",交易明細!$J$2:$J$203,"&lt;&gt;未平倉",交易明細!$L$2:$L$203,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉",交易明細!$L$2:$L$206,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$B$2:$B$203,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$B$2:$B$206,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$203,"做空",交易明細!$J$2:$J$203,"&lt;&gt;未平倉",交易明細!$L$2:$L$203,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉",交易明細!$L$2:$L$206,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,19 +1085,19 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -1108,47 +1108,70 @@
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1214,7 +1237,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R401</f>
+        <f>資金明細!R405</f>
         <v/>
       </c>
     </row>
@@ -1252,7 +1275,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$401)</f>
+        <f>MAX(資金明細!$R$2:$R$405)</f>
         <v/>
       </c>
     </row>
@@ -1271,7 +1294,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$401)</f>
+        <f>MIN(資金明細!$R$2:$R$405)</f>
         <v/>
       </c>
     </row>
@@ -1291,7 +1314,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$401)</f>
+        <f>MIN(資金明細!$X$2:$X$405)</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1333,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$401,"進場",資金明細!$N$2:$N$401,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$405,"進場",資金明細!$N$2:$N$405,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1329,7 +1352,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$401,"進場",資金明細!$N$2:$N$401,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$405,"進場",資金明細!$N$2:$N$405,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1340,7 +1363,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$401,"出場",資金明細!$N$2:$N$401,"已下單",資金明細!$K$2:$K$401,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$405,"出場",資金明細!$N$2:$N$405,"已下單",資金明細!$K$2:$K$405,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1351,7 +1374,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$203),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$206),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1360,7 +1383,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$401,"出場",資金明細!$N$2:$N$401,"已下單",資金明細!$K$2:$K$401,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$405,"出場",資金明細!$N$2:$N$405,"已下單",資金明細!$K$2:$K$405,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1376,7 +1399,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$401,"出場",資金明細!$N$2:$N$401,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$405,"出場",資金明細!$N$2:$N$405,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1392,7 +1415,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$401)</f>
+        <f>MAX(資金明細!$U$2:$U$405)</f>
         <v/>
       </c>
     </row>
@@ -1408,7 +1431,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$401)</f>
+        <f>MAX(資金明細!$S$2:$S$405)</f>
         <v/>
       </c>
     </row>
@@ -1419,7 +1442,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V401</f>
+        <f>B5*資金明細!V405</f>
         <v/>
       </c>
     </row>
@@ -1430,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N355="已下單",資金明細!O355*交易明細!L179,0)+IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N396="已下單",資金明細!O396*交易明細!L201,0)+IF(資金明細!N400="已下單",資金明細!O400*交易明細!L202,0)+IF(資金明細!N401="已下單",資金明細!O401*交易明細!L203,0)</f>
+        <f>IF(資金明細!N355="已下單",資金明細!O355*交易明細!L179,0)+IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N400="已下單",資金明細!O400*交易明細!L202,0)+IF(資金明細!N401="已下單",資金明細!O401*交易明細!L203,0)+IF(資金明細!N403="已下單",資金明細!O403*交易明細!L204,0)+IF(資金明細!N404="已下單",資金明細!O404*交易明細!L205,0)+IF(資金明細!N405="已下單",資金明細!O405*交易明細!L206,0)</f>
         <v/>
       </c>
     </row>
@@ -1441,7 +1464,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$401)</f>
+        <f>MAX(資金明細!$Y$2:$Y$405)</f>
         <v/>
       </c>
     </row>
@@ -1463,7 +1486,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$401,MATCH(1,資金明細!$Z$2:$Z$401,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$405,MATCH(1,資金明細!$Z$2:$Z$405,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1474,7 +1497,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$401,"進場",資金明細!$N$2:$N$401,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$405,"進場",資金明細!$N$2:$N$405,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1539,7 +1562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z401"/>
+  <dimension ref="A1:Z405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -39695,11 +39718,7 @@
         <v>1.32405</v>
       </c>
       <c r="J396" s="17" t="n"/>
-      <c r="K396" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K396" s="2" t="n"/>
       <c r="L396" s="5" t="n"/>
       <c r="M396" s="16">
         <f>資金模擬!$B$5*V395</f>
@@ -40251,9 +40270,394 @@
         <v/>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B402" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G402" s="17" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="H402" s="17" t="n">
+        <v>1.22317</v>
+      </c>
+      <c r="I402" s="17" t="n">
+        <v>1.32405</v>
+      </c>
+      <c r="J402" s="17" t="n">
+        <v>1.22317</v>
+      </c>
+      <c r="K402" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L402" s="5">
+        <f>交易明細!K201</f>
+        <v/>
+      </c>
+      <c r="M402" s="16">
+        <f>M396</f>
+        <v/>
+      </c>
+      <c r="N402" s="2">
+        <f>N396</f>
+        <v/>
+      </c>
+      <c r="O402" s="16">
+        <f>O396</f>
+        <v/>
+      </c>
+      <c r="P402" s="4">
+        <f>交易明細!L201</f>
+        <v/>
+      </c>
+      <c r="Q402" s="10">
+        <f>IF(N402="已下單",O402*P402,0)</f>
+        <v/>
+      </c>
+      <c r="R402" s="10">
+        <f>R401+Q402</f>
+        <v/>
+      </c>
+      <c r="S402" s="16">
+        <f>S401-IF(N402="已下單",M402,0)</f>
+        <v/>
+      </c>
+      <c r="T402" s="16">
+        <f>R402-S402</f>
+        <v/>
+      </c>
+      <c r="U402" s="2">
+        <f>U401-IF(N402="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V402" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R402,0),MAX(V401,FLOOR(MAX(R402,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W402" s="10">
+        <f>MAX(W401,R402)</f>
+        <v/>
+      </c>
+      <c r="X402" s="4">
+        <f>IF(W402&gt;0,R402/W402-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y402" s="16">
+        <f>IF(R402&gt;0,S402*資金模擬!$B$7/R402,0)</f>
+        <v/>
+      </c>
+      <c r="Z402" s="2">
+        <f>IF(OR(Z401=1,R402&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n">
+        <v>401</v>
+      </c>
+      <c r="B403" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G403" s="17" t="n">
+        <v>0.06694</v>
+      </c>
+      <c r="H403" s="17" t="n">
+        <v>0.0649318</v>
+      </c>
+      <c r="I403" s="17" t="n">
+        <v>0.070287</v>
+      </c>
+      <c r="J403" s="17" t="n"/>
+      <c r="K403" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L403" s="5" t="n"/>
+      <c r="M403" s="16">
+        <f>資金模擬!$B$5*V402</f>
+        <v/>
+      </c>
+      <c r="N403" s="2">
+        <f>IF(Z402=1,"已停止",IF(T402&gt;=M403,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O403" s="16">
+        <f>IF(N403="已下單",M403*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P403" s="4" t="n"/>
+      <c r="Q403" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R403" s="10">
+        <f>R402+Q403</f>
+        <v/>
+      </c>
+      <c r="S403" s="16">
+        <f>S402+IF(N403="已下單",M403,0)</f>
+        <v/>
+      </c>
+      <c r="T403" s="16">
+        <f>R403-S403</f>
+        <v/>
+      </c>
+      <c r="U403" s="2">
+        <f>U402+IF(N403="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V403" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R403,0),MAX(V402,FLOOR(MAX(R403,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W403" s="10">
+        <f>MAX(W402,R403)</f>
+        <v/>
+      </c>
+      <c r="X403" s="4">
+        <f>IF(W403&gt;0,R403/W403-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y403" s="16">
+        <f>IF(R403&gt;0,S403*資金模擬!$B$7/R403,0)</f>
+        <v/>
+      </c>
+      <c r="Z403" s="2">
+        <f>IF(OR(Z402=1,R403&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n">
+        <v>402</v>
+      </c>
+      <c r="B404" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>VVV_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G404" s="17" t="n">
+        <v>22.673</v>
+      </c>
+      <c r="H404" s="17" t="n">
+        <v>21.99281</v>
+      </c>
+      <c r="I404" s="17" t="n">
+        <v>23.80665</v>
+      </c>
+      <c r="J404" s="17" t="n"/>
+      <c r="K404" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L404" s="5" t="n"/>
+      <c r="M404" s="16">
+        <f>資金模擬!$B$5*V403</f>
+        <v/>
+      </c>
+      <c r="N404" s="2">
+        <f>IF(Z403=1,"已停止",IF(T403&gt;=M404,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O404" s="16">
+        <f>IF(N404="已下單",M404*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P404" s="4" t="n"/>
+      <c r="Q404" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R404" s="10">
+        <f>R403+Q404</f>
+        <v/>
+      </c>
+      <c r="S404" s="16">
+        <f>S403+IF(N404="已下單",M404,0)</f>
+        <v/>
+      </c>
+      <c r="T404" s="16">
+        <f>R404-S404</f>
+        <v/>
+      </c>
+      <c r="U404" s="2">
+        <f>U403+IF(N404="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V404" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R404,0),MAX(V403,FLOOR(MAX(R404,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W404" s="10">
+        <f>MAX(W403,R404)</f>
+        <v/>
+      </c>
+      <c r="X404" s="4">
+        <f>IF(W404&gt;0,R404/W404-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y404" s="16">
+        <f>IF(R404&gt;0,S404*資金模擬!$B$7/R404,0)</f>
+        <v/>
+      </c>
+      <c r="Z404" s="2">
+        <f>IF(OR(Z403=1,R404&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="B405" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G405" s="17" t="n">
+        <v>0.13497</v>
+      </c>
+      <c r="H405" s="17" t="n">
+        <v>0.1309209</v>
+      </c>
+      <c r="I405" s="17" t="n">
+        <v>0.1417185</v>
+      </c>
+      <c r="J405" s="17" t="n"/>
+      <c r="K405" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L405" s="5" t="n"/>
+      <c r="M405" s="16">
+        <f>資金模擬!$B$5*V404</f>
+        <v/>
+      </c>
+      <c r="N405" s="2">
+        <f>IF(Z404=1,"已停止",IF(T404&gt;=M405,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O405" s="16">
+        <f>IF(N405="已下單",M405*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P405" s="4" t="n"/>
+      <c r="Q405" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R405" s="10">
+        <f>R404+Q405</f>
+        <v/>
+      </c>
+      <c r="S405" s="16">
+        <f>S404+IF(N405="已下單",M405,0)</f>
+        <v/>
+      </c>
+      <c r="T405" s="16">
+        <f>R405-S405</f>
+        <v/>
+      </c>
+      <c r="U405" s="2">
+        <f>U404+IF(N405="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V405" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R405,0),MAX(V404,FLOOR(MAX(R405,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W405" s="10">
+        <f>MAX(W404,R405)</f>
+        <v/>
+      </c>
+      <c r="X405" s="4">
+        <f>IF(W405&gt;0,R405/W405-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y405" s="16">
+        <f>IF(R405&gt;0,S405*資金模擬!$B$7/R405,0)</f>
+        <v/>
+      </c>
+      <c r="Z405" s="2">
+        <f>IF(OR(Z404=1,R405&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z401"/>
-  <conditionalFormatting sqref="K2:K401">
+  <autoFilter ref="A1:Z405"/>
+  <conditionalFormatting sqref="K2:K405">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -40261,7 +40665,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N401">
+  <conditionalFormatting sqref="N2:N405">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -40269,7 +40673,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q401">
+  <conditionalFormatting sqref="Q2:Q405">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -40334,7 +40738,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-13 16:19（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-13 17:04（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -40538,7 +40942,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$203),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$206),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -40703,7 +41107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC203"/>
+  <dimension ref="A1:AC206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -57889,10 +58293,10 @@
         <v>0.14889</v>
       </c>
       <c r="H179" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="I179" s="17" t="n">
-        <v>0.1393</v>
+        <v>0.1385</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
@@ -58373,10 +58777,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5628</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -58412,7 +58816,7 @@
         <v>1281726.24259</v>
       </c>
       <c r="S184" s="4" t="n">
-        <v>0.01615735862311207</v>
+        <v>0.01949420442571126</v>
       </c>
       <c r="T184" s="4" t="n">
         <v>0.02388479100807861</v>
@@ -60009,14 +60413,14 @@
         <v>1.32405</v>
       </c>
       <c r="H201" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="I201" s="17" t="n">
-        <v>1.272</v>
+        <v>1.22317</v>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K201" s="5">
@@ -60027,11 +60431,7 @@
         <f>IF(C201="做多",I201/E201-1,1-I201/E201)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M201" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M201" s="2" t="inlineStr"/>
       <c r="N201" s="4" t="n">
         <v>-0.03149001536098317</v>
       </c>
@@ -60048,7 +60448,7 @@
         <v>1633132.5949</v>
       </c>
       <c r="S201" s="4" t="n">
-        <v>0.009516256938937206</v>
+        <v>0.03</v>
       </c>
       <c r="T201" s="4" t="n">
         <v>0.04203013481364004</v>
@@ -60109,10 +60509,10 @@
         <v>0.00393435</v>
       </c>
       <c r="H202" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="I202" s="17" t="n">
-        <v>0.003718</v>
+        <v>0.003676</v>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
@@ -60148,7 +60548,7 @@
         <v>2666544.507709</v>
       </c>
       <c r="S202" s="4" t="n">
-        <v>0.009607686148919159</v>
+        <v>0.02348545503069122</v>
       </c>
       <c r="T202" s="4" t="n">
         <v>0.004536962903656239</v>
@@ -60209,10 +60609,10 @@
         <v>0.235662</v>
       </c>
       <c r="H203" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="I203" s="17" t="n">
-        <v>0.22431</v>
+        <v>0.22485</v>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
@@ -60251,7 +60651,7 @@
         <v>0.01327749064337913</v>
       </c>
       <c r="T203" s="4" t="n">
-        <v>0.005123863838887965</v>
+        <v>0.01920335056139733</v>
       </c>
       <c r="U203" s="16" t="n">
         <v>1.125300022122543</v>
@@ -60282,9 +60682,309 @@
         <v/>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="E204" s="17" t="n">
+        <v>0.06694</v>
+      </c>
+      <c r="F204" s="17" t="n">
+        <v>0.0649318</v>
+      </c>
+      <c r="G204" s="17" t="n">
+        <v>0.070287</v>
+      </c>
+      <c r="H204" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="I204" s="17" t="n">
+        <v>0.06694</v>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K204" s="5">
+        <f>(H204-D204)*24</f>
+        <v/>
+      </c>
+      <c r="L204" s="4">
+        <f>IF(C204="做多",I204/E204-1,1-I204/E204)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N204" s="4" t="n">
+        <v>-0.02163110201695406</v>
+      </c>
+      <c r="O204" s="4" t="n">
+        <v>0.05683338164555901</v>
+      </c>
+      <c r="P204" s="4" t="n">
+        <v>-0.02280938651874009</v>
+      </c>
+      <c r="Q204" s="19" t="n">
+        <v>-12550292</v>
+      </c>
+      <c r="R204" s="19" t="n">
+        <v>3660542.31503</v>
+      </c>
+      <c r="S204" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T204" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" s="16" t="n">
+        <v>0.6170410304977394</v>
+      </c>
+      <c r="V204" s="16" t="n">
+        <v>0.870848708487084</v>
+      </c>
+      <c r="W204" s="4" t="n">
+        <v>-0.08609589574517806</v>
+      </c>
+      <c r="X204" s="4" t="n">
+        <v>0.08925170068027211</v>
+      </c>
+      <c r="Y204" s="4" t="n">
+        <v>0.004148521748605805</v>
+      </c>
+      <c r="Z204" s="4" t="n">
+        <v>0.005552773695665758</v>
+      </c>
+      <c r="AA204" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB204" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC204" s="4">
+        <f>(AB204+2*參數!$B$7)/(AA204+AB204)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>VVV_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="E205" s="17" t="n">
+        <v>22.673</v>
+      </c>
+      <c r="F205" s="17" t="n">
+        <v>21.99281</v>
+      </c>
+      <c r="G205" s="17" t="n">
+        <v>23.80665</v>
+      </c>
+      <c r="H205" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="I205" s="17" t="n">
+        <v>22.673</v>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K205" s="5">
+        <f>(H205-D205)*24</f>
+        <v/>
+      </c>
+      <c r="L205" s="4">
+        <f>IF(C205="做多",I205/E205-1,1-I205/E205)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N205" s="4" t="n">
+        <v>-0.02309448920677326</v>
+      </c>
+      <c r="O205" s="4" t="n">
+        <v>0.02184826900916101</v>
+      </c>
+      <c r="P205" s="4" t="n">
+        <v>-0.04285072008882129</v>
+      </c>
+      <c r="Q205" s="19" t="n">
+        <v>-7973.100000000006</v>
+      </c>
+      <c r="R205" s="19" t="n">
+        <v>1862546.13313</v>
+      </c>
+      <c r="S205" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T205" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U205" s="16" t="n">
+        <v>1.542546484066931</v>
+      </c>
+      <c r="V205" s="16" t="n">
+        <v>0.9434571890145451</v>
+      </c>
+      <c r="W205" s="4" t="n">
+        <v>0.06339370140216238</v>
+      </c>
+      <c r="X205" s="4" t="n">
+        <v>0.02254699086049328</v>
+      </c>
+      <c r="Y205" s="4" t="n">
+        <v>0.004148521748605805</v>
+      </c>
+      <c r="Z205" s="4" t="n">
+        <v>0.005552773695665758</v>
+      </c>
+      <c r="AA205" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB205" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC205" s="4">
+        <f>(AB205+2*參數!$B$7)/(AA205+AB205)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="E206" s="17" t="n">
+        <v>0.13497</v>
+      </c>
+      <c r="F206" s="17" t="n">
+        <v>0.1309209</v>
+      </c>
+      <c r="G206" s="17" t="n">
+        <v>0.1417185</v>
+      </c>
+      <c r="H206" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="I206" s="17" t="n">
+        <v>0.13497</v>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K206" s="5">
+        <f>(H206-D206)*24</f>
+        <v/>
+      </c>
+      <c r="L206" s="4">
+        <f>IF(C206="做多",I206/E206-1,1-I206/E206)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N206" s="4" t="n">
+        <v>-0.0527091521617068</v>
+      </c>
+      <c r="O206" s="4" t="n">
+        <v>0.06786401863590003</v>
+      </c>
+      <c r="P206" s="4" t="n">
+        <v>-0.00759906914160291</v>
+      </c>
+      <c r="Q206" s="19" t="n">
+        <v>-4457033</v>
+      </c>
+      <c r="R206" s="19" t="n">
+        <v>2751747.85932</v>
+      </c>
+      <c r="S206" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T206" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" s="16" t="n">
+        <v>3.10622767745523</v>
+      </c>
+      <c r="V206" s="16" t="n">
+        <v>0.8714153561517111</v>
+      </c>
+      <c r="W206" s="4" t="n">
+        <v>-0.1647645142499623</v>
+      </c>
+      <c r="X206" s="4" t="n">
+        <v>0.0762439258093216</v>
+      </c>
+      <c r="Y206" s="4" t="n">
+        <v>0.004148521748605805</v>
+      </c>
+      <c r="Z206" s="4" t="n">
+        <v>0.005552773695665758</v>
+      </c>
+      <c r="AA206" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB206" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC206" s="4">
+        <f>(AB206+2*參數!$B$7)/(AA206+AB206)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC203"/>
-  <conditionalFormatting sqref="J2:J203">
+  <autoFilter ref="A1:AC206"/>
+  <conditionalFormatting sqref="J2:J206">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -60391,27 +61091,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -60419,19 +61119,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A2,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -60442,27 +61142,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -60470,19 +61170,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A3,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -60493,27 +61193,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -60521,19 +61221,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A4,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -60544,27 +61244,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -60572,19 +61272,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A5,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -60595,27 +61295,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -60623,19 +61323,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A6,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -60646,27 +61346,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -60674,19 +61374,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A7,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -60697,27 +61397,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -60725,19 +61425,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A8,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -60748,27 +61448,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -60776,19 +61476,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A9,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -60799,27 +61499,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -60827,50 +61527,50 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A10,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ARB_USDT_PERP</t>
+          <t>牛来_USDT_PERP</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -60878,50 +61578,50 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A11,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>牛来_USDT_PERP</t>
+          <t>VVV_USDT_PERP</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -60929,50 +61629,50 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A12,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NEAR_USDT_PERP</t>
+          <t>ARB_USDT_PERP</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -60980,50 +61680,50 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A13,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RAY_USDT_PERP</t>
+          <t>NEAR_USDT_PERP</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -61031,50 +61731,50 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A14,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>VVV_USDT_PERP</t>
+          <t>RAY_USDT_PERP</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -61082,19 +61782,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A15,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61105,27 +61805,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -61133,19 +61833,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A16,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61156,27 +61856,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -61184,19 +61884,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A17,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61207,27 +61907,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -61235,19 +61935,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A18,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61258,27 +61958,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -61286,19 +61986,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A19,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61309,27 +62009,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -61337,19 +62037,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A20,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61360,27 +62060,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -61388,19 +62088,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A21,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61411,27 +62111,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -61439,19 +62139,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A22,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61462,27 +62162,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -61490,19 +62190,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A23,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61513,27 +62213,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -61541,19 +62241,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A24,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61564,27 +62264,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -61592,19 +62292,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A25,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61615,27 +62315,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -61643,19 +62343,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A26,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61666,27 +62366,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -61694,19 +62394,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A27,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61717,27 +62417,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -61745,19 +62445,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A28,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61768,27 +62468,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -61796,50 +62496,50 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A29,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RIVER_USDT_PERP</t>
+          <t>LAB_USDT_PERP</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -61847,50 +62547,50 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A30,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SKYAI_USDT_PERP</t>
+          <t>RIVER_USDT_PERP</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -61898,50 +62598,50 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A31,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>XMR_USDT_PERP</t>
+          <t>SKYAI_USDT_PERP</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -61949,50 +62649,50 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A32,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CRV_USDT_PERP</t>
+          <t>XMR_USDT_PERP</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -62000,50 +62700,50 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A33,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MAGMA_USDT_PERP</t>
+          <t>CRV_USDT_PERP</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -62051,50 +62751,50 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A34,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TRUMP_USDT_PERP</t>
+          <t>MAGMA_USDT_PERP</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -62102,50 +62802,50 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A35,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CHIP_USDT_PERP</t>
+          <t>TRUMP_USDT_PERP</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -62153,50 +62853,50 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A36,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PENGU_USDT_PERP</t>
+          <t>CHIP_USDT_PERP</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -62204,50 +62904,50 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A37,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FARTCOIN_USDT_PERP</t>
+          <t>PENGU_USDT_PERP</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -62255,50 +62955,50 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A38,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TRIA_USDT_PERP</t>
+          <t>FARTCOIN_USDT_PERP</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -62306,50 +63006,50 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A39,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ZEN_USDT_PERP</t>
+          <t>TRIA_USDT_PERP</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -62357,50 +63057,50 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A40,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TAO_USDT_PERP</t>
+          <t>ZEN_USDT_PERP</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -62408,50 +63108,50 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A41,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>KAS_USDT_PERP</t>
+          <t>TAO_USDT_PERP</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -62459,50 +63159,50 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A42,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>CASHCAT_USDT_PERP</t>
+          <t>KAS_USDT_PERP</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -62510,50 +63210,50 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A43,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>INJ_USDT_PERP</t>
+          <t>CASHCAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -62561,50 +63261,50 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A44,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ICP_USDT_PERP</t>
+          <t>INJ_USDT_PERP</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -62612,50 +63312,50 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A45,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FF_USDT_PERP</t>
+          <t>ICP_USDT_PERP</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -62663,50 +63363,50 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A46,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>KAT_USDT_PERP</t>
+          <t>FF_USDT_PERP</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -62714,50 +63414,50 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A47,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MET_USDT_PERP</t>
+          <t>KAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -62765,50 +63465,50 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A48,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LAB_USDT_PERP</t>
+          <t>MET_USDT_PERP</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$C$2:$C$203,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$C$2:$C$206,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$C$2:$C$203,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$C$2:$C$206,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -62816,19 +63516,19 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$203,交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$203,交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$203,$A49,交易明細!$J$2:$J$203,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66662,7 +67362,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr"/>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="17" t="n"/>
       <c r="F210" s="17" t="n"/>
@@ -68664,11 +69368,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C321" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C321" s="2" t="inlineStr"/>
       <c r="D321" s="2" t="n"/>
       <c r="E321" s="17" t="n"/>
       <c r="F321" s="17" t="n"/>
@@ -70148,7 +70848,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C403" s="2" t="inlineStr"/>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D403" s="2" t="n"/>
       <c r="E403" s="17" t="n"/>
       <c r="F403" s="17" t="n"/>
@@ -70868,7 +71572,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr"/>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="17" t="n"/>
       <c r="F443" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,7 +17,7 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$405</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$408</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$405</f>
+              <f>'資金明細'!$R$2:$R$408</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 17:04（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 20:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,42 +1085,42 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -1131,47 +1131,70 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1237,7 +1260,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R405</f>
+        <f>資金明細!R408</f>
         <v/>
       </c>
     </row>
@@ -1275,7 +1298,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$405)</f>
+        <f>MAX(資金明細!$R$2:$R$408)</f>
         <v/>
       </c>
     </row>
@@ -1294,7 +1317,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$405)</f>
+        <f>MIN(資金明細!$R$2:$R$408)</f>
         <v/>
       </c>
     </row>
@@ -1314,7 +1337,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$405)</f>
+        <f>MIN(資金明細!$X$2:$X$408)</f>
         <v/>
       </c>
     </row>
@@ -1333,7 +1356,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$405,"進場",資金明細!$N$2:$N$405,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$408,"進場",資金明細!$N$2:$N$408,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1352,7 +1375,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$405,"進場",資金明細!$N$2:$N$405,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$408,"進場",資金明細!$N$2:$N$408,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1363,7 +1386,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$405,"出場",資金明細!$N$2:$N$405,"已下單",資金明細!$K$2:$K$405,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$408,"出場",資金明細!$N$2:$N$408,"已下單",資金明細!$K$2:$K$408,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1383,7 +1406,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$405,"出場",資金明細!$N$2:$N$405,"已下單",資金明細!$K$2:$K$405,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$408,"出場",資金明細!$N$2:$N$408,"已下單",資金明細!$K$2:$K$408,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1399,7 +1422,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$405,"出場",資金明細!$N$2:$N$405,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$408,"出場",資金明細!$N$2:$N$408,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1438,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$405)</f>
+        <f>MAX(資金明細!$U$2:$U$408)</f>
         <v/>
       </c>
     </row>
@@ -1431,7 +1454,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$405)</f>
+        <f>MAX(資金明細!$S$2:$S$408)</f>
         <v/>
       </c>
     </row>
@@ -1442,7 +1465,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V405</f>
+        <f>B5*資金明細!V408</f>
         <v/>
       </c>
     </row>
@@ -1453,7 +1476,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N355="已下單",資金明細!O355*交易明細!L179,0)+IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N400="已下單",資金明細!O400*交易明細!L202,0)+IF(資金明細!N401="已下單",資金明細!O401*交易明細!L203,0)+IF(資金明細!N403="已下單",資金明細!O403*交易明細!L204,0)+IF(資金明細!N404="已下單",資金明細!O404*交易明細!L205,0)+IF(資金明細!N405="已下單",資金明細!O405*交易明細!L206,0)</f>
+        <f>IF(資金明細!N355="已下單",資金明細!O355*交易明細!L179,0)+IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N403="已下單",資金明細!O403*交易明細!L204,0)+IF(資金明細!N404="已下單",資金明細!O404*交易明細!L205,0)</f>
         <v/>
       </c>
     </row>
@@ -1464,7 +1487,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$405)</f>
+        <f>MAX(資金明細!$Y$2:$Y$408)</f>
         <v/>
       </c>
     </row>
@@ -1486,7 +1509,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$405,MATCH(1,資金明細!$Z$2:$Z$405,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$408,MATCH(1,資金明細!$Z$2:$Z$408,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1497,7 +1520,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$405,"進場",資金明細!$N$2:$N$405,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$408,"進場",資金明細!$N$2:$N$408,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1562,7 +1585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z405"/>
+  <dimension ref="A1:Z408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -40117,11 +40140,7 @@
         <v>0.00393435</v>
       </c>
       <c r="J400" s="17" t="n"/>
-      <c r="K400" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K400" s="2" t="n"/>
       <c r="L400" s="5" t="n"/>
       <c r="M400" s="16">
         <f>資金模擬!$B$5*V399</f>
@@ -40211,11 +40230,7 @@
         <v>0.235662</v>
       </c>
       <c r="J401" s="17" t="n"/>
-      <c r="K401" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K401" s="2" t="n"/>
       <c r="L401" s="5" t="n"/>
       <c r="M401" s="16">
         <f>資金模擬!$B$5*V400</f>
@@ -40596,11 +40611,7 @@
         <v>0.1417185</v>
       </c>
       <c r="J405" s="17" t="n"/>
-      <c r="K405" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K405" s="2" t="n"/>
       <c r="L405" s="5" t="n"/>
       <c r="M405" s="16">
         <f>資金模擬!$B$5*V404</f>
@@ -40655,9 +40666,318 @@
         <v/>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="B406" s="7" t="n">
+        <v>46278.75</v>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>PUMP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G406" s="17" t="n">
+        <v>0.003747</v>
+      </c>
+      <c r="H406" s="17" t="n">
+        <v>0.00363459</v>
+      </c>
+      <c r="I406" s="17" t="n">
+        <v>0.00393435</v>
+      </c>
+      <c r="J406" s="17" t="n">
+        <v>0.00363459</v>
+      </c>
+      <c r="K406" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L406" s="5">
+        <f>交易明細!K202</f>
+        <v/>
+      </c>
+      <c r="M406" s="16">
+        <f>M400</f>
+        <v/>
+      </c>
+      <c r="N406" s="2">
+        <f>N400</f>
+        <v/>
+      </c>
+      <c r="O406" s="16">
+        <f>O400</f>
+        <v/>
+      </c>
+      <c r="P406" s="4">
+        <f>交易明細!L202</f>
+        <v/>
+      </c>
+      <c r="Q406" s="10">
+        <f>IF(N406="已下單",O406*P406,0)</f>
+        <v/>
+      </c>
+      <c r="R406" s="10">
+        <f>R405+Q406</f>
+        <v/>
+      </c>
+      <c r="S406" s="16">
+        <f>S405-IF(N406="已下單",M406,0)</f>
+        <v/>
+      </c>
+      <c r="T406" s="16">
+        <f>R406-S406</f>
+        <v/>
+      </c>
+      <c r="U406" s="2">
+        <f>U405-IF(N406="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V406" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R406,0),MAX(V405,FLOOR(MAX(R406,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W406" s="10">
+        <f>MAX(W405,R406)</f>
+        <v/>
+      </c>
+      <c r="X406" s="4">
+        <f>IF(W406&gt;0,R406/W406-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y406" s="16">
+        <f>IF(R406&gt;0,S406*資金模擬!$B$7/R406,0)</f>
+        <v/>
+      </c>
+      <c r="Z406" s="2">
+        <f>IF(OR(Z405=1,R406&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="B407" s="7" t="n">
+        <v>46278.75</v>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G407" s="17" t="n">
+        <v>0.13497</v>
+      </c>
+      <c r="H407" s="17" t="n">
+        <v>0.1309209</v>
+      </c>
+      <c r="I407" s="17" t="n">
+        <v>0.1417185</v>
+      </c>
+      <c r="J407" s="17" t="n">
+        <v>0.1309209</v>
+      </c>
+      <c r="K407" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L407" s="5">
+        <f>交易明細!K206</f>
+        <v/>
+      </c>
+      <c r="M407" s="16">
+        <f>M405</f>
+        <v/>
+      </c>
+      <c r="N407" s="2">
+        <f>N405</f>
+        <v/>
+      </c>
+      <c r="O407" s="16">
+        <f>O405</f>
+        <v/>
+      </c>
+      <c r="P407" s="4">
+        <f>交易明細!L206</f>
+        <v/>
+      </c>
+      <c r="Q407" s="10">
+        <f>IF(N407="已下單",O407*P407,0)</f>
+        <v/>
+      </c>
+      <c r="R407" s="10">
+        <f>R406+Q407</f>
+        <v/>
+      </c>
+      <c r="S407" s="16">
+        <f>S406-IF(N407="已下單",M407,0)</f>
+        <v/>
+      </c>
+      <c r="T407" s="16">
+        <f>R407-S407</f>
+        <v/>
+      </c>
+      <c r="U407" s="2">
+        <f>U406-IF(N407="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V407" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R407,0),MAX(V406,FLOOR(MAX(R407,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W407" s="10">
+        <f>MAX(W406,R407)</f>
+        <v/>
+      </c>
+      <c r="X407" s="4">
+        <f>IF(W407&gt;0,R407/W407-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y407" s="16">
+        <f>IF(R407&gt;0,S407*資金模擬!$B$7/R407,0)</f>
+        <v/>
+      </c>
+      <c r="Z407" s="2">
+        <f>IF(OR(Z406=1,R407&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n">
+        <v>406</v>
+      </c>
+      <c r="B408" s="7" t="n">
+        <v>46278.83333333334</v>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G408" s="17" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="H408" s="17" t="n">
+        <v>0.2177068</v>
+      </c>
+      <c r="I408" s="17" t="n">
+        <v>0.235662</v>
+      </c>
+      <c r="J408" s="17" t="n">
+        <v>0.2177068</v>
+      </c>
+      <c r="K408" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L408" s="5">
+        <f>交易明細!K203</f>
+        <v/>
+      </c>
+      <c r="M408" s="16">
+        <f>M401</f>
+        <v/>
+      </c>
+      <c r="N408" s="2">
+        <f>N401</f>
+        <v/>
+      </c>
+      <c r="O408" s="16">
+        <f>O401</f>
+        <v/>
+      </c>
+      <c r="P408" s="4">
+        <f>交易明細!L203</f>
+        <v/>
+      </c>
+      <c r="Q408" s="10">
+        <f>IF(N408="已下單",O408*P408,0)</f>
+        <v/>
+      </c>
+      <c r="R408" s="10">
+        <f>R407+Q408</f>
+        <v/>
+      </c>
+      <c r="S408" s="16">
+        <f>S407-IF(N408="已下單",M408,0)</f>
+        <v/>
+      </c>
+      <c r="T408" s="16">
+        <f>R408-S408</f>
+        <v/>
+      </c>
+      <c r="U408" s="2">
+        <f>U407-IF(N408="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V408" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R408,0),MAX(V407,FLOOR(MAX(R408,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W408" s="10">
+        <f>MAX(W407,R408)</f>
+        <v/>
+      </c>
+      <c r="X408" s="4">
+        <f>IF(W408&gt;0,R408/W408-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y408" s="16">
+        <f>IF(R408&gt;0,S408*資金模擬!$B$7/R408,0)</f>
+        <v/>
+      </c>
+      <c r="Z408" s="2">
+        <f>IF(OR(Z407=1,R408&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z405"/>
-  <conditionalFormatting sqref="K2:K405">
+  <autoFilter ref="A1:Z408"/>
+  <conditionalFormatting sqref="K2:K408">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -40665,7 +40985,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N405">
+  <conditionalFormatting sqref="N2:N408">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -40673,7 +40993,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q405">
+  <conditionalFormatting sqref="Q2:Q408">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -40738,7 +41058,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-13 17:04（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-13 20:05（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -58293,10 +58613,10 @@
         <v>0.14889</v>
       </c>
       <c r="H179" s="7" t="n">
-        <v>46278.70833333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="I179" s="17" t="n">
-        <v>0.1385</v>
+        <v>0.1399</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
@@ -58777,10 +59097,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46278.70833333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5607</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -58816,7 +59136,7 @@
         <v>1281726.24259</v>
       </c>
       <c r="S184" s="4" t="n">
-        <v>0.01949420442571126</v>
+        <v>0.0277485072005621</v>
       </c>
       <c r="T184" s="4" t="n">
         <v>0.02388479100807861</v>
@@ -60509,14 +60829,14 @@
         <v>0.00393435</v>
       </c>
       <c r="H202" s="7" t="n">
-        <v>46278.70833333334</v>
+        <v>46278.75</v>
       </c>
       <c r="I202" s="17" t="n">
-        <v>0.003676</v>
+        <v>0.00363459</v>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K202" s="5">
@@ -60527,11 +60847,7 @@
         <f>IF(C202="做多",I202/E202-1,1-I202/E202)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M202" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M202" s="2" t="inlineStr"/>
       <c r="N202" s="4" t="n">
         <v>-0.02371026576341839</v>
       </c>
@@ -60548,7 +60864,7 @@
         <v>2666544.507709</v>
       </c>
       <c r="S202" s="4" t="n">
-        <v>0.02348545503069122</v>
+        <v>0.03</v>
       </c>
       <c r="T202" s="4" t="n">
         <v>0.004536962903656239</v>
@@ -60609,14 +60925,14 @@
         <v>0.235662</v>
       </c>
       <c r="H203" s="7" t="n">
-        <v>46278.70833333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="I203" s="17" t="n">
-        <v>0.22485</v>
+        <v>0.2177068</v>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K203" s="5">
@@ -60627,11 +60943,7 @@
         <f>IF(C203="做多",I203/E203-1,1-I203/E203)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M203" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M203" s="2" t="inlineStr"/>
       <c r="N203" s="4" t="n">
         <v>-0.02383437717466952</v>
       </c>
@@ -60648,10 +60960,10 @@
         <v>1943593.26169</v>
       </c>
       <c r="S203" s="4" t="n">
-        <v>0.01327749064337913</v>
+        <v>0.03</v>
       </c>
       <c r="T203" s="4" t="n">
-        <v>0.01920335056139733</v>
+        <v>0.03199073248975215</v>
       </c>
       <c r="U203" s="16" t="n">
         <v>1.125300022122543</v>
@@ -60709,10 +61021,10 @@
         <v>0.070287</v>
       </c>
       <c r="H204" s="7" t="n">
-        <v>46278.70833333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="I204" s="17" t="n">
-        <v>0.06694</v>
+        <v>0.06607</v>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
@@ -60748,10 +61060,10 @@
         <v>3660542.31503</v>
       </c>
       <c r="S204" s="4" t="n">
-        <v>0</v>
+        <v>0.02166118912458903</v>
       </c>
       <c r="T204" s="4" t="n">
-        <v>0</v>
+        <v>0.01210038840752925</v>
       </c>
       <c r="U204" s="16" t="n">
         <v>0.6170410304977394</v>
@@ -60809,10 +61121,10 @@
         <v>23.80665</v>
       </c>
       <c r="H205" s="7" t="n">
-        <v>46278.70833333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="I205" s="17" t="n">
-        <v>22.673</v>
+        <v>22.617</v>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
@@ -60848,10 +61160,10 @@
         <v>1862546.13313</v>
       </c>
       <c r="S205" s="4" t="n">
-        <v>0</v>
+        <v>0.009085696643584829</v>
       </c>
       <c r="T205" s="4" t="n">
-        <v>0</v>
+        <v>0.0170246548758437</v>
       </c>
       <c r="U205" s="16" t="n">
         <v>1.542546484066931</v>
@@ -60909,14 +61221,14 @@
         <v>0.1417185</v>
       </c>
       <c r="H206" s="7" t="n">
-        <v>46278.70833333334</v>
+        <v>46278.75</v>
       </c>
       <c r="I206" s="17" t="n">
-        <v>0.13497</v>
+        <v>0.1309209</v>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K206" s="5">
@@ -60927,11 +61239,7 @@
         <f>IF(C206="做多",I206/E206-1,1-I206/E206)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M206" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M206" s="2" t="inlineStr"/>
       <c r="N206" s="4" t="n">
         <v>-0.0527091521617068</v>
       </c>
@@ -60948,7 +61256,7 @@
         <v>2751747.85932</v>
       </c>
       <c r="S206" s="4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T206" s="4" t="n">
         <v>0</v>
@@ -69094,11 +69402,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C306" s="2" t="inlineStr"/>
       <c r="D306" s="2" t="n"/>
       <c r="E306" s="17" t="n"/>
       <c r="F306" s="17" t="n"/>
@@ -70718,11 +71022,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C396" s="2" t="inlineStr"/>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="17" t="n"/>
       <c r="F396" s="17" t="n"/>
@@ -71572,11 +71872,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C443" s="2" t="inlineStr"/>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="17" t="n"/>
       <c r="F443" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$408</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$414</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$208</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$408</f>
+              <f>'資金明細'!$R$2:$R$414</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 20:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 00:24（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$206,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$208,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$J$2:$J$206,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$J$2:$J$208,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$J$2:$J$206,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$J$2:$J$208,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$J$2:$J$206,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$J$2:$J$208,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$206,"&lt;&gt;未平倉",交易明細!$L$2:$L$206,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$208,"&lt;&gt;未平倉",交易明細!$L$2:$L$208,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$B$2:$B$206,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$B$2:$B$208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$206,"做多",交易明細!$J$2:$J$206,"&lt;&gt;未平倉",交易明細!$L$2:$L$206,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉",交易明細!$L$2:$L$208,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$B$2:$B$206,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$B$2:$B$208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$206,"做空",交易明細!$J$2:$J$206,"&lt;&gt;未平倉",交易明細!$L$2:$L$206,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉",交易明細!$L$2:$L$208,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,65 +1085,65 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -1154,47 +1154,70 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1260,7 +1283,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R408</f>
+        <f>資金明細!R414</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1321,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$408)</f>
+        <f>MAX(資金明細!$R$2:$R$414)</f>
         <v/>
       </c>
     </row>
@@ -1317,7 +1340,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$408)</f>
+        <f>MIN(資金明細!$R$2:$R$414)</f>
         <v/>
       </c>
     </row>
@@ -1337,7 +1360,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$408)</f>
+        <f>MIN(資金明細!$X$2:$X$414)</f>
         <v/>
       </c>
     </row>
@@ -1356,7 +1379,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$408,"進場",資金明細!$N$2:$N$408,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$414,"進場",資金明細!$N$2:$N$414,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1398,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$408,"進場",資金明細!$N$2:$N$408,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$414,"進場",資金明細!$N$2:$N$414,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1386,7 +1409,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$408,"出場",資金明細!$N$2:$N$408,"已下單",資金明細!$K$2:$K$408,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$414,"出場",資金明細!$N$2:$N$414,"已下單",資金明細!$K$2:$K$414,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1397,7 +1420,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$206),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$208),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1406,7 +1429,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$408,"出場",資金明細!$N$2:$N$408,"已下單",資金明細!$K$2:$K$408,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$414,"出場",資金明細!$N$2:$N$414,"已下單",資金明細!$K$2:$K$414,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1422,7 +1445,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$408,"出場",資金明細!$N$2:$N$408,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$414,"出場",資金明細!$N$2:$N$414,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1438,7 +1461,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$408)</f>
+        <f>MAX(資金明細!$U$2:$U$414)</f>
         <v/>
       </c>
     </row>
@@ -1454,7 +1477,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$408)</f>
+        <f>MAX(資金明細!$S$2:$S$414)</f>
         <v/>
       </c>
     </row>
@@ -1465,7 +1488,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V408</f>
+        <f>B5*資金明細!V414</f>
         <v/>
       </c>
     </row>
@@ -1476,7 +1499,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N355="已下單",資金明細!O355*交易明細!L179,0)+IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N403="已下單",資金明細!O403*交易明細!L204,0)+IF(資金明細!N404="已下單",資金明細!O404*交易明細!L205,0)</f>
+        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N414="已下單",資金明細!O414*交易明細!L208,0)</f>
         <v/>
       </c>
     </row>
@@ -1487,7 +1510,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$408)</f>
+        <f>MAX(資金明細!$Y$2:$Y$414)</f>
         <v/>
       </c>
     </row>
@@ -1509,7 +1532,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$408,MATCH(1,資金明細!$Z$2:$Z$408,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$414,MATCH(1,資金明細!$Z$2:$Z$414,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1520,7 +1543,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$408,"進場",資金明細!$N$2:$N$408,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$414,"進場",資金明細!$N$2:$N$414,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1585,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z408"/>
+  <dimension ref="A1:Z414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -35796,11 +35819,7 @@
         <v>0.14889</v>
       </c>
       <c r="J355" s="17" t="n"/>
-      <c r="K355" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K355" s="2" t="n"/>
       <c r="L355" s="5" t="n"/>
       <c r="M355" s="16">
         <f>資金模擬!$B$5*V354</f>
@@ -40423,11 +40442,7 @@
         <v>0.070287</v>
       </c>
       <c r="J403" s="17" t="n"/>
-      <c r="K403" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K403" s="2" t="n"/>
       <c r="L403" s="5" t="n"/>
       <c r="M403" s="16">
         <f>資金模擬!$B$5*V402</f>
@@ -40517,11 +40532,7 @@
         <v>23.80665</v>
       </c>
       <c r="J404" s="17" t="n"/>
-      <c r="K404" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K404" s="2" t="n"/>
       <c r="L404" s="5" t="n"/>
       <c r="M404" s="16">
         <f>資金模擬!$B$5*V403</f>
@@ -40975,9 +40986,605 @@
         <v/>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="B409" s="7" t="n">
+        <v>46278.875</v>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G409" s="17" t="n">
+        <v>0.06694</v>
+      </c>
+      <c r="H409" s="17" t="n">
+        <v>0.0649318</v>
+      </c>
+      <c r="I409" s="17" t="n">
+        <v>0.070287</v>
+      </c>
+      <c r="J409" s="17" t="n">
+        <v>0.0649318</v>
+      </c>
+      <c r="K409" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L409" s="5">
+        <f>交易明細!K204</f>
+        <v/>
+      </c>
+      <c r="M409" s="16">
+        <f>M403</f>
+        <v/>
+      </c>
+      <c r="N409" s="2">
+        <f>N403</f>
+        <v/>
+      </c>
+      <c r="O409" s="16">
+        <f>O403</f>
+        <v/>
+      </c>
+      <c r="P409" s="4">
+        <f>交易明細!L204</f>
+        <v/>
+      </c>
+      <c r="Q409" s="10">
+        <f>IF(N409="已下單",O409*P409,0)</f>
+        <v/>
+      </c>
+      <c r="R409" s="10">
+        <f>R408+Q409</f>
+        <v/>
+      </c>
+      <c r="S409" s="16">
+        <f>S408-IF(N409="已下單",M409,0)</f>
+        <v/>
+      </c>
+      <c r="T409" s="16">
+        <f>R409-S409</f>
+        <v/>
+      </c>
+      <c r="U409" s="2">
+        <f>U408-IF(N409="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V409" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R409,0),MAX(V408,FLOOR(MAX(R409,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W409" s="10">
+        <f>MAX(W408,R409)</f>
+        <v/>
+      </c>
+      <c r="X409" s="4">
+        <f>IF(W409&gt;0,R409/W409-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y409" s="16">
+        <f>IF(R409&gt;0,S409*資金模擬!$B$7/R409,0)</f>
+        <v/>
+      </c>
+      <c r="Z409" s="2">
+        <f>IF(OR(Z408=1,R409&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="B410" s="7" t="n">
+        <v>46278.91666666666</v>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>ENA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G410" s="17" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="H410" s="17" t="n">
+        <v>0.137546</v>
+      </c>
+      <c r="I410" s="17" t="n">
+        <v>0.14889</v>
+      </c>
+      <c r="J410" s="17" t="n">
+        <v>0.137546</v>
+      </c>
+      <c r="K410" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L410" s="5">
+        <f>交易明細!K179</f>
+        <v/>
+      </c>
+      <c r="M410" s="16">
+        <f>M355</f>
+        <v/>
+      </c>
+      <c r="N410" s="2">
+        <f>N355</f>
+        <v/>
+      </c>
+      <c r="O410" s="16">
+        <f>O355</f>
+        <v/>
+      </c>
+      <c r="P410" s="4">
+        <f>交易明細!L179</f>
+        <v/>
+      </c>
+      <c r="Q410" s="10">
+        <f>IF(N410="已下單",O410*P410,0)</f>
+        <v/>
+      </c>
+      <c r="R410" s="10">
+        <f>R409+Q410</f>
+        <v/>
+      </c>
+      <c r="S410" s="16">
+        <f>S409-IF(N410="已下單",M410,0)</f>
+        <v/>
+      </c>
+      <c r="T410" s="16">
+        <f>R410-S410</f>
+        <v/>
+      </c>
+      <c r="U410" s="2">
+        <f>U409-IF(N410="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V410" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R410,0),MAX(V409,FLOOR(MAX(R410,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W410" s="10">
+        <f>MAX(W409,R410)</f>
+        <v/>
+      </c>
+      <c r="X410" s="4">
+        <f>IF(W410&gt;0,R410/W410-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y410" s="16">
+        <f>IF(R410&gt;0,S410*資金模擬!$B$7/R410,0)</f>
+        <v/>
+      </c>
+      <c r="Z410" s="2">
+        <f>IF(OR(Z409=1,R410&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="B411" s="7" t="n">
+        <v>46278.91666666666</v>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>VVV_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G411" s="17" t="n">
+        <v>22.673</v>
+      </c>
+      <c r="H411" s="17" t="n">
+        <v>21.99281</v>
+      </c>
+      <c r="I411" s="17" t="n">
+        <v>23.80665</v>
+      </c>
+      <c r="J411" s="17" t="n">
+        <v>21.99281</v>
+      </c>
+      <c r="K411" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L411" s="5">
+        <f>交易明細!K205</f>
+        <v/>
+      </c>
+      <c r="M411" s="16">
+        <f>M404</f>
+        <v/>
+      </c>
+      <c r="N411" s="2">
+        <f>N404</f>
+        <v/>
+      </c>
+      <c r="O411" s="16">
+        <f>O404</f>
+        <v/>
+      </c>
+      <c r="P411" s="4">
+        <f>交易明細!L205</f>
+        <v/>
+      </c>
+      <c r="Q411" s="10">
+        <f>IF(N411="已下單",O411*P411,0)</f>
+        <v/>
+      </c>
+      <c r="R411" s="10">
+        <f>R410+Q411</f>
+        <v/>
+      </c>
+      <c r="S411" s="16">
+        <f>S410-IF(N411="已下單",M411,0)</f>
+        <v/>
+      </c>
+      <c r="T411" s="16">
+        <f>R411-S411</f>
+        <v/>
+      </c>
+      <c r="U411" s="2">
+        <f>U410-IF(N411="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V411" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R411,0),MAX(V410,FLOOR(MAX(R411,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W411" s="10">
+        <f>MAX(W410,R411)</f>
+        <v/>
+      </c>
+      <c r="X411" s="4">
+        <f>IF(W411&gt;0,R411/W411-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y411" s="16">
+        <f>IF(R411&gt;0,S411*資金模擬!$B$7/R411,0)</f>
+        <v/>
+      </c>
+      <c r="Z411" s="2">
+        <f>IF(OR(Z410=1,R411&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="B412" s="7" t="n">
+        <v>46278.91666666666</v>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G412" s="17" t="n">
+        <v>0.06630999999999999</v>
+      </c>
+      <c r="H412" s="17" t="n">
+        <v>0.06432069999999999</v>
+      </c>
+      <c r="I412" s="17" t="n">
+        <v>0.06962549999999999</v>
+      </c>
+      <c r="J412" s="17" t="n"/>
+      <c r="K412" s="2" t="n"/>
+      <c r="L412" s="5" t="n"/>
+      <c r="M412" s="16">
+        <f>資金模擬!$B$5*V411</f>
+        <v/>
+      </c>
+      <c r="N412" s="2">
+        <f>IF(Z411=1,"已停止",IF(T411&gt;=M412,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O412" s="16">
+        <f>IF(N412="已下單",M412*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P412" s="4" t="n"/>
+      <c r="Q412" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R412" s="10">
+        <f>R411+Q412</f>
+        <v/>
+      </c>
+      <c r="S412" s="16">
+        <f>S411+IF(N412="已下單",M412,0)</f>
+        <v/>
+      </c>
+      <c r="T412" s="16">
+        <f>R412-S412</f>
+        <v/>
+      </c>
+      <c r="U412" s="2">
+        <f>U411+IF(N412="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V412" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R412,0),MAX(V411,FLOOR(MAX(R412,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W412" s="10">
+        <f>MAX(W411,R412)</f>
+        <v/>
+      </c>
+      <c r="X412" s="4">
+        <f>IF(W412&gt;0,R412/W412-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y412" s="16">
+        <f>IF(R412&gt;0,S412*資金模擬!$B$7/R412,0)</f>
+        <v/>
+      </c>
+      <c r="Z412" s="2">
+        <f>IF(OR(Z411=1,R412&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>411</v>
+      </c>
+      <c r="B413" s="7" t="n">
+        <v>46278.95833333334</v>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G413" s="17" t="n">
+        <v>0.06630999999999999</v>
+      </c>
+      <c r="H413" s="17" t="n">
+        <v>0.06432069999999999</v>
+      </c>
+      <c r="I413" s="17" t="n">
+        <v>0.06962549999999999</v>
+      </c>
+      <c r="J413" s="17" t="n">
+        <v>0.06962549999999999</v>
+      </c>
+      <c r="K413" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L413" s="5">
+        <f>交易明細!K207</f>
+        <v/>
+      </c>
+      <c r="M413" s="16">
+        <f>M412</f>
+        <v/>
+      </c>
+      <c r="N413" s="2">
+        <f>N412</f>
+        <v/>
+      </c>
+      <c r="O413" s="16">
+        <f>O412</f>
+        <v/>
+      </c>
+      <c r="P413" s="4">
+        <f>交易明細!L207</f>
+        <v/>
+      </c>
+      <c r="Q413" s="10">
+        <f>IF(N413="已下單",O413*P413,0)</f>
+        <v/>
+      </c>
+      <c r="R413" s="10">
+        <f>R412+Q413</f>
+        <v/>
+      </c>
+      <c r="S413" s="16">
+        <f>S412-IF(N413="已下單",M413,0)</f>
+        <v/>
+      </c>
+      <c r="T413" s="16">
+        <f>R413-S413</f>
+        <v/>
+      </c>
+      <c r="U413" s="2">
+        <f>U412-IF(N413="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V413" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R413,0),MAX(V412,FLOOR(MAX(R413,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W413" s="10">
+        <f>MAX(W412,R413)</f>
+        <v/>
+      </c>
+      <c r="X413" s="4">
+        <f>IF(W413&gt;0,R413/W413-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y413" s="16">
+        <f>IF(R413&gt;0,S413*資金模擬!$B$7/R413,0)</f>
+        <v/>
+      </c>
+      <c r="Z413" s="2">
+        <f>IF(OR(Z412=1,R413&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n">
+        <v>412</v>
+      </c>
+      <c r="B414" s="7" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>PUMP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G414" s="17" t="n">
+        <v>0.003569</v>
+      </c>
+      <c r="H414" s="17" t="n">
+        <v>0.00346193</v>
+      </c>
+      <c r="I414" s="17" t="n">
+        <v>0.00374745</v>
+      </c>
+      <c r="J414" s="17" t="n"/>
+      <c r="K414" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L414" s="5" t="n"/>
+      <c r="M414" s="16">
+        <f>資金模擬!$B$5*V413</f>
+        <v/>
+      </c>
+      <c r="N414" s="2">
+        <f>IF(Z413=1,"已停止",IF(T413&gt;=M414,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O414" s="16">
+        <f>IF(N414="已下單",M414*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P414" s="4" t="n"/>
+      <c r="Q414" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R414" s="10">
+        <f>R413+Q414</f>
+        <v/>
+      </c>
+      <c r="S414" s="16">
+        <f>S413+IF(N414="已下單",M414,0)</f>
+        <v/>
+      </c>
+      <c r="T414" s="16">
+        <f>R414-S414</f>
+        <v/>
+      </c>
+      <c r="U414" s="2">
+        <f>U413+IF(N414="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V414" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R414,0),MAX(V413,FLOOR(MAX(R414,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W414" s="10">
+        <f>MAX(W413,R414)</f>
+        <v/>
+      </c>
+      <c r="X414" s="4">
+        <f>IF(W414&gt;0,R414/W414-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y414" s="16">
+        <f>IF(R414&gt;0,S414*資金模擬!$B$7/R414,0)</f>
+        <v/>
+      </c>
+      <c r="Z414" s="2">
+        <f>IF(OR(Z413=1,R414&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z408"/>
-  <conditionalFormatting sqref="K2:K408">
+  <autoFilter ref="A1:Z414"/>
+  <conditionalFormatting sqref="K2:K414">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -40985,7 +41592,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N408">
+  <conditionalFormatting sqref="N2:N414">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -40993,7 +41600,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q408">
+  <conditionalFormatting sqref="Q2:Q414">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -41058,7 +41665,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-13 20:05（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 00:24（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -41262,7 +41869,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$206),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$208),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -41427,7 +42034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC206"/>
+  <dimension ref="A1:AC208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -58613,14 +59220,14 @@
         <v>0.14889</v>
       </c>
       <c r="H179" s="7" t="n">
-        <v>46278.83333333334</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="I179" s="17" t="n">
-        <v>0.1399</v>
+        <v>0.137546</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K179" s="5">
@@ -58631,11 +59238,7 @@
         <f>IF(C179="做多",I179/E179-1,1-I179/E179)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M179" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M179" s="2" t="inlineStr"/>
       <c r="N179" s="4" t="n">
         <v>-0.02475928473177436</v>
       </c>
@@ -58652,7 +59255,7 @@
         <v>7836145.6262</v>
       </c>
       <c r="S179" s="4" t="n">
-        <v>0.02679830747531731</v>
+        <v>0.03</v>
       </c>
       <c r="T179" s="4" t="n">
         <v>0.01410437235543016</v>
@@ -59097,10 +59700,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46278.83333333334</v>
+        <v>46279</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5607</v>
+        <v>0.5611</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -61021,14 +61624,14 @@
         <v>0.070287</v>
       </c>
       <c r="H204" s="7" t="n">
-        <v>46278.83333333334</v>
+        <v>46278.875</v>
       </c>
       <c r="I204" s="17" t="n">
-        <v>0.06607</v>
+        <v>0.0649318</v>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K204" s="5">
@@ -61039,11 +61642,7 @@
         <f>IF(C204="做多",I204/E204-1,1-I204/E204)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M204" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M204" s="2" t="inlineStr"/>
       <c r="N204" s="4" t="n">
         <v>-0.02163110201695406</v>
       </c>
@@ -61060,7 +61659,7 @@
         <v>3660542.31503</v>
       </c>
       <c r="S204" s="4" t="n">
-        <v>0.02166118912458903</v>
+        <v>0.03</v>
       </c>
       <c r="T204" s="4" t="n">
         <v>0.01210038840752925</v>
@@ -61121,14 +61720,14 @@
         <v>23.80665</v>
       </c>
       <c r="H205" s="7" t="n">
-        <v>46278.83333333334</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="I205" s="17" t="n">
-        <v>22.617</v>
+        <v>21.99281</v>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K205" s="5">
@@ -61139,11 +61738,7 @@
         <f>IF(C205="做多",I205/E205-1,1-I205/E205)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M205" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M205" s="2" t="inlineStr"/>
       <c r="N205" s="4" t="n">
         <v>-0.02309448920677326</v>
       </c>
@@ -61160,7 +61755,7 @@
         <v>1862546.13313</v>
       </c>
       <c r="S205" s="4" t="n">
-        <v>0.009085696643584829</v>
+        <v>0.03</v>
       </c>
       <c r="T205" s="4" t="n">
         <v>0.0170246548758437</v>
@@ -61290,9 +61885,205 @@
         <v/>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="n">
+        <v>46278.91666666666</v>
+      </c>
+      <c r="E207" s="17" t="n">
+        <v>0.06630999999999999</v>
+      </c>
+      <c r="F207" s="17" t="n">
+        <v>0.06432069999999999</v>
+      </c>
+      <c r="G207" s="17" t="n">
+        <v>0.06962549999999999</v>
+      </c>
+      <c r="H207" s="7" t="n">
+        <v>46278.95833333334</v>
+      </c>
+      <c r="I207" s="17" t="n">
+        <v>0.06962549999999999</v>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="K207" s="5">
+        <f>(H207-D207)*24</f>
+        <v/>
+      </c>
+      <c r="L207" s="4">
+        <f>IF(C207="做多",I207/E207-1,1-I207/E207)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="4" t="n">
+        <v>-0.02154345580640404</v>
+      </c>
+      <c r="O207" s="4" t="n">
+        <v>0.05072047984250207</v>
+      </c>
+      <c r="P207" s="4" t="n">
+        <v>-0.01728750009262481</v>
+      </c>
+      <c r="Q207" s="19" t="n">
+        <v>-3247400</v>
+      </c>
+      <c r="R207" s="19" t="n">
+        <v>2692569.84842</v>
+      </c>
+      <c r="S207" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U207" s="16" t="n">
+        <v>0.3851967586724329</v>
+      </c>
+      <c r="V207" s="16" t="n">
+        <v>0.7575757575757599</v>
+      </c>
+      <c r="W207" s="4" t="n">
+        <v>-0.07609418866944684</v>
+      </c>
+      <c r="X207" s="4" t="n">
+        <v>0.1144497863247864</v>
+      </c>
+      <c r="Y207" s="4" t="n">
+        <v>-0.001146942940892126</v>
+      </c>
+      <c r="Z207" s="4" t="n">
+        <v>0.003088123556609257</v>
+      </c>
+      <c r="AA207" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB207" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC207" s="4">
+        <f>(AB207+2*參數!$B$7)/(AA207+AB207)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>PUMP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E208" s="17" t="n">
+        <v>0.003569</v>
+      </c>
+      <c r="F208" s="17" t="n">
+        <v>0.00346193</v>
+      </c>
+      <c r="G208" s="17" t="n">
+        <v>0.00374745</v>
+      </c>
+      <c r="H208" s="7" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I208" s="17" t="n">
+        <v>0.003569</v>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K208" s="5">
+        <f>(H208-D208)*24</f>
+        <v/>
+      </c>
+      <c r="L208" s="4">
+        <f>IF(C208="做多",I208/E208-1,1-I208/E208)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N208" s="4" t="n">
+        <v>-0.0309530274232962</v>
+      </c>
+      <c r="O208" s="4" t="n">
+        <v>0.02022154281324897</v>
+      </c>
+      <c r="P208" s="4" t="n">
+        <v>-0.04703416418568007</v>
+      </c>
+      <c r="Q208" s="19" t="n">
+        <v>-126643814</v>
+      </c>
+      <c r="R208" s="19" t="n">
+        <v>2834501.678442</v>
+      </c>
+      <c r="S208" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" s="16" t="n">
+        <v>1.170633405432124</v>
+      </c>
+      <c r="V208" s="16" t="n">
+        <v>0.9133858267716523</v>
+      </c>
+      <c r="W208" s="4" t="n">
+        <v>0.06902371394064588</v>
+      </c>
+      <c r="X208" s="4" t="n">
+        <v>0.02459688439464325</v>
+      </c>
+      <c r="Y208" s="4" t="n">
+        <v>0.001000322642925155</v>
+      </c>
+      <c r="Z208" s="4" t="n">
+        <v>-0.0005462274681169443</v>
+      </c>
+      <c r="AA208" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB208" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC208" s="4">
+        <f>(AB208+2*參數!$B$7)/(AA208+AB208)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC206"/>
-  <conditionalFormatting sqref="J2:J206">
+  <autoFilter ref="A1:AC208"/>
+  <conditionalFormatting sqref="J2:J208">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -61399,27 +62190,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -61427,50 +62218,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A2,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>USELESS_USDT_PERP</t>
+          <t>PUMP_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -61478,50 +62269,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A3,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PUMP_USDT_PERP</t>
+          <t>USELESS_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -61529,19 +62320,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A4,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61552,27 +62343,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -61580,19 +62371,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A5,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61603,27 +62394,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -61631,19 +62422,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A6,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61654,27 +62445,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -61682,19 +62473,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A7,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61705,27 +62496,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -61733,19 +62524,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A8,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61756,27 +62547,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -61784,19 +62575,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A9,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61807,27 +62598,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -61835,19 +62626,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A10,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61858,27 +62649,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -61886,19 +62677,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A11,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61909,27 +62700,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -61937,19 +62728,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A12,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -61960,27 +62751,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -61988,19 +62779,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A13,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62011,27 +62802,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -62039,19 +62830,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A14,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62062,27 +62853,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -62090,19 +62881,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A15,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62113,27 +62904,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -62141,19 +62932,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A16,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62164,27 +62955,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -62192,19 +62983,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A17,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62215,27 +63006,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -62243,19 +63034,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A18,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62266,27 +63057,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -62294,19 +63085,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A19,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62317,27 +63108,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -62345,19 +63136,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A20,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62368,27 +63159,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -62396,19 +63187,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A21,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62419,27 +63210,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -62447,50 +63238,50 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A22,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ACE_USDT_PERP</t>
+          <t>LAB_USDT_PERP</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -62498,50 +63289,50 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A23,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EDGE_USDT_PERP</t>
+          <t>ACE_USDT_PERP</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -62549,50 +63340,50 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A24,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>4_USDT_PERP</t>
+          <t>EDGE_USDT_PERP</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -62600,50 +63391,50 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A25,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ZEC_USDT_PERP</t>
+          <t>4_USDT_PERP</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -62651,50 +63442,50 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A26,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>WLD_USDT_PERP</t>
+          <t>ZEC_USDT_PERP</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -62702,50 +63493,50 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A27,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AERO_USDT_PERP</t>
+          <t>WLD_USDT_PERP</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -62753,50 +63544,50 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A28,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DOT_USDT_PERP</t>
+          <t>AERO_USDT_PERP</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -62804,50 +63595,50 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A29,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LAB_USDT_PERP</t>
+          <t>DOT_USDT_PERP</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -62855,19 +63646,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A30,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62878,27 +63669,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -62906,19 +63697,19 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A31,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62929,27 +63720,27 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -62957,19 +63748,19 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A32,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62980,27 +63771,27 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -63008,19 +63799,19 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A33,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63031,27 +63822,27 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -63059,19 +63850,19 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A34,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63082,27 +63873,27 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -63110,19 +63901,19 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A35,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63133,27 +63924,27 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -63161,19 +63952,19 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A36,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63184,27 +63975,27 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -63212,19 +64003,19 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A37,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63235,27 +64026,27 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -63263,19 +64054,19 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A38,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63286,27 +64077,27 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -63314,19 +64105,19 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A39,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63337,27 +64128,27 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -63365,19 +64156,19 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A40,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63388,27 +64179,27 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -63416,19 +64207,19 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A41,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63439,27 +64230,27 @@
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -63467,19 +64258,19 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A42,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63490,27 +64281,27 @@
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -63518,19 +64309,19 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A43,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63541,27 +64332,27 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -63569,19 +64360,19 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A44,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63592,27 +64383,27 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -63620,19 +64411,19 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A45,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63643,27 +64434,27 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -63671,19 +64462,19 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A46,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63694,27 +64485,27 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -63722,19 +64513,19 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A47,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63745,27 +64536,27 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -63773,19 +64564,19 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A48,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63796,27 +64587,27 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$C$2:$C$206,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$C$2:$C$208,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$C$2:$C$206,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$C$2:$C$208,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -63824,19 +64615,19 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$206,交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$206,交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$206,$A49,交易明細!$J$2:$J$206,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66334,11 +67125,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C136" s="2" t="inlineStr"/>
       <c r="D136" s="2" t="n"/>
       <c r="E136" s="17" t="n"/>
       <c r="F136" s="17" t="n"/>
@@ -67670,11 +68457,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C210" s="2" t="inlineStr"/>
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="17" t="n"/>
       <c r="F210" s="17" t="n"/>
@@ -69402,7 +70185,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C306" s="2" t="inlineStr"/>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D306" s="2" t="n"/>
       <c r="E306" s="17" t="n"/>
       <c r="F306" s="17" t="n"/>
@@ -71148,11 +71935,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C403" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C403" s="2" t="inlineStr"/>
       <c r="D403" s="2" t="n"/>
       <c r="E403" s="17" t="n"/>
       <c r="F403" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$414</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$415</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$414</f>
+              <f>'資金明細'!$R$2:$R$415</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 00:24（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 03:31（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$208,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$209,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$J$2:$J$208,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$J$2:$J$209,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$J$2:$J$208,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$J$2:$J$209,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$J$2:$J$208,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$J$2:$J$209,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$208,"&lt;&gt;未平倉",交易明細!$L$2:$L$208,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$209,"&lt;&gt;未平倉",交易明細!$L$2:$L$209,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$B$2:$B$208,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$B$2:$B$209,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$208,"做多",交易明細!$J$2:$J$208,"&lt;&gt;未平倉",交易明細!$L$2:$L$208,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉",交易明細!$L$2:$L$209,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$B$2:$B$208,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$B$2:$B$209,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$208,"做空",交易明細!$J$2:$J$208,"&lt;&gt;未平倉",交易明細!$L$2:$L$208,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉",交易明細!$L$2:$L$209,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,88 +1085,88 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -1177,47 +1177,70 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1283,7 +1306,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R414</f>
+        <f>資金明細!R415</f>
         <v/>
       </c>
     </row>
@@ -1321,7 +1344,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$414)</f>
+        <f>MAX(資金明細!$R$2:$R$415)</f>
         <v/>
       </c>
     </row>
@@ -1340,7 +1363,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$414)</f>
+        <f>MIN(資金明細!$R$2:$R$415)</f>
         <v/>
       </c>
     </row>
@@ -1360,7 +1383,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$414)</f>
+        <f>MIN(資金明細!$X$2:$X$415)</f>
         <v/>
       </c>
     </row>
@@ -1379,7 +1402,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$414,"進場",資金明細!$N$2:$N$414,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$415,"進場",資金明細!$N$2:$N$415,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1398,7 +1421,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$414,"進場",資金明細!$N$2:$N$414,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$415,"進場",資金明細!$N$2:$N$415,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1409,7 +1432,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$414,"出場",資金明細!$N$2:$N$414,"已下單",資金明細!$K$2:$K$414,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$415,"出場",資金明細!$N$2:$N$415,"已下單",資金明細!$K$2:$K$415,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1420,7 +1443,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$208),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$209),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1429,7 +1452,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$414,"出場",資金明細!$N$2:$N$414,"已下單",資金明細!$K$2:$K$414,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$415,"出場",資金明細!$N$2:$N$415,"已下單",資金明細!$K$2:$K$415,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1445,7 +1468,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$414,"出場",資金明細!$N$2:$N$414,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$415,"出場",資金明細!$N$2:$N$415,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1461,7 +1484,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$414)</f>
+        <f>MAX(資金明細!$U$2:$U$415)</f>
         <v/>
       </c>
     </row>
@@ -1477,7 +1500,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$414)</f>
+        <f>MAX(資金明細!$S$2:$S$415)</f>
         <v/>
       </c>
     </row>
@@ -1488,7 +1511,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V414</f>
+        <f>B5*資金明細!V415</f>
         <v/>
       </c>
     </row>
@@ -1499,7 +1522,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N414="已下單",資金明細!O414*交易明細!L208,0)</f>
+        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N414="已下單",資金明細!O414*交易明細!L208,0)+IF(資金明細!N415="已下單",資金明細!O415*交易明細!L209,0)</f>
         <v/>
       </c>
     </row>
@@ -1510,7 +1533,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$414)</f>
+        <f>MAX(資金明細!$Y$2:$Y$415)</f>
         <v/>
       </c>
     </row>
@@ -1532,7 +1555,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$414,MATCH(1,資金明細!$Z$2:$Z$414,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$415,MATCH(1,資金明細!$Z$2:$Z$415,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1543,7 +1566,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$414,"進場",資金明細!$N$2:$N$414,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$415,"進場",資金明細!$N$2:$N$415,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1608,7 +1631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z414"/>
+  <dimension ref="A1:Z415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -41582,9 +41605,103 @@
         <v/>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="B415" s="7" t="n">
+        <v>46279.04166666666</v>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G415" s="17" t="n">
+        <v>0.06729</v>
+      </c>
+      <c r="H415" s="17" t="n">
+        <v>0.0652713</v>
+      </c>
+      <c r="I415" s="17" t="n">
+        <v>0.07065450000000001</v>
+      </c>
+      <c r="J415" s="17" t="n"/>
+      <c r="K415" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L415" s="5" t="n"/>
+      <c r="M415" s="16">
+        <f>資金模擬!$B$5*V414</f>
+        <v/>
+      </c>
+      <c r="N415" s="2">
+        <f>IF(Z414=1,"已停止",IF(T414&gt;=M415,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O415" s="16">
+        <f>IF(N415="已下單",M415*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P415" s="4" t="n"/>
+      <c r="Q415" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R415" s="10">
+        <f>R414+Q415</f>
+        <v/>
+      </c>
+      <c r="S415" s="16">
+        <f>S414+IF(N415="已下單",M415,0)</f>
+        <v/>
+      </c>
+      <c r="T415" s="16">
+        <f>R415-S415</f>
+        <v/>
+      </c>
+      <c r="U415" s="2">
+        <f>U414+IF(N415="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V415" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R415,0),MAX(V414,FLOOR(MAX(R415,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W415" s="10">
+        <f>MAX(W414,R415)</f>
+        <v/>
+      </c>
+      <c r="X415" s="4">
+        <f>IF(W415&gt;0,R415/W415-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y415" s="16">
+        <f>IF(R415&gt;0,S415*資金模擬!$B$7/R415,0)</f>
+        <v/>
+      </c>
+      <c r="Z415" s="2">
+        <f>IF(OR(Z414=1,R415&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z414"/>
-  <conditionalFormatting sqref="K2:K414">
+  <autoFilter ref="A1:Z415"/>
+  <conditionalFormatting sqref="K2:K415">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -41592,7 +41709,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N414">
+  <conditionalFormatting sqref="N2:N415">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -41600,7 +41717,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q414">
+  <conditionalFormatting sqref="Q2:Q415">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -41665,7 +41782,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 00:24（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 03:31（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -41869,7 +41986,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$208),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$209),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -42034,7 +42151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC208"/>
+  <dimension ref="A1:AC209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -59700,10 +59817,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46279</v>
+        <v>46279.125</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5611</v>
+        <v>0.5665</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -62008,10 +62125,10 @@
         <v>0.00374745</v>
       </c>
       <c r="H208" s="7" t="n">
-        <v>46279</v>
+        <v>46279.125</v>
       </c>
       <c r="I208" s="17" t="n">
-        <v>0.003569</v>
+        <v>0.003597</v>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
@@ -62047,10 +62164,10 @@
         <v>2834501.678442</v>
       </c>
       <c r="S208" s="4" t="n">
-        <v>0</v>
+        <v>0.001120762118240415</v>
       </c>
       <c r="T208" s="4" t="n">
-        <v>0</v>
+        <v>0.02577752871952921</v>
       </c>
       <c r="U208" s="16" t="n">
         <v>1.170633405432124</v>
@@ -62081,9 +62198,109 @@
         <v/>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="n">
+        <v>46279.04166666666</v>
+      </c>
+      <c r="E209" s="17" t="n">
+        <v>0.06729</v>
+      </c>
+      <c r="F209" s="17" t="n">
+        <v>0.0652713</v>
+      </c>
+      <c r="G209" s="17" t="n">
+        <v>0.07065450000000001</v>
+      </c>
+      <c r="H209" s="7" t="n">
+        <v>46279.125</v>
+      </c>
+      <c r="I209" s="17" t="n">
+        <v>0.06877999999999999</v>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K209" s="5">
+        <f>(H209-D209)*24</f>
+        <v/>
+      </c>
+      <c r="L209" s="4">
+        <f>IF(C209="做多",I209/E209-1,1-I209/E209)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N209" s="4" t="n">
+        <v>-0.03235547886108714</v>
+      </c>
+      <c r="O209" s="4" t="n">
+        <v>0.05239573335881385</v>
+      </c>
+      <c r="P209" s="4" t="n">
+        <v>-0.006606384941871046</v>
+      </c>
+      <c r="Q209" s="19" t="n">
+        <v>-158654</v>
+      </c>
+      <c r="R209" s="19" t="n">
+        <v>2639902.52603</v>
+      </c>
+      <c r="S209" s="4" t="n">
+        <v>0.01456382820627145</v>
+      </c>
+      <c r="T209" s="4" t="n">
+        <v>0.0306137613315498</v>
+      </c>
+      <c r="U209" s="16" t="n">
+        <v>3.057108558523112</v>
+      </c>
+      <c r="V209" s="16" t="n">
+        <v>0.9469214437367303</v>
+      </c>
+      <c r="W209" s="4" t="n">
+        <v>-0.09114436379910895</v>
+      </c>
+      <c r="X209" s="4" t="n">
+        <v>0.04227156276686594</v>
+      </c>
+      <c r="Y209" s="4" t="n">
+        <v>-0.002005242684949948</v>
+      </c>
+      <c r="Z209" s="4" t="n">
+        <v>-0.002472360720056743</v>
+      </c>
+      <c r="AA209" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB209" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC209" s="4">
+        <f>(AB209+2*參數!$B$7)/(AA209+AB209)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC208"/>
-  <conditionalFormatting sqref="J2:J208">
+  <autoFilter ref="A1:AC209"/>
+  <conditionalFormatting sqref="J2:J209">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -62190,27 +62407,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -62218,19 +62435,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A2,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62241,27 +62458,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -62269,19 +62486,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A3,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62292,27 +62509,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -62320,19 +62537,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A4,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62343,27 +62560,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -62371,19 +62588,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A5,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62394,27 +62611,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -62422,19 +62639,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A6,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62445,27 +62662,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -62473,19 +62690,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A7,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62496,27 +62713,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -62524,19 +62741,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A8,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62547,27 +62764,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -62575,19 +62792,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A9,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62598,27 +62815,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -62626,19 +62843,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A10,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62649,27 +62866,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -62677,19 +62894,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A11,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62700,27 +62917,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -62728,19 +62945,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A12,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62751,27 +62968,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -62779,19 +62996,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A13,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62802,27 +63019,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -62830,19 +63047,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A14,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62853,27 +63070,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -62881,19 +63098,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A15,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62904,27 +63121,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -62932,19 +63149,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A16,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62955,27 +63172,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -62983,19 +63200,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A17,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63006,27 +63223,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -63034,19 +63251,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A18,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63057,27 +63274,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -63085,50 +63302,50 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A19,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BTR_USDT_PERP</t>
+          <t>LAB_USDT_PERP</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -63136,50 +63353,50 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A20,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>XPL_USDT_PERP</t>
+          <t>BTR_USDT_PERP</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -63187,50 +63404,50 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A21,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ENA_USDT_PERP</t>
+          <t>XPL_USDT_PERP</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -63238,50 +63455,50 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A22,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>LAB_USDT_PERP</t>
+          <t>ENA_USDT_PERP</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -63289,19 +63506,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A23,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63312,27 +63529,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -63340,19 +63557,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A24,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63363,27 +63580,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -63391,19 +63608,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A25,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63414,27 +63631,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -63442,19 +63659,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A26,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63465,27 +63682,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -63493,19 +63710,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A27,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63516,27 +63733,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -63544,19 +63761,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A28,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63567,27 +63784,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -63595,19 +63812,19 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A29,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63618,27 +63835,27 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -63646,19 +63863,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A30,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63669,27 +63886,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -63697,19 +63914,19 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A31,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63720,27 +63937,27 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -63748,19 +63965,19 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A32,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63771,27 +63988,27 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -63799,19 +64016,19 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A33,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63822,27 +64039,27 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -63850,19 +64067,19 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A34,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63873,27 +64090,27 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -63901,19 +64118,19 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A35,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63924,27 +64141,27 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -63952,19 +64169,19 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A36,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63975,27 +64192,27 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -64003,19 +64220,19 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A37,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64026,27 +64243,27 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -64054,19 +64271,19 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A38,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64077,27 +64294,27 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -64105,19 +64322,19 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A39,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64128,27 +64345,27 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -64156,19 +64373,19 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A40,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64179,27 +64396,27 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -64207,19 +64424,19 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A41,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64230,27 +64447,27 @@
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -64258,19 +64475,19 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A42,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64281,27 +64498,27 @@
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -64309,19 +64526,19 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A43,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64332,27 +64549,27 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -64360,19 +64577,19 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A44,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64383,27 +64600,27 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -64411,19 +64628,19 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A45,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64434,27 +64651,27 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -64462,19 +64679,19 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A46,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64485,27 +64702,27 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -64513,19 +64730,19 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A47,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64536,27 +64753,27 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -64564,19 +64781,19 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A48,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64587,27 +64804,27 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$C$2:$C$208,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$C$2:$C$209,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$C$2:$C$208,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$C$2:$C$209,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -64615,19 +64832,19 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$208,交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$208,交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$208,$A49,交易明細!$J$2:$J$208,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68457,7 +68674,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr"/>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="17" t="n"/>
       <c r="F210" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 03:31（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 06:27（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,16 +1085,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -1103,93 +1103,93 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -1200,47 +1200,70 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -41782,7 +41805,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 03:31（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 06:27（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -59817,10 +59840,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46279.125</v>
+        <v>46279.25</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5665</v>
+        <v>0.5682</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -62125,10 +62148,10 @@
         <v>0.00374745</v>
       </c>
       <c r="H208" s="7" t="n">
-        <v>46279.125</v>
+        <v>46279.25</v>
       </c>
       <c r="I208" s="17" t="n">
-        <v>0.003597</v>
+        <v>0.003589</v>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
@@ -62164,7 +62187,7 @@
         <v>2834501.678442</v>
       </c>
       <c r="S208" s="4" t="n">
-        <v>0.001120762118240415</v>
+        <v>0.002801905295600982</v>
       </c>
       <c r="T208" s="4" t="n">
         <v>0.02577752871952921</v>
@@ -62225,10 +62248,10 @@
         <v>0.07065450000000001</v>
       </c>
       <c r="H209" s="7" t="n">
-        <v>46279.125</v>
+        <v>46279.25</v>
       </c>
       <c r="I209" s="17" t="n">
-        <v>0.06877999999999999</v>
+        <v>0.06682</v>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$415</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$419</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$211</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$415</f>
+              <f>'資金明細'!$R$2:$R$419</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 06:27（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 09:11（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$209,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$211,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$J$2:$J$209,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$J$2:$J$211,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$J$2:$J$209,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$J$2:$J$211,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$J$2:$J$209,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$J$2:$J$211,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$209,"&lt;&gt;未平倉",交易明細!$L$2:$L$209,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$211,"&lt;&gt;未平倉",交易明細!$L$2:$L$211,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$B$2:$B$209,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$B$2:$B$211,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$209,"做多",交易明細!$J$2:$J$209,"&lt;&gt;未平倉",交易明細!$L$2:$L$209,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉",交易明細!$L$2:$L$211,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$B$2:$B$209,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$B$2:$B$211,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$209,"做空",交易明細!$J$2:$J$209,"&lt;&gt;未平倉",交易明細!$L$2:$L$209,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉",交易明細!$L$2:$L$211,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,39 +1085,39 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -1126,93 +1126,93 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1223,47 +1223,70 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1329,7 +1352,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R415</f>
+        <f>資金明細!R419</f>
         <v/>
       </c>
     </row>
@@ -1367,7 +1390,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$415)</f>
+        <f>MAX(資金明細!$R$2:$R$419)</f>
         <v/>
       </c>
     </row>
@@ -1386,7 +1409,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$415)</f>
+        <f>MIN(資金明細!$R$2:$R$419)</f>
         <v/>
       </c>
     </row>
@@ -1406,7 +1429,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$415)</f>
+        <f>MIN(資金明細!$X$2:$X$419)</f>
         <v/>
       </c>
     </row>
@@ -1425,7 +1448,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$415,"進場",資金明細!$N$2:$N$415,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$419,"進場",資金明細!$N$2:$N$419,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1444,7 +1467,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$415,"進場",資金明細!$N$2:$N$415,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$419,"進場",資金明細!$N$2:$N$419,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +1478,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$415,"出場",資金明細!$N$2:$N$415,"已下單",資金明細!$K$2:$K$415,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$419,"出場",資金明細!$N$2:$N$419,"已下單",資金明細!$K$2:$K$419,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1466,7 +1489,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$209),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$211),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1475,7 +1498,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$415,"出場",資金明細!$N$2:$N$415,"已下單",資金明細!$K$2:$K$415,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$419,"出場",資金明細!$N$2:$N$419,"已下單",資金明細!$K$2:$K$419,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1491,7 +1514,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$415,"出場",資金明細!$N$2:$N$415,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$419,"出場",資金明細!$N$2:$N$419,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1507,7 +1530,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$415)</f>
+        <f>MAX(資金明細!$U$2:$U$419)</f>
         <v/>
       </c>
     </row>
@@ -1523,7 +1546,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$415)</f>
+        <f>MAX(資金明細!$S$2:$S$419)</f>
         <v/>
       </c>
     </row>
@@ -1534,7 +1557,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V415</f>
+        <f>B5*資金明細!V419</f>
         <v/>
       </c>
     </row>
@@ -1545,7 +1568,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N414="已下單",資金明細!O414*交易明細!L208,0)+IF(資金明細!N415="已下單",資金明細!O415*交易明細!L209,0)</f>
+        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N417="已下單",資金明細!O417*交易明細!L210,0)+IF(資金明細!N418="已下單",資金明細!O418*交易明細!L211,0)</f>
         <v/>
       </c>
     </row>
@@ -1556,7 +1579,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$415)</f>
+        <f>MAX(資金明細!$Y$2:$Y$419)</f>
         <v/>
       </c>
     </row>
@@ -1578,7 +1601,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$415,MATCH(1,資金明細!$Z$2:$Z$415,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$419,MATCH(1,資金明細!$Z$2:$Z$419,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1589,7 +1612,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$415,"進場",資金明細!$N$2:$N$415,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$419,"進場",資金明細!$N$2:$N$419,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1654,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z415"/>
+  <dimension ref="A1:Z419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -41569,11 +41592,7 @@
         <v>0.00374745</v>
       </c>
       <c r="J414" s="17" t="n"/>
-      <c r="K414" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K414" s="2" t="n"/>
       <c r="L414" s="5" t="n"/>
       <c r="M414" s="16">
         <f>資金模擬!$B$5*V413</f>
@@ -41663,11 +41682,7 @@
         <v>0.07065450000000001</v>
       </c>
       <c r="J415" s="17" t="n"/>
-      <c r="K415" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K415" s="2" t="n"/>
       <c r="L415" s="5" t="n"/>
       <c r="M415" s="16">
         <f>資金模擬!$B$5*V414</f>
@@ -41722,9 +41737,403 @@
         <v/>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" s="2" t="n">
+        <v>414</v>
+      </c>
+      <c r="B416" s="7" t="n">
+        <v>46279.29166666666</v>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G416" s="17" t="n">
+        <v>0.06729</v>
+      </c>
+      <c r="H416" s="17" t="n">
+        <v>0.0652713</v>
+      </c>
+      <c r="I416" s="17" t="n">
+        <v>0.07065450000000001</v>
+      </c>
+      <c r="J416" s="17" t="n">
+        <v>0.0652713</v>
+      </c>
+      <c r="K416" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L416" s="5">
+        <f>交易明細!K209</f>
+        <v/>
+      </c>
+      <c r="M416" s="16">
+        <f>M415</f>
+        <v/>
+      </c>
+      <c r="N416" s="2">
+        <f>N415</f>
+        <v/>
+      </c>
+      <c r="O416" s="16">
+        <f>O415</f>
+        <v/>
+      </c>
+      <c r="P416" s="4">
+        <f>交易明細!L209</f>
+        <v/>
+      </c>
+      <c r="Q416" s="10">
+        <f>IF(N416="已下單",O416*P416,0)</f>
+        <v/>
+      </c>
+      <c r="R416" s="10">
+        <f>R415+Q416</f>
+        <v/>
+      </c>
+      <c r="S416" s="16">
+        <f>S415-IF(N416="已下單",M416,0)</f>
+        <v/>
+      </c>
+      <c r="T416" s="16">
+        <f>R416-S416</f>
+        <v/>
+      </c>
+      <c r="U416" s="2">
+        <f>U415-IF(N416="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V416" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R416,0),MAX(V415,FLOOR(MAX(R416,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W416" s="10">
+        <f>MAX(W415,R416)</f>
+        <v/>
+      </c>
+      <c r="X416" s="4">
+        <f>IF(W416&gt;0,R416/W416-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y416" s="16">
+        <f>IF(R416&gt;0,S416*資金模擬!$B$7/R416,0)</f>
+        <v/>
+      </c>
+      <c r="Z416" s="2">
+        <f>IF(OR(Z415=1,R416&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="B417" s="7" t="n">
+        <v>46279.29166666666</v>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G417" s="17" t="n">
+        <v>0.21683</v>
+      </c>
+      <c r="H417" s="17" t="n">
+        <v>0.2103251</v>
+      </c>
+      <c r="I417" s="17" t="n">
+        <v>0.2276715</v>
+      </c>
+      <c r="J417" s="17" t="n"/>
+      <c r="K417" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L417" s="5" t="n"/>
+      <c r="M417" s="16">
+        <f>資金模擬!$B$5*V416</f>
+        <v/>
+      </c>
+      <c r="N417" s="2">
+        <f>IF(Z416=1,"已停止",IF(T416&gt;=M417,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O417" s="16">
+        <f>IF(N417="已下單",M417*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P417" s="4" t="n"/>
+      <c r="Q417" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R417" s="10">
+        <f>R416+Q417</f>
+        <v/>
+      </c>
+      <c r="S417" s="16">
+        <f>S416+IF(N417="已下單",M417,0)</f>
+        <v/>
+      </c>
+      <c r="T417" s="16">
+        <f>R417-S417</f>
+        <v/>
+      </c>
+      <c r="U417" s="2">
+        <f>U416+IF(N417="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V417" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R417,0),MAX(V416,FLOOR(MAX(R417,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W417" s="10">
+        <f>MAX(W416,R417)</f>
+        <v/>
+      </c>
+      <c r="X417" s="4">
+        <f>IF(W417&gt;0,R417/W417-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y417" s="16">
+        <f>IF(R417&gt;0,S417*資金模擬!$B$7/R417,0)</f>
+        <v/>
+      </c>
+      <c r="Z417" s="2">
+        <f>IF(OR(Z416=1,R417&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="B418" s="7" t="n">
+        <v>46279.29166666666</v>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>VVV_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G418" s="17" t="n">
+        <v>21.468</v>
+      </c>
+      <c r="H418" s="17" t="n">
+        <v>20.82396</v>
+      </c>
+      <c r="I418" s="17" t="n">
+        <v>22.5414</v>
+      </c>
+      <c r="J418" s="17" t="n"/>
+      <c r="K418" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L418" s="5" t="n"/>
+      <c r="M418" s="16">
+        <f>資金模擬!$B$5*V417</f>
+        <v/>
+      </c>
+      <c r="N418" s="2">
+        <f>IF(Z417=1,"已停止",IF(T417&gt;=M418,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O418" s="16">
+        <f>IF(N418="已下單",M418*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P418" s="4" t="n"/>
+      <c r="Q418" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R418" s="10">
+        <f>R417+Q418</f>
+        <v/>
+      </c>
+      <c r="S418" s="16">
+        <f>S417+IF(N418="已下單",M418,0)</f>
+        <v/>
+      </c>
+      <c r="T418" s="16">
+        <f>R418-S418</f>
+        <v/>
+      </c>
+      <c r="U418" s="2">
+        <f>U417+IF(N418="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V418" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R418,0),MAX(V417,FLOOR(MAX(R418,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W418" s="10">
+        <f>MAX(W417,R418)</f>
+        <v/>
+      </c>
+      <c r="X418" s="4">
+        <f>IF(W418&gt;0,R418/W418-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y418" s="16">
+        <f>IF(R418&gt;0,S418*資金模擬!$B$7/R418,0)</f>
+        <v/>
+      </c>
+      <c r="Z418" s="2">
+        <f>IF(OR(Z417=1,R418&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n">
+        <v>417</v>
+      </c>
+      <c r="B419" s="7" t="n">
+        <v>46279.375</v>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>PUMP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G419" s="17" t="n">
+        <v>0.003569</v>
+      </c>
+      <c r="H419" s="17" t="n">
+        <v>0.00346193</v>
+      </c>
+      <c r="I419" s="17" t="n">
+        <v>0.00374745</v>
+      </c>
+      <c r="J419" s="17" t="n">
+        <v>0.00346193</v>
+      </c>
+      <c r="K419" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L419" s="5">
+        <f>交易明細!K208</f>
+        <v/>
+      </c>
+      <c r="M419" s="16">
+        <f>M414</f>
+        <v/>
+      </c>
+      <c r="N419" s="2">
+        <f>N414</f>
+        <v/>
+      </c>
+      <c r="O419" s="16">
+        <f>O414</f>
+        <v/>
+      </c>
+      <c r="P419" s="4">
+        <f>交易明細!L208</f>
+        <v/>
+      </c>
+      <c r="Q419" s="10">
+        <f>IF(N419="已下單",O419*P419,0)</f>
+        <v/>
+      </c>
+      <c r="R419" s="10">
+        <f>R418+Q419</f>
+        <v/>
+      </c>
+      <c r="S419" s="16">
+        <f>S418-IF(N419="已下單",M419,0)</f>
+        <v/>
+      </c>
+      <c r="T419" s="16">
+        <f>R419-S419</f>
+        <v/>
+      </c>
+      <c r="U419" s="2">
+        <f>U418-IF(N419="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V419" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R419,0),MAX(V418,FLOOR(MAX(R419,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W419" s="10">
+        <f>MAX(W418,R419)</f>
+        <v/>
+      </c>
+      <c r="X419" s="4">
+        <f>IF(W419&gt;0,R419/W419-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y419" s="16">
+        <f>IF(R419&gt;0,S419*資金模擬!$B$7/R419,0)</f>
+        <v/>
+      </c>
+      <c r="Z419" s="2">
+        <f>IF(OR(Z418=1,R419&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z415"/>
-  <conditionalFormatting sqref="K2:K415">
+  <autoFilter ref="A1:Z419"/>
+  <conditionalFormatting sqref="K2:K419">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -41732,7 +42141,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N415">
+  <conditionalFormatting sqref="N2:N419">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -41740,7 +42149,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q415">
+  <conditionalFormatting sqref="Q2:Q419">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -41805,7 +42214,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 06:27（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 09:11（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -42009,7 +42418,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$209),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$211),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -42174,7 +42583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC209"/>
+  <dimension ref="A1:AC211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -59840,10 +60249,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46279.25</v>
+        <v>46279.375</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5682</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -59879,7 +60288,7 @@
         <v>1281726.24259</v>
       </c>
       <c r="S184" s="4" t="n">
-        <v>0.0277485072005621</v>
+        <v>0.02792413066385668</v>
       </c>
       <c r="T184" s="4" t="n">
         <v>0.02388479100807861</v>
@@ -62148,14 +62557,14 @@
         <v>0.00374745</v>
       </c>
       <c r="H208" s="7" t="n">
-        <v>46279.25</v>
+        <v>46279.375</v>
       </c>
       <c r="I208" s="17" t="n">
-        <v>0.003589</v>
+        <v>0.00346193</v>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K208" s="5">
@@ -62166,11 +62575,7 @@
         <f>IF(C208="做多",I208/E208-1,1-I208/E208)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M208" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M208" s="2" t="inlineStr"/>
       <c r="N208" s="4" t="n">
         <v>-0.0309530274232962</v>
       </c>
@@ -62187,7 +62592,7 @@
         <v>2834501.678442</v>
       </c>
       <c r="S208" s="4" t="n">
-        <v>0.002801905295600982</v>
+        <v>0.03</v>
       </c>
       <c r="T208" s="4" t="n">
         <v>0.02577752871952921</v>
@@ -62248,14 +62653,14 @@
         <v>0.07065450000000001</v>
       </c>
       <c r="H209" s="7" t="n">
-        <v>46279.25</v>
+        <v>46279.29166666666</v>
       </c>
       <c r="I209" s="17" t="n">
-        <v>0.06682</v>
+        <v>0.0652713</v>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K209" s="5">
@@ -62266,11 +62671,7 @@
         <f>IF(C209="做多",I209/E209-1,1-I209/E209)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M209" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M209" s="2" t="inlineStr"/>
       <c r="N209" s="4" t="n">
         <v>-0.03235547886108714</v>
       </c>
@@ -62287,7 +62688,7 @@
         <v>2639902.52603</v>
       </c>
       <c r="S209" s="4" t="n">
-        <v>0.01456382820627145</v>
+        <v>0.03</v>
       </c>
       <c r="T209" s="4" t="n">
         <v>0.0306137613315498</v>
@@ -62321,9 +62722,209 @@
         <v/>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="n">
+        <v>46279.29166666666</v>
+      </c>
+      <c r="E210" s="17" t="n">
+        <v>0.21683</v>
+      </c>
+      <c r="F210" s="17" t="n">
+        <v>0.2103251</v>
+      </c>
+      <c r="G210" s="17" t="n">
+        <v>0.2276715</v>
+      </c>
+      <c r="H210" s="7" t="n">
+        <v>46279.375</v>
+      </c>
+      <c r="I210" s="17" t="n">
+        <v>0.21367</v>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K210" s="5">
+        <f>(H210-D210)*24</f>
+        <v/>
+      </c>
+      <c r="L210" s="4">
+        <f>IF(C210="做多",I210/E210-1,1-I210/E210)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N210" s="4" t="n">
+        <v>-0.03738068812430639</v>
+      </c>
+      <c r="O210" s="4" t="n">
+        <v>0.03386106881319671</v>
+      </c>
+      <c r="P210" s="4" t="n">
+        <v>-0.01970491232591187</v>
+      </c>
+      <c r="Q210" s="19" t="n">
+        <v>-3175872</v>
+      </c>
+      <c r="R210" s="19" t="n">
+        <v>2128113.32288</v>
+      </c>
+      <c r="S210" s="4" t="n">
+        <v>0.02273670617534473</v>
+      </c>
+      <c r="T210" s="4" t="n">
+        <v>0.01000784024350887</v>
+      </c>
+      <c r="U210" s="16" t="n">
+        <v>0.5672975038799286</v>
+      </c>
+      <c r="V210" s="16" t="n">
+        <v>0.7184300341296932</v>
+      </c>
+      <c r="W210" s="4" t="n">
+        <v>0.05441177111906748</v>
+      </c>
+      <c r="X210" s="4" t="n">
+        <v>0.06558931264813628</v>
+      </c>
+      <c r="Y210" s="4" t="n">
+        <v>0.007608961493219879</v>
+      </c>
+      <c r="Z210" s="4" t="n">
+        <v>0.00463370666291496</v>
+      </c>
+      <c r="AA210" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB210" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC210" s="4">
+        <f>(AB210+2*參數!$B$7)/(AA210+AB210)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>VVV_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="n">
+        <v>46279.29166666666</v>
+      </c>
+      <c r="E211" s="17" t="n">
+        <v>21.468</v>
+      </c>
+      <c r="F211" s="17" t="n">
+        <v>20.82396</v>
+      </c>
+      <c r="G211" s="17" t="n">
+        <v>22.5414</v>
+      </c>
+      <c r="H211" s="7" t="n">
+        <v>46279.375</v>
+      </c>
+      <c r="I211" s="17" t="n">
+        <v>21.541</v>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K211" s="5">
+        <f>(H211-D211)*24</f>
+        <v/>
+      </c>
+      <c r="L211" s="4">
+        <f>IF(C211="做多",I211/E211-1,1-I211/E211)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N211" s="4" t="n">
+        <v>-0.02289381457375628</v>
+      </c>
+      <c r="O211" s="4" t="n">
+        <v>0.02160081896245285</v>
+      </c>
+      <c r="P211" s="4" t="n">
+        <v>-0.04553578573905626</v>
+      </c>
+      <c r="Q211" s="19" t="n">
+        <v>-14412.56</v>
+      </c>
+      <c r="R211" s="19" t="n">
+        <v>1369833.00885</v>
+      </c>
+      <c r="S211" s="4" t="n">
+        <v>0.005915781628470285</v>
+      </c>
+      <c r="T211" s="4" t="n">
+        <v>0.009502515371716092</v>
+      </c>
+      <c r="U211" s="16" t="n">
+        <v>0.6271932459439219</v>
+      </c>
+      <c r="V211" s="16" t="n">
+        <v>0.9384328358208933</v>
+      </c>
+      <c r="W211" s="4" t="n">
+        <v>0.09222223725694489</v>
+      </c>
+      <c r="X211" s="4" t="n">
+        <v>0.1147216494845361</v>
+      </c>
+      <c r="Y211" s="4" t="n">
+        <v>0.007608961493219879</v>
+      </c>
+      <c r="Z211" s="4" t="n">
+        <v>0.00463370666291496</v>
+      </c>
+      <c r="AA211" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB211" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC211" s="4">
+        <f>(AB211+2*參數!$B$7)/(AA211+AB211)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC209"/>
-  <conditionalFormatting sqref="J2:J209">
+  <autoFilter ref="A1:AC211"/>
+  <conditionalFormatting sqref="J2:J211">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -62426,31 +63027,31 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PONS_USDT_PERP</t>
+          <t>USELESS_USDT_PERP</t>
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -62458,50 +63059,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A2,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PUMP_USDT_PERP</t>
+          <t>PONS_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -62509,50 +63110,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A3,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>USELESS_USDT_PERP</t>
+          <t>PUMP_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -62560,19 +63161,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A4,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62583,27 +63184,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -62611,19 +63212,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A5,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62634,27 +63235,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -62662,19 +63263,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A6,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62685,27 +63286,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -62713,19 +63314,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A7,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62736,27 +63337,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -62764,19 +63365,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A8,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62787,27 +63388,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -62815,19 +63416,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A9,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62838,27 +63439,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -62866,50 +63467,50 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A10,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>牛来_USDT_PERP</t>
+          <t>VVV_USDT_PERP</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -62917,50 +63518,50 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A11,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>VVV_USDT_PERP</t>
+          <t>牛来_USDT_PERP</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -62968,19 +63569,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A12,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -62991,27 +63592,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -63019,19 +63620,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A13,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63042,27 +63643,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -63070,19 +63671,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A14,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63093,27 +63694,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -63121,19 +63722,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A15,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63144,27 +63745,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -63172,19 +63773,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A16,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63195,27 +63796,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -63223,19 +63824,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A17,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63246,27 +63847,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -63274,19 +63875,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A18,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63297,27 +63898,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -63325,19 +63926,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A19,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63348,27 +63949,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -63376,19 +63977,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A20,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63399,27 +64000,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -63427,19 +64028,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A21,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63450,27 +64051,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -63478,19 +64079,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A22,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63501,27 +64102,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -63529,19 +64130,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A23,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63552,27 +64153,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -63580,19 +64181,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A24,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63603,27 +64204,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -63631,19 +64232,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A25,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63654,27 +64255,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -63682,19 +64283,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A26,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63705,27 +64306,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -63733,19 +64334,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A27,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63756,27 +64357,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -63784,19 +64385,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A28,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63807,27 +64408,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -63835,19 +64436,19 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A29,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63858,27 +64459,27 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -63886,19 +64487,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A30,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63909,27 +64510,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -63937,19 +64538,19 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A31,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63960,27 +64561,27 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -63988,19 +64589,19 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A32,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64011,27 +64612,27 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -64039,19 +64640,19 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A33,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64062,27 +64663,27 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -64090,19 +64691,19 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A34,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64113,27 +64714,27 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -64141,19 +64742,19 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A35,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64164,27 +64765,27 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -64192,19 +64793,19 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A36,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64215,27 +64816,27 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -64243,19 +64844,19 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A37,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64266,27 +64867,27 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -64294,19 +64895,19 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A38,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64317,27 +64918,27 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -64345,19 +64946,19 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A39,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64368,27 +64969,27 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -64396,19 +64997,19 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A40,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64419,27 +65020,27 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -64447,19 +65048,19 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A41,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64470,27 +65071,27 @@
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -64498,19 +65099,19 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A42,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64521,27 +65122,27 @@
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -64549,19 +65150,19 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A43,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64572,27 +65173,27 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -64600,19 +65201,19 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A44,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64623,27 +65224,27 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -64651,19 +65252,19 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A45,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64674,27 +65275,27 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -64702,19 +65303,19 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A46,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64725,27 +65326,27 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -64753,19 +65354,19 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A47,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64776,27 +65377,27 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -64804,19 +65405,19 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A48,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64827,27 +65428,27 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$C$2:$C$209,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$C$2:$C$211,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$C$2:$C$209,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$C$2:$C$211,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -64855,19 +65456,19 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$209,交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$209,交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$209,$A49,交易明細!$J$2:$J$209,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68697,11 +69298,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C210" s="2" t="inlineStr"/>
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="17" t="n"/>
       <c r="F210" s="17" t="n"/>
@@ -70429,11 +71026,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C306" s="2" t="inlineStr"/>
       <c r="D306" s="2" t="n"/>
       <c r="E306" s="17" t="n"/>
       <c r="F306" s="17" t="n"/>
@@ -72053,7 +72646,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr"/>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="17" t="n"/>
       <c r="F396" s="17" t="n"/>
@@ -72179,7 +72776,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C403" s="2" t="inlineStr"/>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D403" s="2" t="n"/>
       <c r="E403" s="17" t="n"/>
       <c r="F403" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$419</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$211</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$424</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$419</f>
+              <f>'資金明細'!$R$2:$R$424</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 09:11（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 14:23（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$211,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$213,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$J$2:$J$211,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$J$2:$J$213,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$J$2:$J$211,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$J$2:$J$213,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$J$2:$J$211,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$J$2:$J$213,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$211,"&lt;&gt;未平倉",交易明細!$L$2:$L$211,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$213,"&lt;&gt;未平倉",交易明細!$L$2:$L$213,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$B$2:$B$211,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$B$2:$B$213,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$211,"做多",交易明細!$J$2:$J$211,"&lt;&gt;未平倉",交易明細!$L$2:$L$211,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉",交易明細!$L$2:$L$213,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$B$2:$B$211,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$B$2:$B$213,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$211,"做空",交易明細!$J$2:$J$211,"&lt;&gt;未平倉",交易明細!$L$2:$L$211,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉",交易明細!$L$2:$L$213,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1097,50 +1097,50 @@
         <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -1149,93 +1149,93 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -1246,47 +1246,70 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1352,7 +1375,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R419</f>
+        <f>資金明細!R424</f>
         <v/>
       </c>
     </row>
@@ -1390,7 +1413,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$419)</f>
+        <f>MAX(資金明細!$R$2:$R$424)</f>
         <v/>
       </c>
     </row>
@@ -1409,7 +1432,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$419)</f>
+        <f>MIN(資金明細!$R$2:$R$424)</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1452,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$419)</f>
+        <f>MIN(資金明細!$X$2:$X$424)</f>
         <v/>
       </c>
     </row>
@@ -1448,7 +1471,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$419,"進場",資金明細!$N$2:$N$419,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$424,"進場",資金明細!$N$2:$N$424,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1467,7 +1490,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$419,"進場",資金明細!$N$2:$N$419,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$424,"進場",資金明細!$N$2:$N$424,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1478,7 +1501,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$419,"出場",資金明細!$N$2:$N$419,"已下單",資金明細!$K$2:$K$419,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$424,"出場",資金明細!$N$2:$N$424,"已下單",資金明細!$K$2:$K$424,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1489,7 +1512,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$211),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$213),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1498,7 +1521,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$419,"出場",資金明細!$N$2:$N$419,"已下單",資金明細!$K$2:$K$419,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$424,"出場",資金明細!$N$2:$N$424,"已下單",資金明細!$K$2:$K$424,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1514,7 +1537,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$419,"出場",資金明細!$N$2:$N$419,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$424,"出場",資金明細!$N$2:$N$424,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1530,7 +1553,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$419)</f>
+        <f>MAX(資金明細!$U$2:$U$424)</f>
         <v/>
       </c>
     </row>
@@ -1546,7 +1569,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$419)</f>
+        <f>MAX(資金明細!$S$2:$S$424)</f>
         <v/>
       </c>
     </row>
@@ -1557,7 +1580,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V419</f>
+        <f>B5*資金明細!V424</f>
         <v/>
       </c>
     </row>
@@ -1568,7 +1591,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N417="已下單",資金明細!O417*交易明細!L210,0)+IF(資金明細!N418="已下單",資金明細!O418*交易明細!L211,0)</f>
+        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N424="已下單",資金明細!O424*交易明細!L213,0)</f>
         <v/>
       </c>
     </row>
@@ -1579,7 +1602,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$419)</f>
+        <f>MAX(資金明細!$Y$2:$Y$424)</f>
         <v/>
       </c>
     </row>
@@ -1601,7 +1624,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$419,MATCH(1,資金明細!$Z$2:$Z$419,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$424,MATCH(1,資金明細!$Z$2:$Z$424,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1612,7 +1635,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$419,"進場",資金明細!$N$2:$N$419,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$424,"進場",資金明細!$N$2:$N$424,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1677,7 +1700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z419"/>
+  <dimension ref="A1:Z424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -41875,11 +41898,7 @@
         <v>0.2276715</v>
       </c>
       <c r="J417" s="17" t="n"/>
-      <c r="K417" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K417" s="2" t="n"/>
       <c r="L417" s="5" t="n"/>
       <c r="M417" s="16">
         <f>資金模擬!$B$5*V416</f>
@@ -41969,11 +41988,7 @@
         <v>22.5414</v>
       </c>
       <c r="J418" s="17" t="n"/>
-      <c r="K418" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K418" s="2" t="n"/>
       <c r="L418" s="5" t="n"/>
       <c r="M418" s="16">
         <f>資金模擬!$B$5*V417</f>
@@ -42131,9 +42146,502 @@
         <v/>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="2" t="n">
+        <v>418</v>
+      </c>
+      <c r="B420" s="7" t="n">
+        <v>46279.41666666666</v>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G420" s="17" t="n">
+        <v>0.21683</v>
+      </c>
+      <c r="H420" s="17" t="n">
+        <v>0.2103251</v>
+      </c>
+      <c r="I420" s="17" t="n">
+        <v>0.2276715</v>
+      </c>
+      <c r="J420" s="17" t="n">
+        <v>0.2103251</v>
+      </c>
+      <c r="K420" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L420" s="5">
+        <f>交易明細!K210</f>
+        <v/>
+      </c>
+      <c r="M420" s="16">
+        <f>M417</f>
+        <v/>
+      </c>
+      <c r="N420" s="2">
+        <f>N417</f>
+        <v/>
+      </c>
+      <c r="O420" s="16">
+        <f>O417</f>
+        <v/>
+      </c>
+      <c r="P420" s="4">
+        <f>交易明細!L210</f>
+        <v/>
+      </c>
+      <c r="Q420" s="10">
+        <f>IF(N420="已下單",O420*P420,0)</f>
+        <v/>
+      </c>
+      <c r="R420" s="10">
+        <f>R419+Q420</f>
+        <v/>
+      </c>
+      <c r="S420" s="16">
+        <f>S419-IF(N420="已下單",M420,0)</f>
+        <v/>
+      </c>
+      <c r="T420" s="16">
+        <f>R420-S420</f>
+        <v/>
+      </c>
+      <c r="U420" s="2">
+        <f>U419-IF(N420="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V420" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R420,0),MAX(V419,FLOOR(MAX(R420,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W420" s="10">
+        <f>MAX(W419,R420)</f>
+        <v/>
+      </c>
+      <c r="X420" s="4">
+        <f>IF(W420&gt;0,R420/W420-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y420" s="16">
+        <f>IF(R420&gt;0,S420*資金模擬!$B$7/R420,0)</f>
+        <v/>
+      </c>
+      <c r="Z420" s="2">
+        <f>IF(OR(Z419=1,R420&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="B421" s="7" t="n">
+        <v>46279.45833333334</v>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>BTW_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G421" s="17" t="n">
+        <v>0.70762</v>
+      </c>
+      <c r="H421" s="17" t="n">
+        <v>0.7288486000000001</v>
+      </c>
+      <c r="I421" s="17" t="n">
+        <v>0.672239</v>
+      </c>
+      <c r="J421" s="17" t="n"/>
+      <c r="K421" s="2" t="n"/>
+      <c r="L421" s="5" t="n"/>
+      <c r="M421" s="16">
+        <f>資金模擬!$B$5*V420</f>
+        <v/>
+      </c>
+      <c r="N421" s="2">
+        <f>IF(Z420=1,"已停止",IF(T420&gt;=M421,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O421" s="16">
+        <f>IF(N421="已下單",M421*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P421" s="4" t="n"/>
+      <c r="Q421" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R421" s="10">
+        <f>R420+Q421</f>
+        <v/>
+      </c>
+      <c r="S421" s="16">
+        <f>S420+IF(N421="已下單",M421,0)</f>
+        <v/>
+      </c>
+      <c r="T421" s="16">
+        <f>R421-S421</f>
+        <v/>
+      </c>
+      <c r="U421" s="2">
+        <f>U420+IF(N421="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V421" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R421,0),MAX(V420,FLOOR(MAX(R421,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W421" s="10">
+        <f>MAX(W420,R421)</f>
+        <v/>
+      </c>
+      <c r="X421" s="4">
+        <f>IF(W421&gt;0,R421/W421-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y421" s="16">
+        <f>IF(R421&gt;0,S421*資金模擬!$B$7/R421,0)</f>
+        <v/>
+      </c>
+      <c r="Z421" s="2">
+        <f>IF(OR(Z420=1,R421&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="B422" s="7" t="n">
+        <v>46279.5</v>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>VVV_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G422" s="17" t="n">
+        <v>21.468</v>
+      </c>
+      <c r="H422" s="17" t="n">
+        <v>20.82396</v>
+      </c>
+      <c r="I422" s="17" t="n">
+        <v>22.5414</v>
+      </c>
+      <c r="J422" s="17" t="n">
+        <v>22.5414</v>
+      </c>
+      <c r="K422" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L422" s="5">
+        <f>交易明細!K211</f>
+        <v/>
+      </c>
+      <c r="M422" s="16">
+        <f>M418</f>
+        <v/>
+      </c>
+      <c r="N422" s="2">
+        <f>N418</f>
+        <v/>
+      </c>
+      <c r="O422" s="16">
+        <f>O418</f>
+        <v/>
+      </c>
+      <c r="P422" s="4">
+        <f>交易明細!L211</f>
+        <v/>
+      </c>
+      <c r="Q422" s="10">
+        <f>IF(N422="已下單",O422*P422,0)</f>
+        <v/>
+      </c>
+      <c r="R422" s="10">
+        <f>R421+Q422</f>
+        <v/>
+      </c>
+      <c r="S422" s="16">
+        <f>S421-IF(N422="已下單",M422,0)</f>
+        <v/>
+      </c>
+      <c r="T422" s="16">
+        <f>R422-S422</f>
+        <v/>
+      </c>
+      <c r="U422" s="2">
+        <f>U421-IF(N422="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V422" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R422,0),MAX(V421,FLOOR(MAX(R422,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W422" s="10">
+        <f>MAX(W421,R422)</f>
+        <v/>
+      </c>
+      <c r="X422" s="4">
+        <f>IF(W422&gt;0,R422/W422-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y422" s="16">
+        <f>IF(R422&gt;0,S422*資金模擬!$B$7/R422,0)</f>
+        <v/>
+      </c>
+      <c r="Z422" s="2">
+        <f>IF(OR(Z421=1,R422&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="B423" s="7" t="n">
+        <v>46279.5</v>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>BTW_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G423" s="17" t="n">
+        <v>0.70762</v>
+      </c>
+      <c r="H423" s="17" t="n">
+        <v>0.7288486000000001</v>
+      </c>
+      <c r="I423" s="17" t="n">
+        <v>0.672239</v>
+      </c>
+      <c r="J423" s="17" t="n">
+        <v>0.672239</v>
+      </c>
+      <c r="K423" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L423" s="5">
+        <f>交易明細!K212</f>
+        <v/>
+      </c>
+      <c r="M423" s="16">
+        <f>M421</f>
+        <v/>
+      </c>
+      <c r="N423" s="2">
+        <f>N421</f>
+        <v/>
+      </c>
+      <c r="O423" s="16">
+        <f>O421</f>
+        <v/>
+      </c>
+      <c r="P423" s="4">
+        <f>交易明細!L212</f>
+        <v/>
+      </c>
+      <c r="Q423" s="10">
+        <f>IF(N423="已下單",O423*P423,0)</f>
+        <v/>
+      </c>
+      <c r="R423" s="10">
+        <f>R422+Q423</f>
+        <v/>
+      </c>
+      <c r="S423" s="16">
+        <f>S422-IF(N423="已下單",M423,0)</f>
+        <v/>
+      </c>
+      <c r="T423" s="16">
+        <f>R423-S423</f>
+        <v/>
+      </c>
+      <c r="U423" s="2">
+        <f>U422-IF(N423="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V423" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R423,0),MAX(V422,FLOOR(MAX(R423,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W423" s="10">
+        <f>MAX(W422,R423)</f>
+        <v/>
+      </c>
+      <c r="X423" s="4">
+        <f>IF(W423&gt;0,R423/W423-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y423" s="16">
+        <f>IF(R423&gt;0,S423*資金模擬!$B$7/R423,0)</f>
+        <v/>
+      </c>
+      <c r="Z423" s="2">
+        <f>IF(OR(Z422=1,R423&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>422</v>
+      </c>
+      <c r="B424" s="7" t="n">
+        <v>46279.5</v>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G424" s="17" t="n">
+        <v>0.11776</v>
+      </c>
+      <c r="H424" s="17" t="n">
+        <v>0.1142272</v>
+      </c>
+      <c r="I424" s="17" t="n">
+        <v>0.123648</v>
+      </c>
+      <c r="J424" s="17" t="n"/>
+      <c r="K424" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L424" s="5" t="n"/>
+      <c r="M424" s="16">
+        <f>資金模擬!$B$5*V423</f>
+        <v/>
+      </c>
+      <c r="N424" s="2">
+        <f>IF(Z423=1,"已停止",IF(T423&gt;=M424,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O424" s="16">
+        <f>IF(N424="已下單",M424*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P424" s="4" t="n"/>
+      <c r="Q424" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R424" s="10">
+        <f>R423+Q424</f>
+        <v/>
+      </c>
+      <c r="S424" s="16">
+        <f>S423+IF(N424="已下單",M424,0)</f>
+        <v/>
+      </c>
+      <c r="T424" s="16">
+        <f>R424-S424</f>
+        <v/>
+      </c>
+      <c r="U424" s="2">
+        <f>U423+IF(N424="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V424" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R424,0),MAX(V423,FLOOR(MAX(R424,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W424" s="10">
+        <f>MAX(W423,R424)</f>
+        <v/>
+      </c>
+      <c r="X424" s="4">
+        <f>IF(W424&gt;0,R424/W424-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y424" s="16">
+        <f>IF(R424&gt;0,S424*資金模擬!$B$7/R424,0)</f>
+        <v/>
+      </c>
+      <c r="Z424" s="2">
+        <f>IF(OR(Z423=1,R424&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z419"/>
-  <conditionalFormatting sqref="K2:K419">
+  <autoFilter ref="A1:Z424"/>
+  <conditionalFormatting sqref="K2:K424">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -42141,7 +42649,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N419">
+  <conditionalFormatting sqref="N2:N424">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -42149,7 +42657,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q419">
+  <conditionalFormatting sqref="Q2:Q424">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -42214,7 +42722,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 09:11（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 14:23（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -42418,7 +42926,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$211),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$213),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -42583,7 +43091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC211"/>
+  <dimension ref="A1:AC213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -60249,10 +60757,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46279.375</v>
+        <v>46279.58333333334</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.572</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -62749,14 +63257,14 @@
         <v>0.2276715</v>
       </c>
       <c r="H210" s="7" t="n">
-        <v>46279.375</v>
+        <v>46279.41666666666</v>
       </c>
       <c r="I210" s="17" t="n">
-        <v>0.21367</v>
+        <v>0.2103251</v>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K210" s="5">
@@ -62767,11 +63275,7 @@
         <f>IF(C210="做多",I210/E210-1,1-I210/E210)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M210" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M210" s="2" t="inlineStr"/>
       <c r="N210" s="4" t="n">
         <v>-0.03738068812430639</v>
       </c>
@@ -62788,7 +63292,7 @@
         <v>2128113.32288</v>
       </c>
       <c r="S210" s="4" t="n">
-        <v>0.02273670617534473</v>
+        <v>0.03</v>
       </c>
       <c r="T210" s="4" t="n">
         <v>0.01000784024350887</v>
@@ -62849,14 +63353,14 @@
         <v>22.5414</v>
       </c>
       <c r="H211" s="7" t="n">
-        <v>46279.375</v>
+        <v>46279.5</v>
       </c>
       <c r="I211" s="17" t="n">
-        <v>21.541</v>
+        <v>22.5414</v>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K211" s="5">
@@ -62867,11 +63371,7 @@
         <f>IF(C211="做多",I211/E211-1,1-I211/E211)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M211" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M211" s="2" t="inlineStr"/>
       <c r="N211" s="4" t="n">
         <v>-0.02289381457375628</v>
       </c>
@@ -62888,10 +63388,10 @@
         <v>1369833.00885</v>
       </c>
       <c r="S211" s="4" t="n">
-        <v>0.005915781628470285</v>
+        <v>0.01276318241103036</v>
       </c>
       <c r="T211" s="4" t="n">
-        <v>0.009502515371716092</v>
+        <v>0.05</v>
       </c>
       <c r="U211" s="16" t="n">
         <v>0.6271932459439219</v>
@@ -62922,9 +63422,205 @@
         <v/>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>BTW_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="n">
+        <v>46279.45833333334</v>
+      </c>
+      <c r="E212" s="17" t="n">
+        <v>0.70762</v>
+      </c>
+      <c r="F212" s="17" t="n">
+        <v>0.7288486000000001</v>
+      </c>
+      <c r="G212" s="17" t="n">
+        <v>0.672239</v>
+      </c>
+      <c r="H212" s="7" t="n">
+        <v>46279.5</v>
+      </c>
+      <c r="I212" s="17" t="n">
+        <v>0.672239</v>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="K212" s="5">
+        <f>(H212-D212)*24</f>
+        <v/>
+      </c>
+      <c r="L212" s="4">
+        <f>IF(C212="做多",I212/E212-1,1-I212/E212)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="4" t="n">
+        <v>0.06417984070839045</v>
+      </c>
+      <c r="O212" s="4" t="n">
+        <v>0.05447806281300982</v>
+      </c>
+      <c r="P212" s="4" t="n">
+        <v>0.05269413873762541</v>
+      </c>
+      <c r="Q212" s="19" t="n">
+        <v>29072</v>
+      </c>
+      <c r="R212" s="19" t="n">
+        <v>1249265.946402</v>
+      </c>
+      <c r="S212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U212" s="16" t="n">
+        <v>0.5619089762421139</v>
+      </c>
+      <c r="V212" s="16" t="n">
+        <v>0.8878120158374936</v>
+      </c>
+      <c r="W212" s="4" t="n">
+        <v>0.3125680158956472</v>
+      </c>
+      <c r="X212" s="4" t="n">
+        <v>0.2763570379829945</v>
+      </c>
+      <c r="Y212" s="4" t="n">
+        <v>0.006412035895985824</v>
+      </c>
+      <c r="Z212" s="4" t="n">
+        <v>0.0072719933770935</v>
+      </c>
+      <c r="AA212" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB212" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC212" s="4">
+        <f>(AB212+2*參數!$B$7)/(AA212+AB212)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="n">
+        <v>46279.5</v>
+      </c>
+      <c r="E213" s="17" t="n">
+        <v>0.11776</v>
+      </c>
+      <c r="F213" s="17" t="n">
+        <v>0.1142272</v>
+      </c>
+      <c r="G213" s="17" t="n">
+        <v>0.123648</v>
+      </c>
+      <c r="H213" s="7" t="n">
+        <v>46279.58333333334</v>
+      </c>
+      <c r="I213" s="17" t="n">
+        <v>0.12095</v>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K213" s="5">
+        <f>(H213-D213)*24</f>
+        <v/>
+      </c>
+      <c r="L213" s="4">
+        <f>IF(C213="做多",I213/E213-1,1-I213/E213)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N213" s="4" t="n">
+        <v>-0.02281968301385784</v>
+      </c>
+      <c r="O213" s="4" t="n">
+        <v>0.05705666237909381</v>
+      </c>
+      <c r="P213" s="4" t="n">
+        <v>-0.04483810265394839</v>
+      </c>
+      <c r="Q213" s="19" t="n">
+        <v>-7024900</v>
+      </c>
+      <c r="R213" s="19" t="n">
+        <v>2030342.06041</v>
+      </c>
+      <c r="S213" s="4" t="n">
+        <v>0.02734375</v>
+      </c>
+      <c r="T213" s="4" t="n">
+        <v>0.04611073369565211</v>
+      </c>
+      <c r="U213" s="16" t="n">
+        <v>0.4761997968648705</v>
+      </c>
+      <c r="V213" s="16" t="n">
+        <v>0.7176470588235297</v>
+      </c>
+      <c r="W213" s="4" t="n">
+        <v>0.02487254034117869</v>
+      </c>
+      <c r="X213" s="4" t="n">
+        <v>0.1282848471389443</v>
+      </c>
+      <c r="Y213" s="4" t="n">
+        <v>0.000323521564452256</v>
+      </c>
+      <c r="Z213" s="4" t="n">
+        <v>-0.006638404311750445</v>
+      </c>
+      <c r="AA213" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB213" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC213" s="4">
+        <f>(AB213+2*參數!$B$7)/(AA213+AB213)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC211"/>
-  <conditionalFormatting sqref="J2:J211">
+  <autoFilter ref="A1:AC213"/>
+  <conditionalFormatting sqref="J2:J213">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -62945,7 +63641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -63031,27 +63727,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -63059,19 +63755,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A2,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63082,27 +63778,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -63110,19 +63806,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A3,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63133,27 +63829,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -63161,19 +63857,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A4,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63184,27 +63880,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -63212,19 +63908,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A5,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63235,27 +63931,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -63263,19 +63959,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A6,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63286,27 +63982,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -63314,19 +64010,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A7,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63337,27 +64033,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -63365,19 +64061,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A8,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63388,27 +64084,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -63416,50 +64112,50 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A9,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AKE_USDT_PERP</t>
+          <t>牛来_USDT_PERP</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -63467,50 +64163,50 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A10,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>VVV_USDT_PERP</t>
+          <t>AKE_USDT_PERP</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -63518,50 +64214,50 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A11,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>牛来_USDT_PERP</t>
+          <t>VVV_USDT_PERP</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -63569,19 +64265,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A12,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63592,27 +64288,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -63620,19 +64316,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A13,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63643,27 +64339,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -63671,19 +64367,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A14,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63694,27 +64390,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -63722,19 +64418,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A15,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63745,27 +64441,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -63773,19 +64469,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A16,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63796,27 +64492,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -63824,19 +64520,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A17,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63847,27 +64543,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -63875,19 +64571,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A18,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63898,27 +64594,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -63926,19 +64622,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A19,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63949,27 +64645,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -63977,19 +64673,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A20,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64000,27 +64696,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -64028,19 +64724,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A21,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64051,27 +64747,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -64079,19 +64775,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A22,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64102,27 +64798,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -64130,19 +64826,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A23,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64153,27 +64849,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -64181,19 +64877,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A24,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64204,27 +64900,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -64232,19 +64928,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A25,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64255,27 +64951,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -64283,19 +64979,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A26,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64306,27 +65002,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -64334,19 +65030,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A27,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64357,27 +65053,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -64385,19 +65081,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A28,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64408,27 +65104,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -64436,19 +65132,19 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A29,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64459,27 +65155,27 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -64487,19 +65183,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A30,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64510,27 +65206,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -64538,19 +65234,19 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A31,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64561,27 +65257,27 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -64589,19 +65285,19 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A32,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64612,27 +65308,27 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -64640,19 +65336,19 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A33,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64663,27 +65359,27 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -64691,19 +65387,19 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A34,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64714,27 +65410,27 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -64742,19 +65438,19 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A35,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64765,27 +65461,27 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -64793,19 +65489,19 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A36,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64816,27 +65512,27 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -64844,19 +65540,19 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A37,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64867,27 +65563,27 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -64895,19 +65591,19 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A38,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64918,27 +65614,27 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -64946,19 +65642,19 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A39,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64969,27 +65665,27 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -64997,19 +65693,19 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A40,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65020,27 +65716,27 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -65048,19 +65744,19 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A41,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65071,27 +65767,27 @@
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -65099,19 +65795,19 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A42,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65122,27 +65818,27 @@
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -65150,19 +65846,19 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A43,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65173,27 +65869,27 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -65201,19 +65897,19 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A44,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65224,27 +65920,27 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -65252,19 +65948,19 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A45,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65275,27 +65971,27 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -65303,19 +65999,19 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A46,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65326,27 +66022,27 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -65354,19 +66050,19 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A47,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65377,27 +66073,27 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -65405,19 +66101,19 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A48,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65428,27 +66124,27 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$C$2:$C$211,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$C$2:$C$213,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$C$2:$C$211,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$C$2:$C$213,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -65456,24 +66152,75 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$211,交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$211,交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$211,$A49,交易明細!$J$2:$J$211,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>BTW_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B50" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50)</f>
+        <v/>
+      </c>
+      <c r="C50" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$C$2:$C$213,"做多")</f>
+        <v/>
+      </c>
+      <c r="D50" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$C$2:$C$213,"做空")</f>
+        <v/>
+      </c>
+      <c r="E50" s="2">
+        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F50" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G50" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"止損")</f>
+        <v/>
+      </c>
+      <c r="H50" s="4">
+        <f>IFERROR(F50/E50,0)</f>
+        <v/>
+      </c>
+      <c r="I50" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J50" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K50" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L50" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L49"/>
+  <autoFilter ref="A1:L50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -72646,11 +73393,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C396" s="2" t="inlineStr"/>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="17" t="n"/>
       <c r="F396" s="17" t="n"/>
@@ -72776,11 +73519,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C403" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C403" s="2" t="inlineStr"/>
       <c r="D403" s="2" t="n"/>
       <c r="E403" s="17" t="n"/>
       <c r="F403" s="17" t="n"/>
@@ -73500,7 +74239,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr"/>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="17" t="n"/>
       <c r="F443" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$424</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$213</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$424</f>
+              <f>'資金明細'!$R$2:$R$437</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 14:23（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 22:10（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$213,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$219,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$J$2:$J$213,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$J$2:$J$219,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$J$2:$J$213,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$J$2:$J$219,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$J$2:$J$213,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$J$2:$J$219,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$213,"&lt;&gt;未平倉",交易明細!$L$2:$L$213,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$219,"&lt;&gt;未平倉",交易明細!$L$2:$L$219,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$B$2:$B$213,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$B$2:$B$219,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$213,"做多",交易明細!$J$2:$J$213,"&lt;&gt;未平倉",交易明細!$L$2:$L$213,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉",交易明細!$L$2:$L$219,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$B$2:$B$213,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$B$2:$B$219,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$213,"做空",交易明細!$J$2:$J$213,"&lt;&gt;未平倉",交易明細!$L$2:$L$213,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉",交易明細!$L$2:$L$219,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,33 +1085,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1120,50 +1120,50 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -1172,93 +1172,93 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -1269,47 +1269,70 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1375,7 +1398,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R424</f>
+        <f>資金明細!R437</f>
         <v/>
       </c>
     </row>
@@ -1413,7 +1436,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$424)</f>
+        <f>MAX(資金明細!$R$2:$R$437)</f>
         <v/>
       </c>
     </row>
@@ -1432,7 +1455,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$424)</f>
+        <f>MIN(資金明細!$R$2:$R$437)</f>
         <v/>
       </c>
     </row>
@@ -1452,7 +1475,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$424)</f>
+        <f>MIN(資金明細!$X$2:$X$437)</f>
         <v/>
       </c>
     </row>
@@ -1471,7 +1494,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$424,"進場",資金明細!$N$2:$N$424,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$437,"進場",資金明細!$N$2:$N$437,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1490,7 +1513,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$424,"進場",資金明細!$N$2:$N$424,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$437,"進場",資金明細!$N$2:$N$437,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1501,7 +1524,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$424,"出場",資金明細!$N$2:$N$424,"已下單",資金明細!$K$2:$K$424,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$437,"出場",資金明細!$N$2:$N$437,"已下單",資金明細!$K$2:$K$437,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1512,7 +1535,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$213),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$219),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1521,7 +1544,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$424,"出場",資金明細!$N$2:$N$424,"已下單",資金明細!$K$2:$K$424,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$437,"出場",資金明細!$N$2:$N$437,"已下單",資金明細!$K$2:$K$437,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1537,7 +1560,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$424,"出場",資金明細!$N$2:$N$424,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$437,"出場",資金明細!$N$2:$N$437,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1553,7 +1576,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$424)</f>
+        <f>MAX(資金明細!$U$2:$U$437)</f>
         <v/>
       </c>
     </row>
@@ -1569,7 +1592,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$424)</f>
+        <f>MAX(資金明細!$S$2:$S$437)</f>
         <v/>
       </c>
     </row>
@@ -1580,7 +1603,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V424</f>
+        <f>B5*資金明細!V437</f>
         <v/>
       </c>
     </row>
@@ -1591,7 +1614,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N424="已下單",資金明細!O424*交易明細!L213,0)</f>
+        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)</f>
         <v/>
       </c>
     </row>
@@ -1602,7 +1625,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$424)</f>
+        <f>MAX(資金明細!$Y$2:$Y$437)</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1647,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$424,MATCH(1,資金明細!$Z$2:$Z$424,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$437,MATCH(1,資金明細!$Z$2:$Z$437,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1635,7 +1658,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$424,"進場",資金明細!$N$2:$N$424,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$437,"進場",資金明細!$N$2:$N$437,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1700,7 +1723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z424"/>
+  <dimension ref="A1:Z437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -42580,11 +42603,7 @@
         <v>0.123648</v>
       </c>
       <c r="J424" s="17" t="n"/>
-      <c r="K424" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K424" s="2" t="n"/>
       <c r="L424" s="5" t="n"/>
       <c r="M424" s="16">
         <f>資金模擬!$B$5*V423</f>
@@ -42639,9 +42658,1270 @@
         <v/>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>423</v>
+      </c>
+      <c r="B425" s="7" t="n">
+        <v>46279.625</v>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G425" s="17" t="n">
+        <v>0.11776</v>
+      </c>
+      <c r="H425" s="17" t="n">
+        <v>0.1142272</v>
+      </c>
+      <c r="I425" s="17" t="n">
+        <v>0.123648</v>
+      </c>
+      <c r="J425" s="17" t="n">
+        <v>0.123648</v>
+      </c>
+      <c r="K425" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L425" s="5">
+        <f>交易明細!K213</f>
+        <v/>
+      </c>
+      <c r="M425" s="16">
+        <f>M424</f>
+        <v/>
+      </c>
+      <c r="N425" s="2">
+        <f>N424</f>
+        <v/>
+      </c>
+      <c r="O425" s="16">
+        <f>O424</f>
+        <v/>
+      </c>
+      <c r="P425" s="4">
+        <f>交易明細!L213</f>
+        <v/>
+      </c>
+      <c r="Q425" s="10">
+        <f>IF(N425="已下單",O425*P425,0)</f>
+        <v/>
+      </c>
+      <c r="R425" s="10">
+        <f>R424+Q425</f>
+        <v/>
+      </c>
+      <c r="S425" s="16">
+        <f>S424-IF(N425="已下單",M425,0)</f>
+        <v/>
+      </c>
+      <c r="T425" s="16">
+        <f>R425-S425</f>
+        <v/>
+      </c>
+      <c r="U425" s="2">
+        <f>U424-IF(N425="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V425" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R425,0),MAX(V424,FLOOR(MAX(R425,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W425" s="10">
+        <f>MAX(W424,R425)</f>
+        <v/>
+      </c>
+      <c r="X425" s="4">
+        <f>IF(W425&gt;0,R425/W425-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y425" s="16">
+        <f>IF(R425&gt;0,S425*資金模擬!$B$7/R425,0)</f>
+        <v/>
+      </c>
+      <c r="Z425" s="2">
+        <f>IF(OR(Z424=1,R425&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>424</v>
+      </c>
+      <c r="B426" s="7" t="n">
+        <v>46279.625</v>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>FIL_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G426" s="17" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="H426" s="17" t="n">
+        <v>1.02588</v>
+      </c>
+      <c r="I426" s="17" t="n">
+        <v>0.9461999999999999</v>
+      </c>
+      <c r="J426" s="17" t="n"/>
+      <c r="K426" s="2" t="n"/>
+      <c r="L426" s="5" t="n"/>
+      <c r="M426" s="16">
+        <f>資金模擬!$B$5*V425</f>
+        <v/>
+      </c>
+      <c r="N426" s="2">
+        <f>IF(Z425=1,"已停止",IF(T425&gt;=M426,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O426" s="16">
+        <f>IF(N426="已下單",M426*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P426" s="4" t="n"/>
+      <c r="Q426" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R426" s="10">
+        <f>R425+Q426</f>
+        <v/>
+      </c>
+      <c r="S426" s="16">
+        <f>S425+IF(N426="已下單",M426,0)</f>
+        <v/>
+      </c>
+      <c r="T426" s="16">
+        <f>R426-S426</f>
+        <v/>
+      </c>
+      <c r="U426" s="2">
+        <f>U425+IF(N426="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V426" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R426,0),MAX(V425,FLOOR(MAX(R426,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W426" s="10">
+        <f>MAX(W425,R426)</f>
+        <v/>
+      </c>
+      <c r="X426" s="4">
+        <f>IF(W426&gt;0,R426/W426-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y426" s="16">
+        <f>IF(R426&gt;0,S426*資金模擬!$B$7/R426,0)</f>
+        <v/>
+      </c>
+      <c r="Z426" s="2">
+        <f>IF(OR(Z425=1,R426&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>425</v>
+      </c>
+      <c r="B427" s="7" t="n">
+        <v>46279.66666666666</v>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>LSK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G427" s="17" t="n">
+        <v>0.9222</v>
+      </c>
+      <c r="H427" s="17" t="n">
+        <v>0.9498660000000001</v>
+      </c>
+      <c r="I427" s="17" t="n">
+        <v>0.8760899999999999</v>
+      </c>
+      <c r="J427" s="17" t="n"/>
+      <c r="K427" s="2" t="n"/>
+      <c r="L427" s="5" t="n"/>
+      <c r="M427" s="16">
+        <f>資金模擬!$B$5*V426</f>
+        <v/>
+      </c>
+      <c r="N427" s="2">
+        <f>IF(Z426=1,"已停止",IF(T426&gt;=M427,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O427" s="16">
+        <f>IF(N427="已下單",M427*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P427" s="4" t="n"/>
+      <c r="Q427" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R427" s="10">
+        <f>R426+Q427</f>
+        <v/>
+      </c>
+      <c r="S427" s="16">
+        <f>S426+IF(N427="已下單",M427,0)</f>
+        <v/>
+      </c>
+      <c r="T427" s="16">
+        <f>R427-S427</f>
+        <v/>
+      </c>
+      <c r="U427" s="2">
+        <f>U426+IF(N427="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V427" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R427,0),MAX(V426,FLOOR(MAX(R427,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W427" s="10">
+        <f>MAX(W426,R427)</f>
+        <v/>
+      </c>
+      <c r="X427" s="4">
+        <f>IF(W427&gt;0,R427/W427-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y427" s="16">
+        <f>IF(R427&gt;0,S427*資金模擬!$B$7/R427,0)</f>
+        <v/>
+      </c>
+      <c r="Z427" s="2">
+        <f>IF(OR(Z426=1,R427&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>426</v>
+      </c>
+      <c r="B428" s="7" t="n">
+        <v>46279.66666666666</v>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G428" s="17" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="H428" s="17" t="n">
+        <v>0.583083</v>
+      </c>
+      <c r="I428" s="17" t="n">
+        <v>0.537795</v>
+      </c>
+      <c r="J428" s="17" t="n"/>
+      <c r="K428" s="2" t="n"/>
+      <c r="L428" s="5" t="n"/>
+      <c r="M428" s="16">
+        <f>資金模擬!$B$5*V427</f>
+        <v/>
+      </c>
+      <c r="N428" s="2">
+        <f>IF(Z427=1,"已停止",IF(T427&gt;=M428,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O428" s="16">
+        <f>IF(N428="已下單",M428*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P428" s="4" t="n"/>
+      <c r="Q428" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R428" s="10">
+        <f>R427+Q428</f>
+        <v/>
+      </c>
+      <c r="S428" s="16">
+        <f>S427+IF(N428="已下單",M428,0)</f>
+        <v/>
+      </c>
+      <c r="T428" s="16">
+        <f>R428-S428</f>
+        <v/>
+      </c>
+      <c r="U428" s="2">
+        <f>U427+IF(N428="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V428" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R428,0),MAX(V427,FLOOR(MAX(R428,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W428" s="10">
+        <f>MAX(W427,R428)</f>
+        <v/>
+      </c>
+      <c r="X428" s="4">
+        <f>IF(W428&gt;0,R428/W428-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y428" s="16">
+        <f>IF(R428&gt;0,S428*資金模擬!$B$7/R428,0)</f>
+        <v/>
+      </c>
+      <c r="Z428" s="2">
+        <f>IF(OR(Z427=1,R428&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>427</v>
+      </c>
+      <c r="B429" s="7" t="n">
+        <v>46279.66666666666</v>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G429" s="17" t="n">
+        <v>0.12014</v>
+      </c>
+      <c r="H429" s="17" t="n">
+        <v>0.1165358</v>
+      </c>
+      <c r="I429" s="17" t="n">
+        <v>0.126147</v>
+      </c>
+      <c r="J429" s="17" t="n"/>
+      <c r="K429" s="2" t="n"/>
+      <c r="L429" s="5" t="n"/>
+      <c r="M429" s="16">
+        <f>資金模擬!$B$5*V428</f>
+        <v/>
+      </c>
+      <c r="N429" s="2">
+        <f>IF(Z428=1,"已停止",IF(T428&gt;=M429,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O429" s="16">
+        <f>IF(N429="已下單",M429*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P429" s="4" t="n"/>
+      <c r="Q429" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R429" s="10">
+        <f>R428+Q429</f>
+        <v/>
+      </c>
+      <c r="S429" s="16">
+        <f>S428+IF(N429="已下單",M429,0)</f>
+        <v/>
+      </c>
+      <c r="T429" s="16">
+        <f>R429-S429</f>
+        <v/>
+      </c>
+      <c r="U429" s="2">
+        <f>U428+IF(N429="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V429" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R429,0),MAX(V428,FLOOR(MAX(R429,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W429" s="10">
+        <f>MAX(W428,R429)</f>
+        <v/>
+      </c>
+      <c r="X429" s="4">
+        <f>IF(W429&gt;0,R429/W429-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y429" s="16">
+        <f>IF(R429&gt;0,S429*資金模擬!$B$7/R429,0)</f>
+        <v/>
+      </c>
+      <c r="Z429" s="2">
+        <f>IF(OR(Z428=1,R429&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="B430" s="7" t="n">
+        <v>46279.70833333334</v>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>LSK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G430" s="17" t="n">
+        <v>0.9222</v>
+      </c>
+      <c r="H430" s="17" t="n">
+        <v>0.9498660000000001</v>
+      </c>
+      <c r="I430" s="17" t="n">
+        <v>0.8760899999999999</v>
+      </c>
+      <c r="J430" s="17" t="n">
+        <v>0.9498660000000001</v>
+      </c>
+      <c r="K430" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L430" s="5">
+        <f>交易明細!K215</f>
+        <v/>
+      </c>
+      <c r="M430" s="16">
+        <f>M427</f>
+        <v/>
+      </c>
+      <c r="N430" s="2">
+        <f>N427</f>
+        <v/>
+      </c>
+      <c r="O430" s="16">
+        <f>O427</f>
+        <v/>
+      </c>
+      <c r="P430" s="4">
+        <f>交易明細!L215</f>
+        <v/>
+      </c>
+      <c r="Q430" s="10">
+        <f>IF(N430="已下單",O430*P430,0)</f>
+        <v/>
+      </c>
+      <c r="R430" s="10">
+        <f>R429+Q430</f>
+        <v/>
+      </c>
+      <c r="S430" s="16">
+        <f>S429-IF(N430="已下單",M430,0)</f>
+        <v/>
+      </c>
+      <c r="T430" s="16">
+        <f>R430-S430</f>
+        <v/>
+      </c>
+      <c r="U430" s="2">
+        <f>U429-IF(N430="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V430" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R430,0),MAX(V429,FLOOR(MAX(R430,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W430" s="10">
+        <f>MAX(W429,R430)</f>
+        <v/>
+      </c>
+      <c r="X430" s="4">
+        <f>IF(W430&gt;0,R430/W430-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y430" s="16">
+        <f>IF(R430&gt;0,S430*資金模擬!$B$7/R430,0)</f>
+        <v/>
+      </c>
+      <c r="Z430" s="2">
+        <f>IF(OR(Z429=1,R430&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="B431" s="7" t="n">
+        <v>46279.70833333334</v>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G431" s="17" t="n">
+        <v>0.12014</v>
+      </c>
+      <c r="H431" s="17" t="n">
+        <v>0.1165358</v>
+      </c>
+      <c r="I431" s="17" t="n">
+        <v>0.126147</v>
+      </c>
+      <c r="J431" s="17" t="n">
+        <v>0.1165358</v>
+      </c>
+      <c r="K431" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L431" s="5">
+        <f>交易明細!K217</f>
+        <v/>
+      </c>
+      <c r="M431" s="16">
+        <f>M429</f>
+        <v/>
+      </c>
+      <c r="N431" s="2">
+        <f>N429</f>
+        <v/>
+      </c>
+      <c r="O431" s="16">
+        <f>O429</f>
+        <v/>
+      </c>
+      <c r="P431" s="4">
+        <f>交易明細!L217</f>
+        <v/>
+      </c>
+      <c r="Q431" s="10">
+        <f>IF(N431="已下單",O431*P431,0)</f>
+        <v/>
+      </c>
+      <c r="R431" s="10">
+        <f>R430+Q431</f>
+        <v/>
+      </c>
+      <c r="S431" s="16">
+        <f>S430-IF(N431="已下單",M431,0)</f>
+        <v/>
+      </c>
+      <c r="T431" s="16">
+        <f>R431-S431</f>
+        <v/>
+      </c>
+      <c r="U431" s="2">
+        <f>U430-IF(N431="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V431" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R431,0),MAX(V430,FLOOR(MAX(R431,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W431" s="10">
+        <f>MAX(W430,R431)</f>
+        <v/>
+      </c>
+      <c r="X431" s="4">
+        <f>IF(W431&gt;0,R431/W431-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y431" s="16">
+        <f>IF(R431&gt;0,S431*資金模擬!$B$7/R431,0)</f>
+        <v/>
+      </c>
+      <c r="Z431" s="2">
+        <f>IF(OR(Z430=1,R431&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="B432" s="7" t="n">
+        <v>46279.70833333334</v>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G432" s="17" t="n">
+        <v>0.20271</v>
+      </c>
+      <c r="H432" s="17" t="n">
+        <v>0.1966287</v>
+      </c>
+      <c r="I432" s="17" t="n">
+        <v>0.2128455</v>
+      </c>
+      <c r="J432" s="17" t="n"/>
+      <c r="K432" s="2" t="n"/>
+      <c r="L432" s="5" t="n"/>
+      <c r="M432" s="16">
+        <f>資金模擬!$B$5*V431</f>
+        <v/>
+      </c>
+      <c r="N432" s="2">
+        <f>IF(Z431=1,"已停止",IF(T431&gt;=M432,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O432" s="16">
+        <f>IF(N432="已下單",M432*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P432" s="4" t="n"/>
+      <c r="Q432" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R432" s="10">
+        <f>R431+Q432</f>
+        <v/>
+      </c>
+      <c r="S432" s="16">
+        <f>S431+IF(N432="已下單",M432,0)</f>
+        <v/>
+      </c>
+      <c r="T432" s="16">
+        <f>R432-S432</f>
+        <v/>
+      </c>
+      <c r="U432" s="2">
+        <f>U431+IF(N432="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V432" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R432,0),MAX(V431,FLOOR(MAX(R432,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W432" s="10">
+        <f>MAX(W431,R432)</f>
+        <v/>
+      </c>
+      <c r="X432" s="4">
+        <f>IF(W432&gt;0,R432/W432-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y432" s="16">
+        <f>IF(R432&gt;0,S432*資金模擬!$B$7/R432,0)</f>
+        <v/>
+      </c>
+      <c r="Z432" s="2">
+        <f>IF(OR(Z431=1,R432&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="B433" s="7" t="n">
+        <v>46279.75</v>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>FIL_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G433" s="17" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="H433" s="17" t="n">
+        <v>1.02588</v>
+      </c>
+      <c r="I433" s="17" t="n">
+        <v>0.9461999999999999</v>
+      </c>
+      <c r="J433" s="17" t="n">
+        <v>1.02588</v>
+      </c>
+      <c r="K433" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L433" s="5">
+        <f>交易明細!K214</f>
+        <v/>
+      </c>
+      <c r="M433" s="16">
+        <f>M426</f>
+        <v/>
+      </c>
+      <c r="N433" s="2">
+        <f>N426</f>
+        <v/>
+      </c>
+      <c r="O433" s="16">
+        <f>O426</f>
+        <v/>
+      </c>
+      <c r="P433" s="4">
+        <f>交易明細!L214</f>
+        <v/>
+      </c>
+      <c r="Q433" s="10">
+        <f>IF(N433="已下單",O433*P433,0)</f>
+        <v/>
+      </c>
+      <c r="R433" s="10">
+        <f>R432+Q433</f>
+        <v/>
+      </c>
+      <c r="S433" s="16">
+        <f>S432-IF(N433="已下單",M433,0)</f>
+        <v/>
+      </c>
+      <c r="T433" s="16">
+        <f>R433-S433</f>
+        <v/>
+      </c>
+      <c r="U433" s="2">
+        <f>U432-IF(N433="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V433" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R433,0),MAX(V432,FLOOR(MAX(R433,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W433" s="10">
+        <f>MAX(W432,R433)</f>
+        <v/>
+      </c>
+      <c r="X433" s="4">
+        <f>IF(W433&gt;0,R433/W433-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y433" s="16">
+        <f>IF(R433&gt;0,S433*資金模擬!$B$7/R433,0)</f>
+        <v/>
+      </c>
+      <c r="Z433" s="2">
+        <f>IF(OR(Z432=1,R433&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="B434" s="7" t="n">
+        <v>46279.75</v>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>LSK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G434" s="17" t="n">
+        <v>0.8768</v>
+      </c>
+      <c r="H434" s="17" t="n">
+        <v>0.850496</v>
+      </c>
+      <c r="I434" s="17" t="n">
+        <v>0.92064</v>
+      </c>
+      <c r="J434" s="17" t="n"/>
+      <c r="K434" s="2" t="n"/>
+      <c r="L434" s="5" t="n"/>
+      <c r="M434" s="16">
+        <f>資金模擬!$B$5*V433</f>
+        <v/>
+      </c>
+      <c r="N434" s="2">
+        <f>IF(Z433=1,"已停止",IF(T433&gt;=M434,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O434" s="16">
+        <f>IF(N434="已下單",M434*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P434" s="4" t="n"/>
+      <c r="Q434" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R434" s="10">
+        <f>R433+Q434</f>
+        <v/>
+      </c>
+      <c r="S434" s="16">
+        <f>S433+IF(N434="已下單",M434,0)</f>
+        <v/>
+      </c>
+      <c r="T434" s="16">
+        <f>R434-S434</f>
+        <v/>
+      </c>
+      <c r="U434" s="2">
+        <f>U433+IF(N434="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V434" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R434,0),MAX(V433,FLOOR(MAX(R434,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W434" s="10">
+        <f>MAX(W433,R434)</f>
+        <v/>
+      </c>
+      <c r="X434" s="4">
+        <f>IF(W434&gt;0,R434/W434-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y434" s="16">
+        <f>IF(R434&gt;0,S434*資金模擬!$B$7/R434,0)</f>
+        <v/>
+      </c>
+      <c r="Z434" s="2">
+        <f>IF(OR(Z433=1,R434&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>433</v>
+      </c>
+      <c r="B435" s="7" t="n">
+        <v>46279.79166666666</v>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>LSK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G435" s="17" t="n">
+        <v>0.8768</v>
+      </c>
+      <c r="H435" s="17" t="n">
+        <v>0.850496</v>
+      </c>
+      <c r="I435" s="17" t="n">
+        <v>0.92064</v>
+      </c>
+      <c r="J435" s="17" t="n">
+        <v>0.850496</v>
+      </c>
+      <c r="K435" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L435" s="5">
+        <f>交易明細!K219</f>
+        <v/>
+      </c>
+      <c r="M435" s="16">
+        <f>M434</f>
+        <v/>
+      </c>
+      <c r="N435" s="2">
+        <f>N434</f>
+        <v/>
+      </c>
+      <c r="O435" s="16">
+        <f>O434</f>
+        <v/>
+      </c>
+      <c r="P435" s="4">
+        <f>交易明細!L219</f>
+        <v/>
+      </c>
+      <c r="Q435" s="10">
+        <f>IF(N435="已下單",O435*P435,0)</f>
+        <v/>
+      </c>
+      <c r="R435" s="10">
+        <f>R434+Q435</f>
+        <v/>
+      </c>
+      <c r="S435" s="16">
+        <f>S434-IF(N435="已下單",M435,0)</f>
+        <v/>
+      </c>
+      <c r="T435" s="16">
+        <f>R435-S435</f>
+        <v/>
+      </c>
+      <c r="U435" s="2">
+        <f>U434-IF(N435="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V435" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R435,0),MAX(V434,FLOOR(MAX(R435,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W435" s="10">
+        <f>MAX(W434,R435)</f>
+        <v/>
+      </c>
+      <c r="X435" s="4">
+        <f>IF(W435&gt;0,R435/W435-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y435" s="16">
+        <f>IF(R435&gt;0,S435*資金模擬!$B$7/R435,0)</f>
+        <v/>
+      </c>
+      <c r="Z435" s="2">
+        <f>IF(OR(Z434=1,R435&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>434</v>
+      </c>
+      <c r="B436" s="7" t="n">
+        <v>46279.83333333334</v>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G436" s="17" t="n">
+        <v>0.20271</v>
+      </c>
+      <c r="H436" s="17" t="n">
+        <v>0.1966287</v>
+      </c>
+      <c r="I436" s="17" t="n">
+        <v>0.2128455</v>
+      </c>
+      <c r="J436" s="17" t="n">
+        <v>0.1966287</v>
+      </c>
+      <c r="K436" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L436" s="5">
+        <f>交易明細!K218</f>
+        <v/>
+      </c>
+      <c r="M436" s="16">
+        <f>M432</f>
+        <v/>
+      </c>
+      <c r="N436" s="2">
+        <f>N432</f>
+        <v/>
+      </c>
+      <c r="O436" s="16">
+        <f>O432</f>
+        <v/>
+      </c>
+      <c r="P436" s="4">
+        <f>交易明細!L218</f>
+        <v/>
+      </c>
+      <c r="Q436" s="10">
+        <f>IF(N436="已下單",O436*P436,0)</f>
+        <v/>
+      </c>
+      <c r="R436" s="10">
+        <f>R435+Q436</f>
+        <v/>
+      </c>
+      <c r="S436" s="16">
+        <f>S435-IF(N436="已下單",M436,0)</f>
+        <v/>
+      </c>
+      <c r="T436" s="16">
+        <f>R436-S436</f>
+        <v/>
+      </c>
+      <c r="U436" s="2">
+        <f>U435-IF(N436="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V436" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R436,0),MAX(V435,FLOOR(MAX(R436,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W436" s="10">
+        <f>MAX(W435,R436)</f>
+        <v/>
+      </c>
+      <c r="X436" s="4">
+        <f>IF(W436&gt;0,R436/W436-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y436" s="16">
+        <f>IF(R436&gt;0,S436*資金模擬!$B$7/R436,0)</f>
+        <v/>
+      </c>
+      <c r="Z436" s="2">
+        <f>IF(OR(Z435=1,R436&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="B437" s="7" t="n">
+        <v>46279.91666666666</v>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G437" s="17" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="H437" s="17" t="n">
+        <v>0.583083</v>
+      </c>
+      <c r="I437" s="17" t="n">
+        <v>0.537795</v>
+      </c>
+      <c r="J437" s="17" t="n">
+        <v>0.537795</v>
+      </c>
+      <c r="K437" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L437" s="5">
+        <f>交易明細!K216</f>
+        <v/>
+      </c>
+      <c r="M437" s="16">
+        <f>M428</f>
+        <v/>
+      </c>
+      <c r="N437" s="2">
+        <f>N428</f>
+        <v/>
+      </c>
+      <c r="O437" s="16">
+        <f>O428</f>
+        <v/>
+      </c>
+      <c r="P437" s="4">
+        <f>交易明細!L216</f>
+        <v/>
+      </c>
+      <c r="Q437" s="10">
+        <f>IF(N437="已下單",O437*P437,0)</f>
+        <v/>
+      </c>
+      <c r="R437" s="10">
+        <f>R436+Q437</f>
+        <v/>
+      </c>
+      <c r="S437" s="16">
+        <f>S436-IF(N437="已下單",M437,0)</f>
+        <v/>
+      </c>
+      <c r="T437" s="16">
+        <f>R437-S437</f>
+        <v/>
+      </c>
+      <c r="U437" s="2">
+        <f>U436-IF(N437="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V437" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R437,0),MAX(V436,FLOOR(MAX(R437,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W437" s="10">
+        <f>MAX(W436,R437)</f>
+        <v/>
+      </c>
+      <c r="X437" s="4">
+        <f>IF(W437&gt;0,R437/W437-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y437" s="16">
+        <f>IF(R437&gt;0,S437*資金模擬!$B$7/R437,0)</f>
+        <v/>
+      </c>
+      <c r="Z437" s="2">
+        <f>IF(OR(Z436=1,R437&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z424"/>
-  <conditionalFormatting sqref="K2:K424">
+  <autoFilter ref="A1:Z437"/>
+  <conditionalFormatting sqref="K2:K437">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -42649,7 +43929,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N424">
+  <conditionalFormatting sqref="N2:N437">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -42657,7 +43937,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q424">
+  <conditionalFormatting sqref="Q2:Q437">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -42722,7 +44002,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 14:23（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 22:10（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -42926,7 +44206,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$213),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$219),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -43091,7 +44371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC213"/>
+  <dimension ref="A1:AC219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -60757,10 +62037,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46279.58333333334</v>
+        <v>46279.91666666666</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.572</v>
+        <v>0.5776</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -60799,7 +62079,7 @@
         <v>0.02792413066385668</v>
       </c>
       <c r="T184" s="4" t="n">
-        <v>0.02388479100807861</v>
+        <v>0.02669476642079371</v>
       </c>
       <c r="U184" s="16" t="n">
         <v>1.01517167462681</v>
@@ -63545,14 +64825,14 @@
         <v>0.123648</v>
       </c>
       <c r="H213" s="7" t="n">
-        <v>46279.58333333334</v>
+        <v>46279.625</v>
       </c>
       <c r="I213" s="17" t="n">
-        <v>0.12095</v>
+        <v>0.123648</v>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K213" s="5">
@@ -63563,11 +64843,7 @@
         <f>IF(C213="做多",I213/E213-1,1-I213/E213)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M213" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M213" s="2" t="inlineStr"/>
       <c r="N213" s="4" t="n">
         <v>-0.02281968301385784</v>
       </c>
@@ -63587,7 +64863,7 @@
         <v>0.02734375</v>
       </c>
       <c r="T213" s="4" t="n">
-        <v>0.04611073369565211</v>
+        <v>0.05</v>
       </c>
       <c r="U213" s="16" t="n">
         <v>0.4761997968648705</v>
@@ -63618,9 +64894,585 @@
         <v/>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>FIL_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="n">
+        <v>46279.625</v>
+      </c>
+      <c r="E214" s="17" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="F214" s="17" t="n">
+        <v>1.02588</v>
+      </c>
+      <c r="G214" s="17" t="n">
+        <v>0.9461999999999999</v>
+      </c>
+      <c r="H214" s="7" t="n">
+        <v>46279.75</v>
+      </c>
+      <c r="I214" s="17" t="n">
+        <v>1.02588</v>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K214" s="5">
+        <f>(H214-D214)*24</f>
+        <v/>
+      </c>
+      <c r="L214" s="4">
+        <f>IF(C214="做多",I214/E214-1,1-I214/E214)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="4" t="n">
+        <v>0.03426791277258578</v>
+      </c>
+      <c r="O214" s="4" t="n">
+        <v>0.03100840294421877</v>
+      </c>
+      <c r="P214" s="4" t="n">
+        <v>0.04902838485438932</v>
+      </c>
+      <c r="Q214" s="19" t="n">
+        <v>135858.4000000001</v>
+      </c>
+      <c r="R214" s="19" t="n">
+        <v>2098980.9254</v>
+      </c>
+      <c r="S214" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T214" s="4" t="n">
+        <v>0.008032128514056214</v>
+      </c>
+      <c r="U214" s="16" t="n">
+        <v>0.6920262478472113</v>
+      </c>
+      <c r="V214" s="16" t="n">
+        <v>0.8000000000000019</v>
+      </c>
+      <c r="W214" s="4" t="n">
+        <v>0.2005207077768671</v>
+      </c>
+      <c r="X214" s="4" t="n">
+        <v>0.2266009852216748</v>
+      </c>
+      <c r="Y214" s="4" t="n">
+        <v>-0.0003170965301131368</v>
+      </c>
+      <c r="Z214" s="4" t="n">
+        <v>0.004886483600883285</v>
+      </c>
+      <c r="AA214" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB214" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC214" s="4">
+        <f>(AB214+2*參數!$B$7)/(AA214+AB214)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>LSK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="n">
+        <v>46279.66666666666</v>
+      </c>
+      <c r="E215" s="17" t="n">
+        <v>0.9222</v>
+      </c>
+      <c r="F215" s="17" t="n">
+        <v>0.9498660000000001</v>
+      </c>
+      <c r="G215" s="17" t="n">
+        <v>0.8760899999999999</v>
+      </c>
+      <c r="H215" s="7" t="n">
+        <v>46279.70833333334</v>
+      </c>
+      <c r="I215" s="17" t="n">
+        <v>0.9498660000000001</v>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K215" s="5">
+        <f>(H215-D215)*24</f>
+        <v/>
+      </c>
+      <c r="L215" s="4">
+        <f>IF(C215="做多",I215/E215-1,1-I215/E215)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="4" t="n">
+        <v>0.05261956397671508</v>
+      </c>
+      <c r="O215" s="4" t="n">
+        <v>0.1493080715481551</v>
+      </c>
+      <c r="P215" s="4" t="n">
+        <v>0.03846673573262471</v>
+      </c>
+      <c r="Q215" s="19" t="n">
+        <v>1655425</v>
+      </c>
+      <c r="R215" s="19" t="n">
+        <v>21319541.3692</v>
+      </c>
+      <c r="S215" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T215" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" s="16" t="n">
+        <v>0.845950323524046</v>
+      </c>
+      <c r="V215" s="16" t="n">
+        <v>0.5388418079096046</v>
+      </c>
+      <c r="W215" s="4" t="n">
+        <v>1.405320813771518</v>
+      </c>
+      <c r="X215" s="4" t="n">
+        <v>0.1928599146294141</v>
+      </c>
+      <c r="Y215" s="4" t="n">
+        <v>0.00386567862774867</v>
+      </c>
+      <c r="Z215" s="4" t="n">
+        <v>0.008051884035208845</v>
+      </c>
+      <c r="AA215" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB215" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC215" s="4">
+        <f>(AB215+2*參數!$B$7)/(AA215+AB215)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="n">
+        <v>46279.66666666666</v>
+      </c>
+      <c r="E216" s="17" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="F216" s="17" t="n">
+        <v>0.583083</v>
+      </c>
+      <c r="G216" s="17" t="n">
+        <v>0.537795</v>
+      </c>
+      <c r="H216" s="7" t="n">
+        <v>46279.91666666666</v>
+      </c>
+      <c r="I216" s="17" t="n">
+        <v>0.537795</v>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="K216" s="5">
+        <f>(H216-D216)*24</f>
+        <v/>
+      </c>
+      <c r="L216" s="4">
+        <f>IF(C216="做多",I216/E216-1,1-I216/E216)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="4" t="n">
+        <v>0.06110590440487362</v>
+      </c>
+      <c r="O216" s="4" t="n">
+        <v>0.03650424816235819</v>
+      </c>
+      <c r="P216" s="4" t="n">
+        <v>0.03450166295091561</v>
+      </c>
+      <c r="Q216" s="19" t="n">
+        <v>605808</v>
+      </c>
+      <c r="R216" s="19" t="n">
+        <v>1677042.4063</v>
+      </c>
+      <c r="S216" s="4" t="n">
+        <v>0.02402402402402393</v>
+      </c>
+      <c r="T216" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U216" s="16" t="n">
+        <v>1.433584458164734</v>
+      </c>
+      <c r="V216" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W216" s="4" t="n">
+        <v>-0.04372415470688384</v>
+      </c>
+      <c r="X216" s="4" t="n">
+        <v>-0.00158730158730136</v>
+      </c>
+      <c r="Y216" s="4" t="n">
+        <v>0.00386567862774867</v>
+      </c>
+      <c r="Z216" s="4" t="n">
+        <v>0.008051884035208845</v>
+      </c>
+      <c r="AA216" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB216" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC216" s="4">
+        <f>(AB216+2*參數!$B$7)/(AA216+AB216)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="n">
+        <v>46279.66666666666</v>
+      </c>
+      <c r="E217" s="17" t="n">
+        <v>0.12014</v>
+      </c>
+      <c r="F217" s="17" t="n">
+        <v>0.1165358</v>
+      </c>
+      <c r="G217" s="17" t="n">
+        <v>0.126147</v>
+      </c>
+      <c r="H217" s="7" t="n">
+        <v>46279.70833333334</v>
+      </c>
+      <c r="I217" s="17" t="n">
+        <v>0.1165358</v>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K217" s="5">
+        <f>(H217-D217)*24</f>
+        <v/>
+      </c>
+      <c r="L217" s="4">
+        <f>IF(C217="做多",I217/E217-1,1-I217/E217)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="4" t="n">
+        <v>-0.02094368837095595</v>
+      </c>
+      <c r="O217" s="4" t="n">
+        <v>0.05348945695792933</v>
+      </c>
+      <c r="P217" s="4" t="n">
+        <v>-0.008001056899156977</v>
+      </c>
+      <c r="Q217" s="19" t="n">
+        <v>-2286112</v>
+      </c>
+      <c r="R217" s="19" t="n">
+        <v>1877770.83223</v>
+      </c>
+      <c r="S217" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T217" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" s="16" t="n">
+        <v>0.6989090661339149</v>
+      </c>
+      <c r="V217" s="16" t="n">
+        <v>0.8567164179104492</v>
+      </c>
+      <c r="W217" s="4" t="n">
+        <v>0.01805490849945646</v>
+      </c>
+      <c r="X217" s="4" t="n">
+        <v>0.1567939359910163</v>
+      </c>
+      <c r="Y217" s="4" t="n">
+        <v>-0.00386567862774867</v>
+      </c>
+      <c r="Z217" s="4" t="n">
+        <v>-0.008051884035208845</v>
+      </c>
+      <c r="AA217" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB217" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC217" s="4">
+        <f>(AB217+2*參數!$B$7)/(AA217+AB217)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="n">
+        <v>46279.70833333334</v>
+      </c>
+      <c r="E218" s="17" t="n">
+        <v>0.20271</v>
+      </c>
+      <c r="F218" s="17" t="n">
+        <v>0.1966287</v>
+      </c>
+      <c r="G218" s="17" t="n">
+        <v>0.2128455</v>
+      </c>
+      <c r="H218" s="7" t="n">
+        <v>46279.83333333334</v>
+      </c>
+      <c r="I218" s="17" t="n">
+        <v>0.1966287</v>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K218" s="5">
+        <f>(H218-D218)*24</f>
+        <v/>
+      </c>
+      <c r="L218" s="4">
+        <f>IF(C218="做多",I218/E218-1,1-I218/E218)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="4" t="n">
+        <v>-0.0318097148588623</v>
+      </c>
+      <c r="O218" s="4" t="n">
+        <v>0.03549055706044232</v>
+      </c>
+      <c r="P218" s="4" t="n">
+        <v>-0.04754297474257441</v>
+      </c>
+      <c r="Q218" s="19" t="n">
+        <v>-887001</v>
+      </c>
+      <c r="R218" s="19" t="n">
+        <v>1992329.76383</v>
+      </c>
+      <c r="S218" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T218" s="4" t="n">
+        <v>0.02989492378274394</v>
+      </c>
+      <c r="U218" s="16" t="n">
+        <v>1.088276490112146</v>
+      </c>
+      <c r="V218" s="16" t="n">
+        <v>0.9719853836784399</v>
+      </c>
+      <c r="W218" s="4" t="n">
+        <v>0.1066100543059095</v>
+      </c>
+      <c r="X218" s="4" t="n">
+        <v>0.09846564376250833</v>
+      </c>
+      <c r="Y218" s="4" t="n">
+        <v>0.001980627866740581</v>
+      </c>
+      <c r="Z218" s="4" t="n">
+        <v>-0.005421194060191814</v>
+      </c>
+      <c r="AA218" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB218" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC218" s="4">
+        <f>(AB218+2*參數!$B$7)/(AA218+AB218)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>LSK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="n">
+        <v>46279.75</v>
+      </c>
+      <c r="E219" s="17" t="n">
+        <v>0.8768</v>
+      </c>
+      <c r="F219" s="17" t="n">
+        <v>0.850496</v>
+      </c>
+      <c r="G219" s="17" t="n">
+        <v>0.92064</v>
+      </c>
+      <c r="H219" s="7" t="n">
+        <v>46279.79166666666</v>
+      </c>
+      <c r="I219" s="17" t="n">
+        <v>0.850496</v>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K219" s="5">
+        <f>(H219-D219)*24</f>
+        <v/>
+      </c>
+      <c r="L219" s="4">
+        <f>IF(C219="做多",I219/E219-1,1-I219/E219)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="4" t="n">
+        <v>-0.09111640924639786</v>
+      </c>
+      <c r="O219" s="4" t="n">
+        <v>0.153993602113604</v>
+      </c>
+      <c r="P219" s="4" t="n">
+        <v>-0.01166100242914059</v>
+      </c>
+      <c r="Q219" s="19" t="n">
+        <v>-1081120</v>
+      </c>
+      <c r="R219" s="19" t="n">
+        <v>21256200.9232</v>
+      </c>
+      <c r="S219" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T219" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" s="16" t="n">
+        <v>0.8150563760825439</v>
+      </c>
+      <c r="V219" s="16" t="n">
+        <v>0.5871743486973944</v>
+      </c>
+      <c r="W219" s="4" t="n">
+        <v>-1.194463285037455</v>
+      </c>
+      <c r="X219" s="4" t="n">
+        <v>-0.1097329451968105</v>
+      </c>
+      <c r="Y219" s="4" t="n">
+        <v>-0.005263842038406796</v>
+      </c>
+      <c r="Z219" s="4" t="n">
+        <v>-0.009867322303158232</v>
+      </c>
+      <c r="AA219" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB219" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC219" s="4">
+        <f>(AB219+2*參數!$B$7)/(AA219+AB219)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC213"/>
-  <conditionalFormatting sqref="J2:J213">
+  <autoFilter ref="A1:AC219"/>
+  <conditionalFormatting sqref="J2:J219">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -63641,7 +65493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -63727,27 +65579,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -63755,19 +65607,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A2,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63778,27 +65630,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -63806,19 +65658,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A3,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63829,27 +65681,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -63857,19 +65709,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A4,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63880,27 +65732,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -63908,19 +65760,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A5,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63931,27 +65783,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -63959,19 +65811,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A6,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -63982,27 +65834,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -64010,19 +65862,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A7,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64033,27 +65885,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -64061,19 +65913,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A8,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64084,27 +65936,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -64112,19 +65964,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A9,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64135,27 +65987,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -64163,19 +66015,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A10,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64186,27 +66038,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -64214,19 +66066,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A11,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64237,27 +66089,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -64265,19 +66117,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A12,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64288,27 +66140,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -64316,19 +66168,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A13,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64339,27 +66191,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -64367,19 +66219,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A14,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64390,27 +66242,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -64418,19 +66270,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A15,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64441,27 +66293,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -64469,19 +66321,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A16,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64492,27 +66344,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -64520,19 +66372,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A17,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64543,27 +66395,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -64571,19 +66423,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A18,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64594,27 +66446,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -64622,19 +66474,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A19,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64645,27 +66497,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -64673,19 +66525,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A20,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64696,27 +66548,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -64724,19 +66576,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A21,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64747,27 +66599,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -64775,19 +66627,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A22,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64798,27 +66650,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -64826,19 +66678,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A23,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64849,27 +66701,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -64877,19 +66729,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A24,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64900,27 +66752,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -64928,19 +66780,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A25,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -64951,27 +66803,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -64979,19 +66831,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A26,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65002,27 +66854,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -65030,19 +66882,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A27,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65053,27 +66905,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -65081,19 +66933,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A28,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65104,27 +66956,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -65132,19 +66984,19 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A29,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65155,27 +67007,27 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -65183,19 +67035,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A30,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65206,27 +67058,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -65234,50 +67086,50 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A31,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SKYAI_USDT_PERP</t>
+          <t>LSK_USDT_PERP</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -65285,50 +67137,50 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A32,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>XMR_USDT_PERP</t>
+          <t>SKYAI_USDT_PERP</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -65336,50 +67188,50 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A33,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CRV_USDT_PERP</t>
+          <t>XMR_USDT_PERP</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -65387,50 +67239,50 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A34,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MAGMA_USDT_PERP</t>
+          <t>CRV_USDT_PERP</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -65438,50 +67290,50 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A35,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TRUMP_USDT_PERP</t>
+          <t>MAGMA_USDT_PERP</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -65489,50 +67341,50 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A36,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CHIP_USDT_PERP</t>
+          <t>TRUMP_USDT_PERP</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -65540,50 +67392,50 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A37,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PENGU_USDT_PERP</t>
+          <t>CHIP_USDT_PERP</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -65591,50 +67443,50 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A38,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FARTCOIN_USDT_PERP</t>
+          <t>PENGU_USDT_PERP</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -65642,50 +67494,50 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A39,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TRIA_USDT_PERP</t>
+          <t>FARTCOIN_USDT_PERP</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -65693,50 +67545,50 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A40,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ZEN_USDT_PERP</t>
+          <t>TRIA_USDT_PERP</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -65744,50 +67596,50 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A41,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TAO_USDT_PERP</t>
+          <t>ZEN_USDT_PERP</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -65795,50 +67647,50 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A42,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>KAS_USDT_PERP</t>
+          <t>TAO_USDT_PERP</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -65846,50 +67698,50 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A43,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CASHCAT_USDT_PERP</t>
+          <t>KAS_USDT_PERP</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -65897,50 +67749,50 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A44,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>INJ_USDT_PERP</t>
+          <t>CASHCAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -65948,50 +67800,50 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A45,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ICP_USDT_PERP</t>
+          <t>INJ_USDT_PERP</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -65999,50 +67851,50 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A46,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FF_USDT_PERP</t>
+          <t>ICP_USDT_PERP</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -66050,50 +67902,50 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A47,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>KAT_USDT_PERP</t>
+          <t>FF_USDT_PERP</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -66101,50 +67953,50 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A48,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MET_USDT_PERP</t>
+          <t>KAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -66152,50 +68004,50 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A49,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>BTW_USDT_PERP</t>
+          <t>MET_USDT_PERP</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$C$2:$C$213,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$C$2:$C$219,"做多")</f>
         <v/>
       </c>
       <c r="D50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$C$2:$C$213,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$C$2:$C$219,"做空")</f>
         <v/>
       </c>
       <c r="E50" s="2">
-        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"時間出場")</f>
+        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"時間出場")</f>
         <v/>
       </c>
       <c r="F50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"止盈")</f>
         <v/>
       </c>
       <c r="G50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"止損")</f>
         <v/>
       </c>
       <c r="H50" s="4">
@@ -66203,24 +68055,126 @@
         <v/>
       </c>
       <c r="I50" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J50" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$213,交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K50" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$213,交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$213,$A50,交易明細!$J$2:$J$213,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>BTW_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B51" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51)</f>
+        <v/>
+      </c>
+      <c r="C51" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$C$2:$C$219,"做多")</f>
+        <v/>
+      </c>
+      <c r="D51" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$C$2:$C$219,"做空")</f>
+        <v/>
+      </c>
+      <c r="E51" s="2">
+        <f>F51+G51+COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F51" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G51" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"止損")</f>
+        <v/>
+      </c>
+      <c r="H51" s="4">
+        <f>IFERROR(F51/E51,0)</f>
+        <v/>
+      </c>
+      <c r="I51" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J51" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K51" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L51" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>FIL_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B52" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52)</f>
+        <v/>
+      </c>
+      <c r="C52" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$C$2:$C$219,"做多")</f>
+        <v/>
+      </c>
+      <c r="D52" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$C$2:$C$219,"做空")</f>
+        <v/>
+      </c>
+      <c r="E52" s="2">
+        <f>F52+G52+COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F52" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G52" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"止損")</f>
+        <v/>
+      </c>
+      <c r="H52" s="4">
+        <f>IFERROR(F52/E52,0)</f>
+        <v/>
+      </c>
+      <c r="I52" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J52" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K52" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L52" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L50"/>
+  <autoFilter ref="A1:L52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -74239,11 +76193,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C443" s="2" t="inlineStr"/>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="17" t="n"/>
       <c r="F443" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$437</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$441</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$222</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$437</f>
+              <f>'資金明細'!$R$2:$R$441</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 22:10（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 03:26（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$219,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$222,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$J$2:$J$219,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$J$2:$J$222,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$J$2:$J$219,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$J$2:$J$222,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$J$2:$J$219,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$J$2:$J$222,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$219,"&lt;&gt;未平倉",交易明細!$L$2:$L$219,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$222,"&lt;&gt;未平倉",交易明細!$L$2:$L$222,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$B$2:$B$219,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$B$2:$B$222,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$219,"做多",交易明細!$J$2:$J$219,"&lt;&gt;未平倉",交易明細!$L$2:$L$219,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉",交易明細!$L$2:$L$222,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$B$2:$B$219,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$B$2:$B$222,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$219,"做空",交易明細!$J$2:$J$219,"&lt;&gt;未平倉",交易明細!$L$2:$L$219,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉",交易明細!$L$2:$L$222,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,56 +1085,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1143,50 +1143,50 @@
         <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -1195,93 +1195,93 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -1292,47 +1292,70 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1398,7 +1421,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R437</f>
+        <f>資金明細!R441</f>
         <v/>
       </c>
     </row>
@@ -1436,7 +1459,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$437)</f>
+        <f>MAX(資金明細!$R$2:$R$441)</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +1478,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$437)</f>
+        <f>MIN(資金明細!$R$2:$R$441)</f>
         <v/>
       </c>
     </row>
@@ -1475,7 +1498,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$437)</f>
+        <f>MIN(資金明細!$X$2:$X$441)</f>
         <v/>
       </c>
     </row>
@@ -1494,7 +1517,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$437,"進場",資金明細!$N$2:$N$437,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$441,"進場",資金明細!$N$2:$N$441,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1513,7 +1536,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$437,"進場",資金明細!$N$2:$N$437,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$441,"進場",資金明細!$N$2:$N$441,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1524,7 +1547,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$437,"出場",資金明細!$N$2:$N$437,"已下單",資金明細!$K$2:$K$437,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$441,"出場",資金明細!$N$2:$N$441,"已下單",資金明細!$K$2:$K$441,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1535,7 +1558,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$219),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$222),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1544,7 +1567,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$437,"出場",資金明細!$N$2:$N$437,"已下單",資金明細!$K$2:$K$437,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$441,"出場",資金明細!$N$2:$N$441,"已下單",資金明細!$K$2:$K$441,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1560,7 +1583,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$437,"出場",資金明細!$N$2:$N$437,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$441,"出場",資金明細!$N$2:$N$441,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1576,7 +1599,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$437)</f>
+        <f>MAX(資金明細!$U$2:$U$441)</f>
         <v/>
       </c>
     </row>
@@ -1592,7 +1615,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$437)</f>
+        <f>MAX(資金明細!$S$2:$S$441)</f>
         <v/>
       </c>
     </row>
@@ -1603,7 +1626,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V437</f>
+        <f>B5*資金明細!V441</f>
         <v/>
       </c>
     </row>
@@ -1614,7 +1637,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)</f>
+        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N440="已下單",資金明細!O440*交易明細!L221,0)+IF(資金明細!N441="已下單",資金明細!O441*交易明細!L222,0)</f>
         <v/>
       </c>
     </row>
@@ -1625,7 +1648,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$437)</f>
+        <f>MAX(資金明細!$Y$2:$Y$441)</f>
         <v/>
       </c>
     </row>
@@ -1647,7 +1670,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$437,MATCH(1,資金明細!$Z$2:$Z$437,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$441,MATCH(1,資金明細!$Z$2:$Z$441,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1658,7 +1681,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$437,"進場",資金明細!$N$2:$N$437,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$441,"進場",資金明細!$N$2:$N$441,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1723,7 +1746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z437"/>
+  <dimension ref="A1:Z441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -43919,9 +43942,390 @@
         <v/>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>436</v>
+      </c>
+      <c r="B438" s="7" t="n">
+        <v>46279.95833333334</v>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G438" s="17" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="H438" s="17" t="n">
+        <v>0.596782</v>
+      </c>
+      <c r="I438" s="17" t="n">
+        <v>0.55043</v>
+      </c>
+      <c r="J438" s="17" t="n"/>
+      <c r="K438" s="2" t="n"/>
+      <c r="L438" s="5" t="n"/>
+      <c r="M438" s="16">
+        <f>資金模擬!$B$5*V437</f>
+        <v/>
+      </c>
+      <c r="N438" s="2">
+        <f>IF(Z437=1,"已停止",IF(T437&gt;=M438,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O438" s="16">
+        <f>IF(N438="已下單",M438*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P438" s="4" t="n"/>
+      <c r="Q438" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R438" s="10">
+        <f>R437+Q438</f>
+        <v/>
+      </c>
+      <c r="S438" s="16">
+        <f>S437+IF(N438="已下單",M438,0)</f>
+        <v/>
+      </c>
+      <c r="T438" s="16">
+        <f>R438-S438</f>
+        <v/>
+      </c>
+      <c r="U438" s="2">
+        <f>U437+IF(N438="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V438" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R438,0),MAX(V437,FLOOR(MAX(R438,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W438" s="10">
+        <f>MAX(W437,R438)</f>
+        <v/>
+      </c>
+      <c r="X438" s="4">
+        <f>IF(W438&gt;0,R438/W438-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y438" s="16">
+        <f>IF(R438&gt;0,S438*資金模擬!$B$7/R438,0)</f>
+        <v/>
+      </c>
+      <c r="Z438" s="2">
+        <f>IF(OR(Z437=1,R438&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>437</v>
+      </c>
+      <c r="B439" s="7" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G439" s="17" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="H439" s="17" t="n">
+        <v>0.596782</v>
+      </c>
+      <c r="I439" s="17" t="n">
+        <v>0.55043</v>
+      </c>
+      <c r="J439" s="17" t="n">
+        <v>0.596782</v>
+      </c>
+      <c r="K439" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L439" s="5">
+        <f>交易明細!K220</f>
+        <v/>
+      </c>
+      <c r="M439" s="16">
+        <f>M438</f>
+        <v/>
+      </c>
+      <c r="N439" s="2">
+        <f>N438</f>
+        <v/>
+      </c>
+      <c r="O439" s="16">
+        <f>O438</f>
+        <v/>
+      </c>
+      <c r="P439" s="4">
+        <f>交易明細!L220</f>
+        <v/>
+      </c>
+      <c r="Q439" s="10">
+        <f>IF(N439="已下單",O439*P439,0)</f>
+        <v/>
+      </c>
+      <c r="R439" s="10">
+        <f>R438+Q439</f>
+        <v/>
+      </c>
+      <c r="S439" s="16">
+        <f>S438-IF(N439="已下單",M439,0)</f>
+        <v/>
+      </c>
+      <c r="T439" s="16">
+        <f>R439-S439</f>
+        <v/>
+      </c>
+      <c r="U439" s="2">
+        <f>U438-IF(N439="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V439" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R439,0),MAX(V438,FLOOR(MAX(R439,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W439" s="10">
+        <f>MAX(W438,R439)</f>
+        <v/>
+      </c>
+      <c r="X439" s="4">
+        <f>IF(W439&gt;0,R439/W439-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y439" s="16">
+        <f>IF(R439&gt;0,S439*資金模擬!$B$7/R439,0)</f>
+        <v/>
+      </c>
+      <c r="Z439" s="2">
+        <f>IF(OR(Z438=1,R439&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="B440" s="7" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>FIL_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G440" s="17" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="H440" s="17" t="n">
+        <v>0.92441</v>
+      </c>
+      <c r="I440" s="17" t="n">
+        <v>1.00065</v>
+      </c>
+      <c r="J440" s="17" t="n"/>
+      <c r="K440" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L440" s="5" t="n"/>
+      <c r="M440" s="16">
+        <f>資金模擬!$B$5*V439</f>
+        <v/>
+      </c>
+      <c r="N440" s="2">
+        <f>IF(Z439=1,"已停止",IF(T439&gt;=M440,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O440" s="16">
+        <f>IF(N440="已下單",M440*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P440" s="4" t="n"/>
+      <c r="Q440" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R440" s="10">
+        <f>R439+Q440</f>
+        <v/>
+      </c>
+      <c r="S440" s="16">
+        <f>S439+IF(N440="已下單",M440,0)</f>
+        <v/>
+      </c>
+      <c r="T440" s="16">
+        <f>R440-S440</f>
+        <v/>
+      </c>
+      <c r="U440" s="2">
+        <f>U439+IF(N440="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V440" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R440,0),MAX(V439,FLOOR(MAX(R440,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W440" s="10">
+        <f>MAX(W439,R440)</f>
+        <v/>
+      </c>
+      <c r="X440" s="4">
+        <f>IF(W440&gt;0,R440/W440-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y440" s="16">
+        <f>IF(R440&gt;0,S440*資金模擬!$B$7/R440,0)</f>
+        <v/>
+      </c>
+      <c r="Z440" s="2">
+        <f>IF(OR(Z439=1,R440&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="B441" s="7" t="n">
+        <v>46280.08333333334</v>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G441" s="17" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="H441" s="17" t="n">
+        <v>0.2217281</v>
+      </c>
+      <c r="I441" s="17" t="n">
+        <v>0.2045065</v>
+      </c>
+      <c r="J441" s="17" t="n"/>
+      <c r="K441" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L441" s="5" t="n"/>
+      <c r="M441" s="16">
+        <f>資金模擬!$B$5*V440</f>
+        <v/>
+      </c>
+      <c r="N441" s="2">
+        <f>IF(Z440=1,"已停止",IF(T440&gt;=M441,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O441" s="16">
+        <f>IF(N441="已下單",M441*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P441" s="4" t="n"/>
+      <c r="Q441" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R441" s="10">
+        <f>R440+Q441</f>
+        <v/>
+      </c>
+      <c r="S441" s="16">
+        <f>S440+IF(N441="已下單",M441,0)</f>
+        <v/>
+      </c>
+      <c r="T441" s="16">
+        <f>R441-S441</f>
+        <v/>
+      </c>
+      <c r="U441" s="2">
+        <f>U440+IF(N441="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V441" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R441,0),MAX(V440,FLOOR(MAX(R441,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W441" s="10">
+        <f>MAX(W440,R441)</f>
+        <v/>
+      </c>
+      <c r="X441" s="4">
+        <f>IF(W441&gt;0,R441/W441-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y441" s="16">
+        <f>IF(R441&gt;0,S441*資金模擬!$B$7/R441,0)</f>
+        <v/>
+      </c>
+      <c r="Z441" s="2">
+        <f>IF(OR(Z440=1,R441&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z437"/>
-  <conditionalFormatting sqref="K2:K437">
+  <autoFilter ref="A1:Z441"/>
+  <conditionalFormatting sqref="K2:K441">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -43929,7 +44333,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N437">
+  <conditionalFormatting sqref="N2:N441">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -43937,7 +44341,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q437">
+  <conditionalFormatting sqref="Q2:Q441">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -44002,7 +44406,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 22:10（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 03:26（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -44206,7 +44610,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$219),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$222),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -44371,7 +44775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC219"/>
+  <dimension ref="A1:AC222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -62037,10 +62441,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46279.91666666666</v>
+        <v>46280.125</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5776</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -65470,9 +65874,305 @@
         <v/>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D220" s="7" t="n">
+        <v>46279.95833333334</v>
+      </c>
+      <c r="E220" s="17" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="F220" s="17" t="n">
+        <v>0.596782</v>
+      </c>
+      <c r="G220" s="17" t="n">
+        <v>0.55043</v>
+      </c>
+      <c r="H220" s="7" t="n">
+        <v>46280</v>
+      </c>
+      <c r="I220" s="17" t="n">
+        <v>0.596782</v>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K220" s="5">
+        <f>(H220-D220)*24</f>
+        <v/>
+      </c>
+      <c r="L220" s="4">
+        <f>IF(C220="做多",I220/E220-1,1-I220/E220)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="4" t="n">
+        <v>0.05903856698958143</v>
+      </c>
+      <c r="O220" s="4" t="n">
+        <v>0.03743199201995348</v>
+      </c>
+      <c r="P220" s="4" t="n">
+        <v>0.05355990144468992</v>
+      </c>
+      <c r="Q220" s="19" t="n">
+        <v>593268</v>
+      </c>
+      <c r="R220" s="19" t="n">
+        <v>1954273.9413</v>
+      </c>
+      <c r="S220" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T220" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" s="16" t="n">
+        <v>2.871295855203831</v>
+      </c>
+      <c r="V220" s="16" t="n">
+        <v>0.7149028077753783</v>
+      </c>
+      <c r="W220" s="4" t="n">
+        <v>-0.01492237880773994</v>
+      </c>
+      <c r="X220" s="4" t="n">
+        <v>0.05556567680816182</v>
+      </c>
+      <c r="Y220" s="4" t="n">
+        <v>0.004340970985113657</v>
+      </c>
+      <c r="Z220" s="4" t="n">
+        <v>0.01218672904312879</v>
+      </c>
+      <c r="AA220" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB220" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC220" s="4">
+        <f>(AB220+2*參數!$B$7)/(AA220+AB220)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>FIL_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E221" s="17" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="F221" s="17" t="n">
+        <v>0.92441</v>
+      </c>
+      <c r="G221" s="17" t="n">
+        <v>1.00065</v>
+      </c>
+      <c r="H221" s="7" t="n">
+        <v>46280.125</v>
+      </c>
+      <c r="I221" s="17" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K221" s="5">
+        <f>(H221-D221)*24</f>
+        <v/>
+      </c>
+      <c r="L221" s="4">
+        <f>IF(C221="做多",I221/E221-1,1-I221/E221)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N221" s="4" t="n">
+        <v>-0.03248730964467006</v>
+      </c>
+      <c r="O221" s="4" t="n">
+        <v>0.03394151974486471</v>
+      </c>
+      <c r="P221" s="4" t="n">
+        <v>-0.03061743464550915</v>
+      </c>
+      <c r="Q221" s="19" t="n">
+        <v>-483300.7</v>
+      </c>
+      <c r="R221" s="19" t="n">
+        <v>2616142.9346</v>
+      </c>
+      <c r="S221" s="4" t="n">
+        <v>0.01364113326337879</v>
+      </c>
+      <c r="T221" s="4" t="n">
+        <v>0.01888772298006303</v>
+      </c>
+      <c r="U221" s="16" t="n">
+        <v>1.332575490212957</v>
+      </c>
+      <c r="V221" s="16" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="W221" s="4" t="n">
+        <v>-0.1257456736164431</v>
+      </c>
+      <c r="X221" s="4" t="n">
+        <v>-0.00527426160337563</v>
+      </c>
+      <c r="Y221" s="4" t="n">
+        <v>-0.0008244306713696137</v>
+      </c>
+      <c r="Z221" s="4" t="n">
+        <v>-0.01217989415057485</v>
+      </c>
+      <c r="AA221" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB221" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC221" s="4">
+        <f>(AB221+2*參數!$B$7)/(AA221+AB221)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="n">
+        <v>46280.08333333334</v>
+      </c>
+      <c r="E222" s="17" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="F222" s="17" t="n">
+        <v>0.2217281</v>
+      </c>
+      <c r="G222" s="17" t="n">
+        <v>0.2045065</v>
+      </c>
+      <c r="H222" s="7" t="n">
+        <v>46280.125</v>
+      </c>
+      <c r="I222" s="17" t="n">
+        <v>0.21967</v>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K222" s="5">
+        <f>(H222-D222)*24</f>
+        <v/>
+      </c>
+      <c r="L222" s="4">
+        <f>IF(C222="做多",I222/E222-1,1-I222/E222)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N222" s="4" t="n">
+        <v>0.07694231827505127</v>
+      </c>
+      <c r="O222" s="4" t="n">
+        <v>0.04129466730861369</v>
+      </c>
+      <c r="P222" s="4" t="n">
+        <v>0.04722917472386601</v>
+      </c>
+      <c r="Q222" s="19" t="n">
+        <v>57563</v>
+      </c>
+      <c r="R222" s="19" t="n">
+        <v>2142958.19727</v>
+      </c>
+      <c r="S222" s="4" t="n">
+        <v>0.02870813397129202</v>
+      </c>
+      <c r="T222" s="4" t="n">
+        <v>0.01337854787011661</v>
+      </c>
+      <c r="U222" s="16" t="n">
+        <v>2.695897368776979</v>
+      </c>
+      <c r="V222" s="16" t="n">
+        <v>0.8418891170431212</v>
+      </c>
+      <c r="W222" s="4" t="n">
+        <v>-0.03711019445659591</v>
+      </c>
+      <c r="X222" s="4" t="n">
+        <v>-0.01193372194427877</v>
+      </c>
+      <c r="Y222" s="4" t="n">
+        <v>0.002349919531133837</v>
+      </c>
+      <c r="Z222" s="4" t="n">
+        <v>0.01492736573107156</v>
+      </c>
+      <c r="AA222" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB222" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC222" s="4">
+        <f>(AB222+2*參數!$B$7)/(AA222+AB222)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC219"/>
-  <conditionalFormatting sqref="J2:J219">
+  <autoFilter ref="A1:AC222"/>
+  <conditionalFormatting sqref="J2:J222">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -65579,27 +66279,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -65607,19 +66307,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A2,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65630,27 +66330,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -65658,19 +66358,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A3,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65681,27 +66381,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -65709,19 +66409,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A4,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65732,27 +66432,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -65760,19 +66460,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A5,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65783,27 +66483,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -65811,19 +66511,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A6,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65834,27 +66534,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -65862,19 +66562,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A7,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65885,27 +66585,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -65913,19 +66613,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A8,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65936,27 +66636,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -65964,19 +66664,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A9,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -65987,27 +66687,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -66015,19 +66715,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A10,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66038,27 +66738,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -66066,19 +66766,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A11,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66089,27 +66789,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -66117,19 +66817,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A12,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66140,27 +66840,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -66168,19 +66868,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A13,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66191,27 +66891,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -66219,19 +66919,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A14,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66242,27 +66942,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -66270,19 +66970,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A15,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66293,27 +66993,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -66321,19 +67021,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A16,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66344,27 +67044,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -66372,19 +67072,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A17,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66395,27 +67095,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -66423,19 +67123,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A18,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66446,27 +67146,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -66474,19 +67174,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A19,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66497,27 +67197,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -66525,19 +67225,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A20,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66548,27 +67248,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -66576,19 +67276,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A21,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66599,27 +67299,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -66627,19 +67327,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A22,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66650,27 +67350,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -66678,19 +67378,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A23,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66701,27 +67401,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -66729,19 +67429,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A24,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66752,27 +67452,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -66780,19 +67480,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A25,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66803,27 +67503,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -66831,19 +67531,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A26,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66854,27 +67554,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -66882,19 +67582,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A27,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66905,27 +67605,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -66933,19 +67633,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A28,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66956,27 +67656,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -66984,19 +67684,19 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A29,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67007,27 +67707,27 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -67035,19 +67735,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A30,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67058,27 +67758,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -67086,50 +67786,50 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A31,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LSK_USDT_PERP</t>
+          <t>FIL_USDT_PERP</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -67137,50 +67837,50 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A32,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SKYAI_USDT_PERP</t>
+          <t>LSK_USDT_PERP</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -67188,50 +67888,50 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A33,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>XMR_USDT_PERP</t>
+          <t>SKYAI_USDT_PERP</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -67239,50 +67939,50 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A34,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CRV_USDT_PERP</t>
+          <t>XMR_USDT_PERP</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -67290,50 +67990,50 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A35,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MAGMA_USDT_PERP</t>
+          <t>CRV_USDT_PERP</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -67341,50 +68041,50 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A36,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TRUMP_USDT_PERP</t>
+          <t>MAGMA_USDT_PERP</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -67392,50 +68092,50 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A37,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CHIP_USDT_PERP</t>
+          <t>TRUMP_USDT_PERP</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -67443,50 +68143,50 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A38,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>PENGU_USDT_PERP</t>
+          <t>CHIP_USDT_PERP</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -67494,50 +68194,50 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A39,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FARTCOIN_USDT_PERP</t>
+          <t>PENGU_USDT_PERP</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -67545,50 +68245,50 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A40,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TRIA_USDT_PERP</t>
+          <t>FARTCOIN_USDT_PERP</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -67596,50 +68296,50 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A41,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ZEN_USDT_PERP</t>
+          <t>TRIA_USDT_PERP</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -67647,50 +68347,50 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A42,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TAO_USDT_PERP</t>
+          <t>ZEN_USDT_PERP</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -67698,50 +68398,50 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A43,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>KAS_USDT_PERP</t>
+          <t>TAO_USDT_PERP</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -67749,50 +68449,50 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A44,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>CASHCAT_USDT_PERP</t>
+          <t>KAS_USDT_PERP</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -67800,50 +68500,50 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A45,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>INJ_USDT_PERP</t>
+          <t>CASHCAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -67851,50 +68551,50 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A46,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ICP_USDT_PERP</t>
+          <t>INJ_USDT_PERP</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -67902,50 +68602,50 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A47,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FF_USDT_PERP</t>
+          <t>ICP_USDT_PERP</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -67953,50 +68653,50 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A48,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>KAT_USDT_PERP</t>
+          <t>FF_USDT_PERP</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -68004,50 +68704,50 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A49,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MET_USDT_PERP</t>
+          <t>KAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E50" s="2">
-        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H50" s="4">
@@ -68055,50 +68755,50 @@
         <v/>
       </c>
       <c r="I50" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J50" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K50" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A50,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>BTW_USDT_PERP</t>
+          <t>MET_USDT_PERP</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51)</f>
         <v/>
       </c>
       <c r="C51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E51" s="2">
-        <f>F51+G51+COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F51+G51+COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H51" s="4">
@@ -68106,50 +68806,50 @@
         <v/>
       </c>
       <c r="I51" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J51" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K51" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A51,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FIL_USDT_PERP</t>
+          <t>BTW_USDT_PERP</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52)</f>
         <v/>
       </c>
       <c r="C52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$C$2:$C$219,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$C$2:$C$222,"做多")</f>
         <v/>
       </c>
       <c r="D52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$C$2:$C$219,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$C$2:$C$222,"做空")</f>
         <v/>
       </c>
       <c r="E52" s="2">
-        <f>F52+G52+COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"時間出場")</f>
+        <f>F52+G52+COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"時間出場")</f>
         <v/>
       </c>
       <c r="F52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"止盈")</f>
         <v/>
       </c>
       <c r="G52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"止損")</f>
         <v/>
       </c>
       <c r="H52" s="4">
@@ -68157,19 +68857,19 @@
         <v/>
       </c>
       <c r="I52" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J52" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$219,交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K52" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$219,交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$219,$A52,交易明細!$J$2:$J$219,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -70937,7 +71637,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr"/>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" s="17" t="n"/>
       <c r="F151" s="17" t="n"/>
@@ -75347,7 +76051,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr"/>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="17" t="n"/>
       <c r="F396" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$441</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$443</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$223</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$441</f>
+              <f>'資金明細'!$R$2:$R$443</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 03:26（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 07:11（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$222,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$223,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$J$2:$J$222,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$J$2:$J$223,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$J$2:$J$222,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$J$2:$J$223,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$J$2:$J$222,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$J$2:$J$223,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$222,"&lt;&gt;未平倉",交易明細!$L$2:$L$222,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$223,"&lt;&gt;未平倉",交易明細!$L$2:$L$223,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$B$2:$B$222,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$B$2:$B$223,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$222,"做多",交易明細!$J$2:$J$222,"&lt;&gt;未平倉",交易明細!$L$2:$L$222,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉",交易明細!$L$2:$L$223,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$B$2:$B$222,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$B$2:$B$223,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$222,"做空",交易明細!$J$2:$J$222,"&lt;&gt;未平倉",交易明細!$L$2:$L$222,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉",交易明細!$L$2:$L$223,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,16 +1085,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -1103,61 +1103,61 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1166,50 +1166,50 @@
         <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -1218,93 +1218,93 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -1315,47 +1315,70 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1421,7 +1444,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R441</f>
+        <f>資金明細!R443</f>
         <v/>
       </c>
     </row>
@@ -1459,7 +1482,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$441)</f>
+        <f>MAX(資金明細!$R$2:$R$443)</f>
         <v/>
       </c>
     </row>
@@ -1478,7 +1501,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$441)</f>
+        <f>MIN(資金明細!$R$2:$R$443)</f>
         <v/>
       </c>
     </row>
@@ -1498,7 +1521,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$441)</f>
+        <f>MIN(資金明細!$X$2:$X$443)</f>
         <v/>
       </c>
     </row>
@@ -1517,7 +1540,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$441,"進場",資金明細!$N$2:$N$441,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$443,"進場",資金明細!$N$2:$N$443,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1536,7 +1559,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$441,"進場",資金明細!$N$2:$N$441,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$443,"進場",資金明細!$N$2:$N$443,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1547,7 +1570,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$441,"出場",資金明細!$N$2:$N$441,"已下單",資金明細!$K$2:$K$441,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$443,"出場",資金明細!$N$2:$N$443,"已下單",資金明細!$K$2:$K$443,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1581,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$222),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$223),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1567,7 +1590,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$441,"出場",資金明細!$N$2:$N$441,"已下單",資金明細!$K$2:$K$441,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$443,"出場",資金明細!$N$2:$N$443,"已下單",資金明細!$K$2:$K$443,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1583,7 +1606,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$441,"出場",資金明細!$N$2:$N$441,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$443,"出場",資金明細!$N$2:$N$443,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1599,7 +1622,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$441)</f>
+        <f>MAX(資金明細!$U$2:$U$443)</f>
         <v/>
       </c>
     </row>
@@ -1615,7 +1638,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$441)</f>
+        <f>MAX(資金明細!$S$2:$S$443)</f>
         <v/>
       </c>
     </row>
@@ -1626,7 +1649,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V441</f>
+        <f>B5*資金明細!V443</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1660,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N440="已下單",資金明細!O440*交易明細!L221,0)+IF(資金明細!N441="已下單",資金明細!O441*交易明細!L222,0)</f>
+        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N440="已下單",資金明細!O440*交易明細!L221,0)+IF(資金明細!N442="已下單",資金明細!O442*交易明細!L223,0)</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1671,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$441)</f>
+        <f>MAX(資金明細!$Y$2:$Y$443)</f>
         <v/>
       </c>
     </row>
@@ -1670,7 +1693,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$441,MATCH(1,資金明細!$Z$2:$Z$441,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$443,MATCH(1,資金明細!$Z$2:$Z$443,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1681,7 +1704,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$441,"進場",資金明細!$N$2:$N$441,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$443,"進場",資金明細!$N$2:$N$443,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z441"/>
+  <dimension ref="A1:Z443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -44264,11 +44287,7 @@
         <v>0.2045065</v>
       </c>
       <c r="J441" s="17" t="n"/>
-      <c r="K441" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K441" s="2" t="n"/>
       <c r="L441" s="5" t="n"/>
       <c r="M441" s="16">
         <f>資金模擬!$B$5*V440</f>
@@ -44323,9 +44342,206 @@
         <v/>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="B442" s="7" t="n">
+        <v>46280.16666666666</v>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>LIT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G442" s="17" t="n">
+        <v>4.538</v>
+      </c>
+      <c r="H442" s="17" t="n">
+        <v>4.67414</v>
+      </c>
+      <c r="I442" s="17" t="n">
+        <v>4.3111</v>
+      </c>
+      <c r="J442" s="17" t="n"/>
+      <c r="K442" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L442" s="5" t="n"/>
+      <c r="M442" s="16">
+        <f>資金模擬!$B$5*V441</f>
+        <v/>
+      </c>
+      <c r="N442" s="2">
+        <f>IF(Z441=1,"已停止",IF(T441&gt;=M442,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O442" s="16">
+        <f>IF(N442="已下單",M442*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P442" s="4" t="n"/>
+      <c r="Q442" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" s="10">
+        <f>R441+Q442</f>
+        <v/>
+      </c>
+      <c r="S442" s="16">
+        <f>S441+IF(N442="已下單",M442,0)</f>
+        <v/>
+      </c>
+      <c r="T442" s="16">
+        <f>R442-S442</f>
+        <v/>
+      </c>
+      <c r="U442" s="2">
+        <f>U441+IF(N442="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V442" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R442,0),MAX(V441,FLOOR(MAX(R442,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W442" s="10">
+        <f>MAX(W441,R442)</f>
+        <v/>
+      </c>
+      <c r="X442" s="4">
+        <f>IF(W442&gt;0,R442/W442-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y442" s="16">
+        <f>IF(R442&gt;0,S442*資金模擬!$B$7/R442,0)</f>
+        <v/>
+      </c>
+      <c r="Z442" s="2">
+        <f>IF(OR(Z441=1,R442&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="B443" s="7" t="n">
+        <v>46280.25</v>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G443" s="17" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="H443" s="17" t="n">
+        <v>0.2217281</v>
+      </c>
+      <c r="I443" s="17" t="n">
+        <v>0.2045065</v>
+      </c>
+      <c r="J443" s="17" t="n">
+        <v>0.2045065</v>
+      </c>
+      <c r="K443" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L443" s="5">
+        <f>交易明細!K222</f>
+        <v/>
+      </c>
+      <c r="M443" s="16">
+        <f>M441</f>
+        <v/>
+      </c>
+      <c r="N443" s="2">
+        <f>N441</f>
+        <v/>
+      </c>
+      <c r="O443" s="16">
+        <f>O441</f>
+        <v/>
+      </c>
+      <c r="P443" s="4">
+        <f>交易明細!L222</f>
+        <v/>
+      </c>
+      <c r="Q443" s="10">
+        <f>IF(N443="已下單",O443*P443,0)</f>
+        <v/>
+      </c>
+      <c r="R443" s="10">
+        <f>R442+Q443</f>
+        <v/>
+      </c>
+      <c r="S443" s="16">
+        <f>S442-IF(N443="已下單",M443,0)</f>
+        <v/>
+      </c>
+      <c r="T443" s="16">
+        <f>R443-S443</f>
+        <v/>
+      </c>
+      <c r="U443" s="2">
+        <f>U442-IF(N443="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V443" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R443,0),MAX(V442,FLOOR(MAX(R443,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W443" s="10">
+        <f>MAX(W442,R443)</f>
+        <v/>
+      </c>
+      <c r="X443" s="4">
+        <f>IF(W443&gt;0,R443/W443-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y443" s="16">
+        <f>IF(R443&gt;0,S443*資金模擬!$B$7/R443,0)</f>
+        <v/>
+      </c>
+      <c r="Z443" s="2">
+        <f>IF(OR(Z442=1,R443&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z441"/>
-  <conditionalFormatting sqref="K2:K441">
+  <autoFilter ref="A1:Z443"/>
+  <conditionalFormatting sqref="K2:K443">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -44333,7 +44549,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N441">
+  <conditionalFormatting sqref="N2:N443">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -44341,7 +44557,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q441">
+  <conditionalFormatting sqref="Q2:Q443">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -44406,7 +44622,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 03:26（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 07:11（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -44610,7 +44826,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$222),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$223),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -44775,7 +44991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC222"/>
+  <dimension ref="A1:AC223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -62441,10 +62657,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46280.125</v>
+        <v>46280.29166666666</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5736</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -62483,7 +62699,7 @@
         <v>0.02792413066385668</v>
       </c>
       <c r="T184" s="4" t="n">
-        <v>0.02669476642079371</v>
+        <v>0.0277485072005621</v>
       </c>
       <c r="U184" s="16" t="n">
         <v>1.01517167462681</v>
@@ -65997,10 +66213,10 @@
         <v>1.00065</v>
       </c>
       <c r="H221" s="7" t="n">
-        <v>46280.125</v>
+        <v>46280.29166666666</v>
       </c>
       <c r="I221" s="17" t="n">
-        <v>0.959</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
@@ -66036,7 +66252,7 @@
         <v>2616142.9346</v>
       </c>
       <c r="S221" s="4" t="n">
-        <v>0.01364113326337879</v>
+        <v>0.02203567681007335</v>
       </c>
       <c r="T221" s="4" t="n">
         <v>0.01888772298006303</v>
@@ -66097,14 +66313,14 @@
         <v>0.2045065</v>
       </c>
       <c r="H222" s="7" t="n">
-        <v>46280.125</v>
+        <v>46280.25</v>
       </c>
       <c r="I222" s="17" t="n">
-        <v>0.21967</v>
+        <v>0.2045065</v>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K222" s="5">
@@ -66115,11 +66331,7 @@
         <f>IF(C222="做多",I222/E222-1,1-I222/E222)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M222" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M222" s="2" t="inlineStr"/>
       <c r="N222" s="4" t="n">
         <v>0.07694231827505127</v>
       </c>
@@ -66139,7 +66351,7 @@
         <v>0.02870813397129202</v>
       </c>
       <c r="T222" s="4" t="n">
-        <v>0.01337854787011661</v>
+        <v>0.05</v>
       </c>
       <c r="U222" s="16" t="n">
         <v>2.695897368776979</v>
@@ -66170,9 +66382,109 @@
         <v/>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>LIT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="n">
+        <v>46280.16666666666</v>
+      </c>
+      <c r="E223" s="17" t="n">
+        <v>4.538</v>
+      </c>
+      <c r="F223" s="17" t="n">
+        <v>4.67414</v>
+      </c>
+      <c r="G223" s="17" t="n">
+        <v>4.3111</v>
+      </c>
+      <c r="H223" s="7" t="n">
+        <v>46280.29166666666</v>
+      </c>
+      <c r="I223" s="17" t="n">
+        <v>4.449</v>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K223" s="5">
+        <f>(H223-D223)*24</f>
+        <v/>
+      </c>
+      <c r="L223" s="4">
+        <f>IF(C223="做多",I223/E223-1,1-I223/E223)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N223" s="4" t="n">
+        <v>0.02437923250564356</v>
+      </c>
+      <c r="O223" s="4" t="n">
+        <v>0.02074968406070711</v>
+      </c>
+      <c r="P223" s="4" t="n">
+        <v>0.01550786582227492</v>
+      </c>
+      <c r="Q223" s="19" t="n">
+        <v>44747.19999999972</v>
+      </c>
+      <c r="R223" s="19" t="n">
+        <v>3149491.7076</v>
+      </c>
+      <c r="S223" s="4" t="n">
+        <v>0.0202732481269281</v>
+      </c>
+      <c r="T223" s="4" t="n">
+        <v>0.02578228294402818</v>
+      </c>
+      <c r="U223" s="16" t="n">
+        <v>1.101212313974368</v>
+      </c>
+      <c r="V223" s="16" t="n">
+        <v>0.9854014598540163</v>
+      </c>
+      <c r="W223" s="4" t="n">
+        <v>0.03869588504305388</v>
+      </c>
+      <c r="X223" s="4" t="n">
+        <v>0.07919143876337698</v>
+      </c>
+      <c r="Y223" s="4" t="n">
+        <v>-0.003054879219244189</v>
+      </c>
+      <c r="Z223" s="4" t="n">
+        <v>0.01231999729168809</v>
+      </c>
+      <c r="AA223" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB223" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC223" s="4">
+        <f>(AB223+2*參數!$B$7)/(AA223+AB223)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC222"/>
-  <conditionalFormatting sqref="J2:J222">
+  <autoFilter ref="A1:AC223"/>
+  <conditionalFormatting sqref="J2:J223">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -66279,27 +66591,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -66307,19 +66619,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A2,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66330,27 +66642,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -66358,19 +66670,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A3,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66381,27 +66693,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -66409,19 +66721,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A4,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66432,27 +66744,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -66460,50 +66772,50 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A5,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MARSCOIN_USDT_PERP</t>
+          <t>LIT_USDT_PERP</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -66511,50 +66823,50 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A6,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BULLA_USDT_PERP</t>
+          <t>MARSCOIN_USDT_PERP</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -66562,50 +66874,50 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A7,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HEMI_USDT_PERP</t>
+          <t>BULLA_USDT_PERP</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -66613,50 +66925,50 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A8,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LIT_USDT_PERP</t>
+          <t>HEMI_USDT_PERP</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -66664,19 +66976,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A9,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66687,27 +66999,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -66715,19 +67027,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A10,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66738,27 +67050,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -66766,19 +67078,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A11,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66789,27 +67101,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -66817,19 +67129,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A12,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66840,27 +67152,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -66868,19 +67180,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A13,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66891,27 +67203,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -66919,19 +67231,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A14,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66942,27 +67254,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -66970,19 +67282,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A15,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66993,27 +67305,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -67021,19 +67333,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A16,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67044,27 +67356,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -67072,19 +67384,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A17,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67095,27 +67407,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -67123,19 +67435,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A18,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67146,27 +67458,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -67174,19 +67486,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A19,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67197,27 +67509,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -67225,19 +67537,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A20,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67248,27 +67560,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -67276,19 +67588,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A21,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67299,27 +67611,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -67327,19 +67639,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A22,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67350,27 +67662,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -67378,19 +67690,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A23,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67401,27 +67713,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -67429,19 +67741,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A24,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67452,27 +67764,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -67480,19 +67792,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A25,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67503,27 +67815,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -67531,19 +67843,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A26,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67554,27 +67866,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -67582,19 +67894,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A27,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67605,27 +67917,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -67633,19 +67945,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A28,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67656,27 +67968,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -67684,19 +67996,19 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A29,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67707,27 +68019,27 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -67735,19 +68047,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A30,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67758,27 +68070,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -67786,19 +68098,19 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A31,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67809,27 +68121,27 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -67837,19 +68149,19 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A32,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67860,27 +68172,27 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -67888,19 +68200,19 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A33,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67911,27 +68223,27 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -67939,19 +68251,19 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A34,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67962,27 +68274,27 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -67990,19 +68302,19 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A35,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68013,27 +68325,27 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -68041,19 +68353,19 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A36,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68064,27 +68376,27 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -68092,19 +68404,19 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A37,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68115,27 +68427,27 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -68143,19 +68455,19 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A38,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68166,27 +68478,27 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -68194,19 +68506,19 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A39,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68217,27 +68529,27 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -68245,19 +68557,19 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A40,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68268,27 +68580,27 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -68296,19 +68608,19 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A41,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68319,27 +68631,27 @@
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -68347,19 +68659,19 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A42,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68370,27 +68682,27 @@
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -68398,19 +68710,19 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A43,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68421,27 +68733,27 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -68449,19 +68761,19 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A44,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68472,27 +68784,27 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -68500,19 +68812,19 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A45,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68523,27 +68835,27 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -68551,19 +68863,19 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A46,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68574,27 +68886,27 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -68602,19 +68914,19 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A47,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68625,27 +68937,27 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -68653,19 +68965,19 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A48,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68676,27 +68988,27 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -68704,19 +69016,19 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A49,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68727,27 +69039,27 @@
         </is>
       </c>
       <c r="B50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E50" s="2">
-        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H50" s="4">
@@ -68755,19 +69067,19 @@
         <v/>
       </c>
       <c r="I50" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J50" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K50" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A50,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68778,27 +69090,27 @@
         </is>
       </c>
       <c r="B51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51)</f>
         <v/>
       </c>
       <c r="C51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E51" s="2">
-        <f>F51+G51+COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F51+G51+COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H51" s="4">
@@ -68806,19 +69118,19 @@
         <v/>
       </c>
       <c r="I51" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J51" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K51" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A51,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68829,27 +69141,27 @@
         </is>
       </c>
       <c r="B52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52)</f>
         <v/>
       </c>
       <c r="C52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$C$2:$C$222,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$C$2:$C$223,"做多")</f>
         <v/>
       </c>
       <c r="D52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$C$2:$C$222,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$C$2:$C$223,"做空")</f>
         <v/>
       </c>
       <c r="E52" s="2">
-        <f>F52+G52+COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"時間出場")</f>
+        <f>F52+G52+COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"時間出場")</f>
         <v/>
       </c>
       <c r="F52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"止盈")</f>
         <v/>
       </c>
       <c r="G52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"止損")</f>
         <v/>
       </c>
       <c r="H52" s="4">
@@ -68857,19 +69169,19 @@
         <v/>
       </c>
       <c r="I52" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J52" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$222,交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K52" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$222,交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$222,$A52,交易明細!$J$2:$J$222,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -72847,7 +73159,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr"/>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D218" s="2" t="n"/>
       <c r="E218" s="17" t="n"/>
       <c r="F218" s="17" t="n"/>
@@ -76051,11 +76367,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C396" s="2" t="inlineStr"/>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="17" t="n"/>
       <c r="F396" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,7 +17,7 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$443</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$444</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$223</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$443</f>
+              <f>'資金明細'!$R$2:$R$444</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 07:11（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 09:33（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,16 +1085,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -1103,21 +1103,21 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -1126,61 +1126,61 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1189,50 +1189,50 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
@@ -1241,93 +1241,93 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -1338,47 +1338,70 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1444,7 +1467,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R443</f>
+        <f>資金明細!R444</f>
         <v/>
       </c>
     </row>
@@ -1482,7 +1505,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$443)</f>
+        <f>MAX(資金明細!$R$2:$R$444)</f>
         <v/>
       </c>
     </row>
@@ -1501,7 +1524,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$443)</f>
+        <f>MIN(資金明細!$R$2:$R$444)</f>
         <v/>
       </c>
     </row>
@@ -1521,7 +1544,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$443)</f>
+        <f>MIN(資金明細!$X$2:$X$444)</f>
         <v/>
       </c>
     </row>
@@ -1540,7 +1563,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$443,"進場",資金明細!$N$2:$N$443,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$444,"進場",資金明細!$N$2:$N$444,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1559,7 +1582,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$443,"進場",資金明細!$N$2:$N$443,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$444,"進場",資金明細!$N$2:$N$444,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1570,7 +1593,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$443,"出場",資金明細!$N$2:$N$443,"已下單",資金明細!$K$2:$K$443,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$444,"出場",資金明細!$N$2:$N$444,"已下單",資金明細!$K$2:$K$444,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1590,7 +1613,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$443,"出場",資金明細!$N$2:$N$443,"已下單",資金明細!$K$2:$K$443,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$444,"出場",資金明細!$N$2:$N$444,"已下單",資金明細!$K$2:$K$444,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1606,7 +1629,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$443,"出場",資金明細!$N$2:$N$443,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$444,"出場",資金明細!$N$2:$N$444,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1622,7 +1645,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$443)</f>
+        <f>MAX(資金明細!$U$2:$U$444)</f>
         <v/>
       </c>
     </row>
@@ -1638,7 +1661,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$443)</f>
+        <f>MAX(資金明細!$S$2:$S$444)</f>
         <v/>
       </c>
     </row>
@@ -1649,7 +1672,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V443</f>
+        <f>B5*資金明細!V444</f>
         <v/>
       </c>
     </row>
@@ -1660,7 +1683,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N440="已下單",資金明細!O440*交易明細!L221,0)+IF(資金明細!N442="已下單",資金明細!O442*交易明細!L223,0)</f>
+        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N442="已下單",資金明細!O442*交易明細!L223,0)</f>
         <v/>
       </c>
     </row>
@@ -1671,7 +1694,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$443)</f>
+        <f>MAX(資金明細!$Y$2:$Y$444)</f>
         <v/>
       </c>
     </row>
@@ -1693,7 +1716,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$443,MATCH(1,資金明細!$Z$2:$Z$443,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$444,MATCH(1,資金明細!$Z$2:$Z$444,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1704,7 +1727,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$443,"進場",資金明細!$N$2:$N$443,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$444,"進場",資金明細!$N$2:$N$444,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1769,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z443"/>
+  <dimension ref="A1:Z444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -44193,11 +44216,7 @@
         <v>1.00065</v>
       </c>
       <c r="J440" s="17" t="n"/>
-      <c r="K440" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K440" s="2" t="n"/>
       <c r="L440" s="5" t="n"/>
       <c r="M440" s="16">
         <f>資金模擬!$B$5*V439</f>
@@ -44539,9 +44558,112 @@
         <v/>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="B444" s="7" t="n">
+        <v>46280.375</v>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>FIL_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G444" s="17" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="H444" s="17" t="n">
+        <v>0.92441</v>
+      </c>
+      <c r="I444" s="17" t="n">
+        <v>1.00065</v>
+      </c>
+      <c r="J444" s="17" t="n">
+        <v>0.92441</v>
+      </c>
+      <c r="K444" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L444" s="5">
+        <f>交易明細!K221</f>
+        <v/>
+      </c>
+      <c r="M444" s="16">
+        <f>M440</f>
+        <v/>
+      </c>
+      <c r="N444" s="2">
+        <f>N440</f>
+        <v/>
+      </c>
+      <c r="O444" s="16">
+        <f>O440</f>
+        <v/>
+      </c>
+      <c r="P444" s="4">
+        <f>交易明細!L221</f>
+        <v/>
+      </c>
+      <c r="Q444" s="10">
+        <f>IF(N444="已下單",O444*P444,0)</f>
+        <v/>
+      </c>
+      <c r="R444" s="10">
+        <f>R443+Q444</f>
+        <v/>
+      </c>
+      <c r="S444" s="16">
+        <f>S443-IF(N444="已下單",M444,0)</f>
+        <v/>
+      </c>
+      <c r="T444" s="16">
+        <f>R444-S444</f>
+        <v/>
+      </c>
+      <c r="U444" s="2">
+        <f>U443-IF(N444="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V444" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R444,0),MAX(V443,FLOOR(MAX(R444,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W444" s="10">
+        <f>MAX(W443,R444)</f>
+        <v/>
+      </c>
+      <c r="X444" s="4">
+        <f>IF(W444&gt;0,R444/W444-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y444" s="16">
+        <f>IF(R444&gt;0,S444*資金模擬!$B$7/R444,0)</f>
+        <v/>
+      </c>
+      <c r="Z444" s="2">
+        <f>IF(OR(Z443=1,R444&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z443"/>
-  <conditionalFormatting sqref="K2:K443">
+  <autoFilter ref="A1:Z444"/>
+  <conditionalFormatting sqref="K2:K444">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -44549,7 +44671,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N443">
+  <conditionalFormatting sqref="N2:N444">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -44557,7 +44679,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q443">
+  <conditionalFormatting sqref="Q2:Q444">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -44622,7 +44744,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 07:11（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 09:33（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -62657,10 +62779,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46280.29166666666</v>
+        <v>46280.375</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5736</v>
+        <v>0.5656</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -66213,14 +66335,14 @@
         <v>1.00065</v>
       </c>
       <c r="H221" s="7" t="n">
-        <v>46280.29166666666</v>
+        <v>46280.375</v>
       </c>
       <c r="I221" s="17" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.92441</v>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K221" s="5">
@@ -66231,11 +66353,7 @@
         <f>IF(C221="做多",I221/E221-1,1-I221/E221)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M221" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M221" s="2" t="inlineStr"/>
       <c r="N221" s="4" t="n">
         <v>-0.03248730964467006</v>
       </c>
@@ -66252,7 +66370,7 @@
         <v>2616142.9346</v>
       </c>
       <c r="S221" s="4" t="n">
-        <v>0.02203567681007335</v>
+        <v>0.03</v>
       </c>
       <c r="T221" s="4" t="n">
         <v>0.01888772298006303</v>
@@ -66409,10 +66527,10 @@
         <v>4.3111</v>
       </c>
       <c r="H223" s="7" t="n">
-        <v>46280.29166666666</v>
+        <v>46280.375</v>
       </c>
       <c r="I223" s="17" t="n">
-        <v>4.449</v>
+        <v>4.379</v>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
@@ -66451,7 +66569,7 @@
         <v>0.0202732481269281</v>
       </c>
       <c r="T223" s="4" t="n">
-        <v>0.02578228294402818</v>
+        <v>0.03657999118554434</v>
       </c>
       <c r="U223" s="16" t="n">
         <v>1.101212313974368</v>
@@ -71949,11 +72067,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C151" s="2" t="inlineStr"/>
       <c r="D151" s="2" t="n"/>
       <c r="E151" s="17" t="n"/>
       <c r="F151" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$444</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$445</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$444</f>
+              <f>'資金明細'!$R$2:$R$445</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 09:33（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 11:28（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$223,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$224,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$J$2:$J$223,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$J$2:$J$224,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$J$2:$J$223,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$J$2:$J$224,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$J$2:$J$223,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$J$2:$J$224,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$223,"&lt;&gt;未平倉",交易明細!$L$2:$L$223,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$224,"&lt;&gt;未平倉",交易明細!$L$2:$L$224,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$B$2:$B$223,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$B$2:$B$224,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$223,"做多",交易明細!$J$2:$J$223,"&lt;&gt;未平倉",交易明細!$L$2:$L$223,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉",交易明細!$L$2:$L$224,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$B$2:$B$223,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$B$2:$B$224,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$223,"做空",交易明細!$J$2:$J$223,"&lt;&gt;未平倉",交易明細!$L$2:$L$223,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉",交易明細!$L$2:$L$224,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,39 +1085,39 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -1126,21 +1126,21 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -1149,61 +1149,61 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1212,50 +1212,50 @@
         <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1264,93 +1264,93 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1361,47 +1361,70 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1467,7 +1490,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R444</f>
+        <f>資金明細!R445</f>
         <v/>
       </c>
     </row>
@@ -1505,7 +1528,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$444)</f>
+        <f>MAX(資金明細!$R$2:$R$445)</f>
         <v/>
       </c>
     </row>
@@ -1524,7 +1547,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$444)</f>
+        <f>MIN(資金明細!$R$2:$R$445)</f>
         <v/>
       </c>
     </row>
@@ -1544,7 +1567,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$444)</f>
+        <f>MIN(資金明細!$X$2:$X$445)</f>
         <v/>
       </c>
     </row>
@@ -1555,7 +1578,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -1563,7 +1586,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$444,"進場",資金明細!$N$2:$N$444,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$445,"進場",資金明細!$N$2:$N$445,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1582,7 +1605,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$444,"進場",資金明細!$N$2:$N$444,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$445,"進場",資金明細!$N$2:$N$445,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1593,7 +1616,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$444,"出場",資金明細!$N$2:$N$444,"已下單",資金明細!$K$2:$K$444,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$445,"出場",資金明細!$N$2:$N$445,"已下單",資金明細!$K$2:$K$445,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1604,7 +1627,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$223),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$224),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1613,7 +1636,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$444,"出場",資金明細!$N$2:$N$444,"已下單",資金明細!$K$2:$K$444,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$445,"出場",資金明細!$N$2:$N$445,"已下單",資金明細!$K$2:$K$445,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1629,7 +1652,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$444,"出場",資金明細!$N$2:$N$444,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$445,"出場",資金明細!$N$2:$N$445,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1645,7 +1668,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$444)</f>
+        <f>MAX(資金明細!$U$2:$U$445)</f>
         <v/>
       </c>
     </row>
@@ -1661,7 +1684,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$444)</f>
+        <f>MAX(資金明細!$S$2:$S$445)</f>
         <v/>
       </c>
     </row>
@@ -1672,7 +1695,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V444</f>
+        <f>B5*資金明細!V445</f>
         <v/>
       </c>
     </row>
@@ -1683,7 +1706,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N442="已下單",資金明細!O442*交易明細!L223,0)</f>
+        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N442="已下單",資金明細!O442*交易明細!L223,0)+IF(資金明細!N445="已下單",資金明細!O445*交易明細!L224,0)</f>
         <v/>
       </c>
     </row>
@@ -1694,7 +1717,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$444)</f>
+        <f>MAX(資金明細!$Y$2:$Y$445)</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1739,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$444,MATCH(1,資金明細!$Z$2:$Z$444,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$445,MATCH(1,資金明細!$Z$2:$Z$445,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1727,7 +1750,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$444,"進場",資金明細!$N$2:$N$444,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$445,"進場",資金明細!$N$2:$N$445,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1792,7 +1815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z444"/>
+  <dimension ref="A1:Z445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -44661,9 +44684,103 @@
         <v/>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="B445" s="7" t="n">
+        <v>46280.45833333334</v>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G445" s="17" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="H445" s="17" t="n">
+        <v>0.109125</v>
+      </c>
+      <c r="I445" s="17" t="n">
+        <v>0.118125</v>
+      </c>
+      <c r="J445" s="17" t="n"/>
+      <c r="K445" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L445" s="5" t="n"/>
+      <c r="M445" s="16">
+        <f>資金模擬!$B$5*V444</f>
+        <v/>
+      </c>
+      <c r="N445" s="2">
+        <f>IF(Z444=1,"已停止",IF(T444&gt;=M445,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O445" s="16">
+        <f>IF(N445="已下單",M445*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P445" s="4" t="n"/>
+      <c r="Q445" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R445" s="10">
+        <f>R444+Q445</f>
+        <v/>
+      </c>
+      <c r="S445" s="16">
+        <f>S444+IF(N445="已下單",M445,0)</f>
+        <v/>
+      </c>
+      <c r="T445" s="16">
+        <f>R445-S445</f>
+        <v/>
+      </c>
+      <c r="U445" s="2">
+        <f>U444+IF(N445="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V445" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R445,0),MAX(V444,FLOOR(MAX(R445,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W445" s="10">
+        <f>MAX(W444,R445)</f>
+        <v/>
+      </c>
+      <c r="X445" s="4">
+        <f>IF(W445&gt;0,R445/W445-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y445" s="16">
+        <f>IF(R445&gt;0,S445*資金模擬!$B$7/R445,0)</f>
+        <v/>
+      </c>
+      <c r="Z445" s="2">
+        <f>IF(OR(Z444=1,R445&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z444"/>
-  <conditionalFormatting sqref="K2:K444">
+  <autoFilter ref="A1:Z445"/>
+  <conditionalFormatting sqref="K2:K445">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -44671,7 +44788,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N444">
+  <conditionalFormatting sqref="N2:N445">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -44679,7 +44796,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q444">
+  <conditionalFormatting sqref="Q2:Q445">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -44744,7 +44861,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 09:33（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 11:28（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -44936,7 +45053,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1M/5M/15M 依序判斷</t>
+          <t>5M/15M/30M 依序判斷</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
@@ -44948,7 +45065,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$223),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$224),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -45113,7 +45230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC223"/>
+  <dimension ref="A1:AC224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -62779,10 +62896,10 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46280.375</v>
+        <v>46280.45833333334</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5656</v>
+        <v>0.5621</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -66527,10 +66644,10 @@
         <v>4.3111</v>
       </c>
       <c r="H223" s="7" t="n">
-        <v>46280.375</v>
+        <v>46280.45833333334</v>
       </c>
       <c r="I223" s="17" t="n">
-        <v>4.379</v>
+        <v>4.36</v>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
@@ -66569,7 +66686,7 @@
         <v>0.0202732481269281</v>
       </c>
       <c r="T223" s="4" t="n">
-        <v>0.03657999118554434</v>
+        <v>0.04186866460996042</v>
       </c>
       <c r="U223" s="16" t="n">
         <v>1.101212313974368</v>
@@ -66600,9 +66717,109 @@
         <v/>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="n">
+        <v>46280.45833333334</v>
+      </c>
+      <c r="E224" s="17" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="F224" s="17" t="n">
+        <v>0.109125</v>
+      </c>
+      <c r="G224" s="17" t="n">
+        <v>0.118125</v>
+      </c>
+      <c r="H224" s="7" t="n">
+        <v>46280.45833333334</v>
+      </c>
+      <c r="I224" s="17" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K224" s="5">
+        <f>(H224-D224)*24</f>
+        <v/>
+      </c>
+      <c r="L224" s="4">
+        <f>IF(C224="做多",I224/E224-1,1-I224/E224)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N224" s="4" t="n">
+        <v>-0.05794674258918098</v>
+      </c>
+      <c r="O224" s="4" t="n">
+        <v>0.05103412800415014</v>
+      </c>
+      <c r="P224" s="4" t="n">
+        <v>-0.03928266438941086</v>
+      </c>
+      <c r="Q224" s="19" t="n">
+        <v>-4340925</v>
+      </c>
+      <c r="R224" s="19" t="n">
+        <v>3147065.65734</v>
+      </c>
+      <c r="S224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" s="16" t="n">
+        <v>1.315326619284867</v>
+      </c>
+      <c r="V224" s="16" t="n">
+        <v>0.9223803363518754</v>
+      </c>
+      <c r="W224" s="4" t="n">
+        <v>0.1160726281871474</v>
+      </c>
+      <c r="X224" s="4" t="n">
+        <v>0.06646751306945486</v>
+      </c>
+      <c r="Y224" s="4" t="n">
+        <v>0.0001271052611305779</v>
+      </c>
+      <c r="Z224" s="4" t="n">
+        <v>0.005401828092954308</v>
+      </c>
+      <c r="AA224" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB224" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC224" s="4">
+        <f>(AB224+2*參數!$B$7)/(AA224+AB224)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC223"/>
-  <conditionalFormatting sqref="J2:J223">
+  <autoFilter ref="A1:AC224"/>
+  <conditionalFormatting sqref="J2:J224">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -66709,27 +66926,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -66737,19 +66954,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A2,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66760,27 +66977,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -66788,19 +67005,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A3,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66811,27 +67028,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -66839,19 +67056,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A4,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66862,27 +67079,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -66890,19 +67107,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A5,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66913,27 +67130,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -66941,19 +67158,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A6,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66964,27 +67181,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -66992,19 +67209,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A7,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67015,27 +67232,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -67043,19 +67260,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A8,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67066,27 +67283,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -67094,19 +67311,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A9,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67117,27 +67334,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -67145,19 +67362,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A10,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67168,27 +67385,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -67196,19 +67413,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A11,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67219,27 +67436,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -67247,19 +67464,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A12,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67270,27 +67487,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -67298,19 +67515,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A13,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67321,27 +67538,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -67349,19 +67566,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A14,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67372,27 +67589,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -67400,19 +67617,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A15,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67423,27 +67640,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -67451,19 +67668,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A16,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67474,27 +67691,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -67502,19 +67719,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A17,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67525,27 +67742,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -67553,19 +67770,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A18,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67576,27 +67793,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -67604,19 +67821,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A19,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67627,27 +67844,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -67655,19 +67872,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A20,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67678,27 +67895,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -67706,19 +67923,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A21,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67729,27 +67946,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -67757,19 +67974,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A22,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67780,27 +67997,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -67808,19 +68025,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A23,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67831,27 +68048,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -67859,19 +68076,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A24,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67882,27 +68099,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -67910,19 +68127,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A25,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67933,27 +68150,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -67961,19 +68178,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A26,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67984,27 +68201,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -68012,19 +68229,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A27,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68035,27 +68252,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -68063,19 +68280,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A28,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68086,27 +68303,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -68114,19 +68331,19 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A29,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68137,27 +68354,27 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -68165,19 +68382,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A30,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68188,27 +68405,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -68216,19 +68433,19 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A31,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68239,27 +68456,27 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -68267,19 +68484,19 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A32,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68290,27 +68507,27 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -68318,19 +68535,19 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A33,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68341,27 +68558,27 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -68369,19 +68586,19 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A34,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68392,27 +68609,27 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -68420,19 +68637,19 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A35,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68443,27 +68660,27 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -68471,19 +68688,19 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A36,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68494,27 +68711,27 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -68522,19 +68739,19 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A37,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68545,27 +68762,27 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -68573,19 +68790,19 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A38,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68596,27 +68813,27 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -68624,19 +68841,19 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A39,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68647,27 +68864,27 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -68675,19 +68892,19 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A40,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68698,27 +68915,27 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -68726,19 +68943,19 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A41,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68749,27 +68966,27 @@
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -68777,19 +68994,19 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A42,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68800,27 +69017,27 @@
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -68828,19 +69045,19 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A43,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68851,27 +69068,27 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -68879,19 +69096,19 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A44,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68902,27 +69119,27 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -68930,19 +69147,19 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A45,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68953,27 +69170,27 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -68981,19 +69198,19 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A46,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69004,27 +69221,27 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -69032,19 +69249,19 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A47,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69055,27 +69272,27 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -69083,19 +69300,19 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A48,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69106,27 +69323,27 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -69134,19 +69351,19 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A49,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69157,27 +69374,27 @@
         </is>
       </c>
       <c r="B50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E50" s="2">
-        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H50" s="4">
@@ -69185,19 +69402,19 @@
         <v/>
       </c>
       <c r="I50" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J50" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K50" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A50,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69208,27 +69425,27 @@
         </is>
       </c>
       <c r="B51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51)</f>
         <v/>
       </c>
       <c r="C51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E51" s="2">
-        <f>F51+G51+COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F51+G51+COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H51" s="4">
@@ -69236,19 +69453,19 @@
         <v/>
       </c>
       <c r="I51" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J51" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K51" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A51,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69259,27 +69476,27 @@
         </is>
       </c>
       <c r="B52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52)</f>
         <v/>
       </c>
       <c r="C52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$C$2:$C$223,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$C$2:$C$224,"做多")</f>
         <v/>
       </c>
       <c r="D52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$C$2:$C$223,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$C$2:$C$224,"做空")</f>
         <v/>
       </c>
       <c r="E52" s="2">
-        <f>F52+G52+COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"時間出場")</f>
+        <f>F52+G52+COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"時間出場")</f>
         <v/>
       </c>
       <c r="F52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"止盈")</f>
         <v/>
       </c>
       <c r="G52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"止損")</f>
         <v/>
       </c>
       <c r="H52" s="4">
@@ -69287,19 +69504,19 @@
         <v/>
       </c>
       <c r="I52" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J52" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$223,交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K52" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$223,交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$223,$A52,交易明細!$J$2:$J$223,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -77327,7 +77544,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr"/>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="17" t="n"/>
       <c r="F443" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$445</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$450</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$226</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$445</f>
+              <f>'資金明細'!$R$2:$R$450</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 11:28（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 15:50（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$224,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$226,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$J$2:$J$224,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$J$2:$J$226,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$J$2:$J$224,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$J$2:$J$226,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$J$2:$J$224,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$J$2:$J$226,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$224,"&lt;&gt;未平倉",交易明細!$L$2:$L$224,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$226,"&lt;&gt;未平倉",交易明細!$L$2:$L$226,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$B$2:$B$224,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$B$2:$B$226,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$224,"做多",交易明細!$J$2:$J$224,"&lt;&gt;未平倉",交易明細!$L$2:$L$224,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉",交易明細!$L$2:$L$226,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$B$2:$B$224,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$B$2:$B$226,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$224,"做空",交易明細!$J$2:$J$224,"&lt;&gt;未平倉",交易明細!$L$2:$L$224,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉",交易明細!$L$2:$L$226,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,62 +1085,62 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -1149,21 +1149,21 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -1172,61 +1172,61 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1235,50 +1235,50 @@
         <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -1287,93 +1287,93 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -1384,47 +1384,70 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1490,7 +1513,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R445</f>
+        <f>資金明細!R450</f>
         <v/>
       </c>
     </row>
@@ -1528,7 +1551,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$445)</f>
+        <f>MAX(資金明細!$R$2:$R$450)</f>
         <v/>
       </c>
     </row>
@@ -1547,7 +1570,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$445)</f>
+        <f>MIN(資金明細!$R$2:$R$450)</f>
         <v/>
       </c>
     </row>
@@ -1567,7 +1590,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$445)</f>
+        <f>MIN(資金明細!$X$2:$X$450)</f>
         <v/>
       </c>
     </row>
@@ -1586,7 +1609,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$445,"進場",資金明細!$N$2:$N$445,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$450,"進場",資金明細!$N$2:$N$450,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1605,7 +1628,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$445,"進場",資金明細!$N$2:$N$445,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$450,"進場",資金明細!$N$2:$N$450,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1616,7 +1639,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$445,"出場",資金明細!$N$2:$N$445,"已下單",資金明細!$K$2:$K$445,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$450,"出場",資金明細!$N$2:$N$450,"已下單",資金明細!$K$2:$K$450,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1627,7 +1650,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$224),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$226),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1636,7 +1659,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$445,"出場",資金明細!$N$2:$N$445,"已下單",資金明細!$K$2:$K$445,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$450,"出場",資金明細!$N$2:$N$450,"已下單",資金明細!$K$2:$K$450,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1652,7 +1675,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$445,"出場",資金明細!$N$2:$N$445,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$450,"出場",資金明細!$N$2:$N$450,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1668,7 +1691,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$445)</f>
+        <f>MAX(資金明細!$U$2:$U$450)</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1707,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$445)</f>
+        <f>MAX(資金明細!$S$2:$S$450)</f>
         <v/>
       </c>
     </row>
@@ -1695,7 +1718,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V445</f>
+        <f>B5*資金明細!V450</f>
         <v/>
       </c>
     </row>
@@ -1706,7 +1729,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N364="已下單",資金明細!O364*交易明細!L184,0)+IF(資金明細!N442="已下單",資金明細!O442*交易明細!L223,0)+IF(資金明細!N445="已下單",資金明細!O445*交易明細!L224,0)</f>
+        <f>IF(資金明細!N449="已下單",資金明細!O449*交易明細!L225,0)+IF(資金明細!N450="已下單",資金明細!O450*交易明細!L226,0)</f>
         <v/>
       </c>
     </row>
@@ -1717,7 +1740,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$445)</f>
+        <f>MAX(資金明細!$Y$2:$Y$450)</f>
         <v/>
       </c>
     </row>
@@ -1739,7 +1762,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$445,MATCH(1,資金明細!$Z$2:$Z$445,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$450,MATCH(1,資金明細!$Z$2:$Z$450,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1750,7 +1773,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$445,"進場",資金明細!$N$2:$N$445,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$450,"進場",資金明細!$N$2:$N$450,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1815,7 +1838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z445"/>
+  <dimension ref="A1:Z450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -36888,11 +36911,7 @@
         <v>0.59787</v>
       </c>
       <c r="J364" s="17" t="n"/>
-      <c r="K364" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K364" s="2" t="n"/>
       <c r="L364" s="5" t="n"/>
       <c r="M364" s="16">
         <f>資金模擬!$B$5*V363</f>
@@ -44419,11 +44438,7 @@
         <v>4.3111</v>
       </c>
       <c r="J442" s="17" t="n"/>
-      <c r="K442" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K442" s="2" t="n"/>
       <c r="L442" s="5" t="n"/>
       <c r="M442" s="16">
         <f>資金模擬!$B$5*V441</f>
@@ -44719,11 +44734,7 @@
         <v>0.118125</v>
       </c>
       <c r="J445" s="17" t="n"/>
-      <c r="K445" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K445" s="2" t="n"/>
       <c r="L445" s="5" t="n"/>
       <c r="M445" s="16">
         <f>資金模擬!$B$5*V444</f>
@@ -44778,9 +44789,506 @@
         <v/>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="B446" s="7" t="n">
+        <v>46280.5</v>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>LIT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G446" s="17" t="n">
+        <v>4.538</v>
+      </c>
+      <c r="H446" s="17" t="n">
+        <v>4.67414</v>
+      </c>
+      <c r="I446" s="17" t="n">
+        <v>4.3111</v>
+      </c>
+      <c r="J446" s="17" t="n">
+        <v>4.3111</v>
+      </c>
+      <c r="K446" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L446" s="5">
+        <f>交易明細!K223</f>
+        <v/>
+      </c>
+      <c r="M446" s="16">
+        <f>M442</f>
+        <v/>
+      </c>
+      <c r="N446" s="2">
+        <f>N442</f>
+        <v/>
+      </c>
+      <c r="O446" s="16">
+        <f>O442</f>
+        <v/>
+      </c>
+      <c r="P446" s="4">
+        <f>交易明細!L223</f>
+        <v/>
+      </c>
+      <c r="Q446" s="10">
+        <f>IF(N446="已下單",O446*P446,0)</f>
+        <v/>
+      </c>
+      <c r="R446" s="10">
+        <f>R445+Q446</f>
+        <v/>
+      </c>
+      <c r="S446" s="16">
+        <f>S445-IF(N446="已下單",M446,0)</f>
+        <v/>
+      </c>
+      <c r="T446" s="16">
+        <f>R446-S446</f>
+        <v/>
+      </c>
+      <c r="U446" s="2">
+        <f>U445-IF(N446="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V446" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R446,0),MAX(V445,FLOOR(MAX(R446,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W446" s="10">
+        <f>MAX(W445,R446)</f>
+        <v/>
+      </c>
+      <c r="X446" s="4">
+        <f>IF(W446&gt;0,R446/W446-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y446" s="16">
+        <f>IF(R446&gt;0,S446*資金模擬!$B$7/R446,0)</f>
+        <v/>
+      </c>
+      <c r="Z446" s="2">
+        <f>IF(OR(Z445=1,R446&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="B447" s="7" t="n">
+        <v>46280.5</v>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G447" s="17" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="H447" s="17" t="n">
+        <v>0.109125</v>
+      </c>
+      <c r="I447" s="17" t="n">
+        <v>0.118125</v>
+      </c>
+      <c r="J447" s="17" t="n">
+        <v>0.109125</v>
+      </c>
+      <c r="K447" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L447" s="5">
+        <f>交易明細!K224</f>
+        <v/>
+      </c>
+      <c r="M447" s="16">
+        <f>M445</f>
+        <v/>
+      </c>
+      <c r="N447" s="2">
+        <f>N445</f>
+        <v/>
+      </c>
+      <c r="O447" s="16">
+        <f>O445</f>
+        <v/>
+      </c>
+      <c r="P447" s="4">
+        <f>交易明細!L224</f>
+        <v/>
+      </c>
+      <c r="Q447" s="10">
+        <f>IF(N447="已下單",O447*P447,0)</f>
+        <v/>
+      </c>
+      <c r="R447" s="10">
+        <f>R446+Q447</f>
+        <v/>
+      </c>
+      <c r="S447" s="16">
+        <f>S446-IF(N447="已下單",M447,0)</f>
+        <v/>
+      </c>
+      <c r="T447" s="16">
+        <f>R447-S447</f>
+        <v/>
+      </c>
+      <c r="U447" s="2">
+        <f>U446-IF(N447="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V447" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R447,0),MAX(V446,FLOOR(MAX(R447,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W447" s="10">
+        <f>MAX(W446,R447)</f>
+        <v/>
+      </c>
+      <c r="X447" s="4">
+        <f>IF(W447&gt;0,R447/W447-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y447" s="16">
+        <f>IF(R447&gt;0,S447*資金模擬!$B$7/R447,0)</f>
+        <v/>
+      </c>
+      <c r="Z447" s="2">
+        <f>IF(OR(Z446=1,R447&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n">
+        <v>446</v>
+      </c>
+      <c r="B448" s="7" t="n">
+        <v>46280.54166666666</v>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>AERO_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G448" s="17" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="H448" s="17" t="n">
+        <v>0.552318</v>
+      </c>
+      <c r="I448" s="17" t="n">
+        <v>0.59787</v>
+      </c>
+      <c r="J448" s="17" t="n">
+        <v>0.552318</v>
+      </c>
+      <c r="K448" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L448" s="5">
+        <f>交易明細!K184</f>
+        <v/>
+      </c>
+      <c r="M448" s="16">
+        <f>M364</f>
+        <v/>
+      </c>
+      <c r="N448" s="2">
+        <f>N364</f>
+        <v/>
+      </c>
+      <c r="O448" s="16">
+        <f>O364</f>
+        <v/>
+      </c>
+      <c r="P448" s="4">
+        <f>交易明細!L184</f>
+        <v/>
+      </c>
+      <c r="Q448" s="10">
+        <f>IF(N448="已下單",O448*P448,0)</f>
+        <v/>
+      </c>
+      <c r="R448" s="10">
+        <f>R447+Q448</f>
+        <v/>
+      </c>
+      <c r="S448" s="16">
+        <f>S447-IF(N448="已下單",M448,0)</f>
+        <v/>
+      </c>
+      <c r="T448" s="16">
+        <f>R448-S448</f>
+        <v/>
+      </c>
+      <c r="U448" s="2">
+        <f>U447-IF(N448="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V448" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R448,0),MAX(V447,FLOOR(MAX(R448,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W448" s="10">
+        <f>MAX(W447,R448)</f>
+        <v/>
+      </c>
+      <c r="X448" s="4">
+        <f>IF(W448&gt;0,R448/W448-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y448" s="16">
+        <f>IF(R448&gt;0,S448*資金模擬!$B$7/R448,0)</f>
+        <v/>
+      </c>
+      <c r="Z448" s="2">
+        <f>IF(OR(Z447=1,R448&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="B449" s="7" t="n">
+        <v>46280.54166666666</v>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G449" s="17" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="H449" s="17" t="n">
+        <v>0.650239</v>
+      </c>
+      <c r="I449" s="17" t="n">
+        <v>0.5997349999999999</v>
+      </c>
+      <c r="J449" s="17" t="n"/>
+      <c r="K449" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L449" s="5" t="n"/>
+      <c r="M449" s="16">
+        <f>資金模擬!$B$5*V448</f>
+        <v/>
+      </c>
+      <c r="N449" s="2">
+        <f>IF(Z448=1,"已停止",IF(T448&gt;=M449,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O449" s="16">
+        <f>IF(N449="已下單",M449*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P449" s="4" t="n"/>
+      <c r="Q449" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R449" s="10">
+        <f>R448+Q449</f>
+        <v/>
+      </c>
+      <c r="S449" s="16">
+        <f>S448+IF(N449="已下單",M449,0)</f>
+        <v/>
+      </c>
+      <c r="T449" s="16">
+        <f>R449-S449</f>
+        <v/>
+      </c>
+      <c r="U449" s="2">
+        <f>U448+IF(N449="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V449" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R449,0),MAX(V448,FLOOR(MAX(R449,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W449" s="10">
+        <f>MAX(W448,R449)</f>
+        <v/>
+      </c>
+      <c r="X449" s="4">
+        <f>IF(W449&gt;0,R449/W449-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y449" s="16">
+        <f>IF(R449&gt;0,S449*資金模擬!$B$7/R449,0)</f>
+        <v/>
+      </c>
+      <c r="Z449" s="2">
+        <f>IF(OR(Z448=1,R449&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n">
+        <v>448</v>
+      </c>
+      <c r="B450" s="7" t="n">
+        <v>46280.54166666666</v>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G450" s="17" t="n">
+        <v>0.20512</v>
+      </c>
+      <c r="H450" s="17" t="n">
+        <v>0.2112736</v>
+      </c>
+      <c r="I450" s="17" t="n">
+        <v>0.194864</v>
+      </c>
+      <c r="J450" s="17" t="n"/>
+      <c r="K450" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L450" s="5" t="n"/>
+      <c r="M450" s="16">
+        <f>資金模擬!$B$5*V449</f>
+        <v/>
+      </c>
+      <c r="N450" s="2">
+        <f>IF(Z449=1,"已停止",IF(T449&gt;=M450,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O450" s="16">
+        <f>IF(N450="已下單",M450*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P450" s="4" t="n"/>
+      <c r="Q450" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R450" s="10">
+        <f>R449+Q450</f>
+        <v/>
+      </c>
+      <c r="S450" s="16">
+        <f>S449+IF(N450="已下單",M450,0)</f>
+        <v/>
+      </c>
+      <c r="T450" s="16">
+        <f>R450-S450</f>
+        <v/>
+      </c>
+      <c r="U450" s="2">
+        <f>U449+IF(N450="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V450" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R450,0),MAX(V449,FLOOR(MAX(R450,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W450" s="10">
+        <f>MAX(W449,R450)</f>
+        <v/>
+      </c>
+      <c r="X450" s="4">
+        <f>IF(W450&gt;0,R450/W450-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y450" s="16">
+        <f>IF(R450&gt;0,S450*資金模擬!$B$7/R450,0)</f>
+        <v/>
+      </c>
+      <c r="Z450" s="2">
+        <f>IF(OR(Z449=1,R450&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z445"/>
-  <conditionalFormatting sqref="K2:K445">
+  <autoFilter ref="A1:Z450"/>
+  <conditionalFormatting sqref="K2:K450">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -44788,7 +45296,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N445">
+  <conditionalFormatting sqref="N2:N450">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -44796,7 +45304,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q445">
+  <conditionalFormatting sqref="Q2:Q450">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -44861,7 +45369,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 11:28（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 15:50（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -45065,7 +45573,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$224),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$226),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -45230,7 +45738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC224"/>
+  <dimension ref="A1:AC226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -62896,14 +63404,14 @@
         <v>0.59787</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>46280.45833333334</v>
+        <v>46280.54166666666</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>0.5621</v>
+        <v>0.552318</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K184" s="5">
@@ -62914,11 +63422,7 @@
         <f>IF(C184="做多",I184/E184-1,1-I184/E184)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M184" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M184" s="2" t="inlineStr"/>
       <c r="N184" s="4" t="n">
         <v>-0.02248927038626614</v>
       </c>
@@ -62935,7 +63439,7 @@
         <v>1281726.24259</v>
       </c>
       <c r="S184" s="4" t="n">
-        <v>0.02792413066385668</v>
+        <v>0.03</v>
       </c>
       <c r="T184" s="4" t="n">
         <v>0.0277485072005621</v>
@@ -66644,14 +67148,14 @@
         <v>4.3111</v>
       </c>
       <c r="H223" s="7" t="n">
-        <v>46280.45833333334</v>
+        <v>46280.5</v>
       </c>
       <c r="I223" s="17" t="n">
-        <v>4.36</v>
+        <v>4.3111</v>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K223" s="5">
@@ -66662,11 +67166,7 @@
         <f>IF(C223="做多",I223/E223-1,1-I223/E223)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M223" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M223" s="2" t="inlineStr"/>
       <c r="N223" s="4" t="n">
         <v>0.02437923250564356</v>
       </c>
@@ -66686,7 +67186,7 @@
         <v>0.0202732481269281</v>
       </c>
       <c r="T223" s="4" t="n">
-        <v>0.04186866460996042</v>
+        <v>0.05</v>
       </c>
       <c r="U223" s="16" t="n">
         <v>1.101212313974368</v>
@@ -66744,14 +67244,14 @@
         <v>0.118125</v>
       </c>
       <c r="H224" s="7" t="n">
-        <v>46280.45833333334</v>
+        <v>46280.5</v>
       </c>
       <c r="I224" s="17" t="n">
-        <v>0.1125</v>
+        <v>0.109125</v>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K224" s="5">
@@ -66762,11 +67262,7 @@
         <f>IF(C224="做多",I224/E224-1,1-I224/E224)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M224" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M224" s="2" t="inlineStr"/>
       <c r="N224" s="4" t="n">
         <v>-0.05794674258918098</v>
       </c>
@@ -66783,7 +67279,7 @@
         <v>3147065.65734</v>
       </c>
       <c r="S224" s="4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T224" s="4" t="n">
         <v>0</v>
@@ -66817,9 +67313,209 @@
         <v/>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="n">
+        <v>46280.54166666666</v>
+      </c>
+      <c r="E225" s="17" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="F225" s="17" t="n">
+        <v>0.650239</v>
+      </c>
+      <c r="G225" s="17" t="n">
+        <v>0.5997349999999999</v>
+      </c>
+      <c r="H225" s="7" t="n">
+        <v>46280.625</v>
+      </c>
+      <c r="I225" s="17" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K225" s="5">
+        <f>(H225-D225)*24</f>
+        <v/>
+      </c>
+      <c r="L225" s="4">
+        <f>IF(C225="做多",I225/E225-1,1-I225/E225)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N225" s="4" t="n">
+        <v>0.03052562846882134</v>
+      </c>
+      <c r="O225" s="4" t="n">
+        <v>0.03689338107401321</v>
+      </c>
+      <c r="P225" s="4" t="n">
+        <v>0.03444320639706344</v>
+      </c>
+      <c r="Q225" s="19" t="n">
+        <v>497440</v>
+      </c>
+      <c r="R225" s="19" t="n">
+        <v>2733460.7658</v>
+      </c>
+      <c r="S225" s="4" t="n">
+        <v>0.01092982734040882</v>
+      </c>
+      <c r="T225" s="4" t="n">
+        <v>0.04150166323459525</v>
+      </c>
+      <c r="U225" s="16" t="n">
+        <v>0.8348760476846643</v>
+      </c>
+      <c r="V225" s="16" t="n">
+        <v>0.8571428571428538</v>
+      </c>
+      <c r="W225" s="4" t="n">
+        <v>0.05967979642330778</v>
+      </c>
+      <c r="X225" s="4" t="n">
+        <v>0.163472171028382</v>
+      </c>
+      <c r="Y225" s="4" t="n">
+        <v>-0.001480964455565226</v>
+      </c>
+      <c r="Z225" s="4" t="n">
+        <v>-0.009528629640421338</v>
+      </c>
+      <c r="AA225" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB225" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC225" s="4">
+        <f>(AB225+2*參數!$B$7)/(AA225+AB225)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="n">
+        <v>46280.54166666666</v>
+      </c>
+      <c r="E226" s="17" t="n">
+        <v>0.20512</v>
+      </c>
+      <c r="F226" s="17" t="n">
+        <v>0.2112736</v>
+      </c>
+      <c r="G226" s="17" t="n">
+        <v>0.194864</v>
+      </c>
+      <c r="H226" s="7" t="n">
+        <v>46280.625</v>
+      </c>
+      <c r="I226" s="17" t="n">
+        <v>0.20194</v>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K226" s="5">
+        <f>(H226-D226)*24</f>
+        <v/>
+      </c>
+      <c r="L226" s="4">
+        <f>IF(C226="做多",I226/E226-1,1-I226/E226)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N226" s="4" t="n">
+        <v>0.03439233484619253</v>
+      </c>
+      <c r="O226" s="4" t="n">
+        <v>0.03966172913084775</v>
+      </c>
+      <c r="P226" s="4" t="n">
+        <v>0.007334507050899441</v>
+      </c>
+      <c r="Q226" s="19" t="n">
+        <v>1093709</v>
+      </c>
+      <c r="R226" s="19" t="n">
+        <v>1884084.0024</v>
+      </c>
+      <c r="S226" s="4" t="n">
+        <v>0.004338923556942209</v>
+      </c>
+      <c r="T226" s="4" t="n">
+        <v>0.0285686427457098</v>
+      </c>
+      <c r="U226" s="16" t="n">
+        <v>0.6198819809527375</v>
+      </c>
+      <c r="V226" s="16" t="n">
+        <v>0.9092071611253179</v>
+      </c>
+      <c r="W226" s="4" t="n">
+        <v>-0.06668905302518446</v>
+      </c>
+      <c r="X226" s="4" t="n">
+        <v>0.001171417415072096</v>
+      </c>
+      <c r="Y226" s="4" t="n">
+        <v>-0.001480964455565226</v>
+      </c>
+      <c r="Z226" s="4" t="n">
+        <v>-0.009528629640421338</v>
+      </c>
+      <c r="AA226" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB226" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC226" s="4">
+        <f>(AB226+2*參數!$B$7)/(AA226+AB226)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC224"/>
-  <conditionalFormatting sqref="J2:J224">
+  <autoFilter ref="A1:AC226"/>
+  <conditionalFormatting sqref="J2:J226">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -66926,27 +67622,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -66954,19 +67650,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A2,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -66977,27 +67673,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -67005,19 +67701,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A3,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67028,27 +67724,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -67056,19 +67752,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A4,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67079,27 +67775,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -67107,19 +67803,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A5,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67130,27 +67826,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -67158,19 +67854,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A6,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67181,27 +67877,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -67209,19 +67905,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A7,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67232,27 +67928,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -67260,19 +67956,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A8,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67283,27 +67979,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -67311,19 +68007,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A9,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67334,27 +68030,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A10,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A10,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$226,$A10,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A10,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A10,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -67362,19 +68058,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A10,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A10,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A10,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A10,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A10,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67385,27 +68081,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A11,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A11,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$226,$A11,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A11,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A11,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -67413,19 +68109,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A11,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A11,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A11,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A11,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A11,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67436,27 +68132,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A12,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A12,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$226,$A12,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A12,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A12,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -67464,19 +68160,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A12,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A12,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A12,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A12,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A12,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67487,27 +68183,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A13,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A13,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$226,$A13,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A13,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A13,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -67515,19 +68211,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A13,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A13,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A13,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A13,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A13,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67538,27 +68234,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A14,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A14,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$226,$A14,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A14,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A14,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -67566,19 +68262,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A14,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A14,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A14,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A14,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A14,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67589,27 +68285,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A15,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A15,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$226,$A15,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A15,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A15,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -67617,19 +68313,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A15,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A15,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A15,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A15,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A15,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67640,27 +68336,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A16,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A16,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$226,$A16,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A16,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A16,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -67668,19 +68364,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A16,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A16,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A16,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A16,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A16,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67691,27 +68387,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A17,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A17,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$226,$A17,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A17,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A17,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -67719,19 +68415,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A17,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A17,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A17,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A17,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A17,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67742,27 +68438,27 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A18,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A18,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F18+G18+COUNTIFS(交易明細!$B$2:$B$226,$A18,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A18,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A18,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -67770,19 +68466,19 @@
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A18,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A18,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A18,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L18" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A18,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A18,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67793,27 +68489,27 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A19,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A19,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F19+G19+COUNTIFS(交易明細!$B$2:$B$226,$A19,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A19,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A19,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H19" s="4">
@@ -67821,19 +68517,19 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A19,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A19,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A19,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L19" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A19,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A19,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67844,27 +68540,27 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A20,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A20,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F20+G20+COUNTIFS(交易明細!$B$2:$B$226,$A20,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A20,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A20,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -67872,19 +68568,19 @@
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A20,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A20,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A20,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L20" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A20,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A20,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67895,27 +68591,27 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A21,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A21,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F21+G21+COUNTIFS(交易明細!$B$2:$B$226,$A21,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A21,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A21,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H21" s="4">
@@ -67923,19 +68619,19 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A21,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A21,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A21,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L21" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A21,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A21,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67946,27 +68642,27 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A22,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A22,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F22+G22+COUNTIFS(交易明細!$B$2:$B$226,$A22,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A22,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A22,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -67974,19 +68670,19 @@
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A22,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A22,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A22,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L22" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A22,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A22,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67997,27 +68693,27 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A23,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A23,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F23+G23+COUNTIFS(交易明細!$B$2:$B$226,$A23,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A23,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A23,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H23" s="4">
@@ -68025,19 +68721,19 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A23,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A23,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A23,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L23" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A23,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A23,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68048,27 +68744,27 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A24,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A24,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F24+G24+COUNTIFS(交易明細!$B$2:$B$226,$A24,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A24,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A24,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -68076,19 +68772,19 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A24,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A24,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A24,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L24" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A24,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A24,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68099,27 +68795,27 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A25,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A25,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F25+G25+COUNTIFS(交易明細!$B$2:$B$226,$A25,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A25,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A25,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H25" s="4">
@@ -68127,19 +68823,19 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A25,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A25,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A25,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L25" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A25,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A25,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68150,27 +68846,27 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A26,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A26,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F26+G26+COUNTIFS(交易明細!$B$2:$B$226,$A26,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A26,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A26,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -68178,19 +68874,19 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A26,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A26,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A26,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L26" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A26,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A26,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68201,27 +68897,27 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A27,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A27,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F27+G27+COUNTIFS(交易明細!$B$2:$B$226,$A27,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A27,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A27,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H27" s="4">
@@ -68229,19 +68925,19 @@
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A27,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A27,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A27,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L27" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A27,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A27,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68252,27 +68948,27 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A28,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A28,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F28+G28+COUNTIFS(交易明細!$B$2:$B$226,$A28,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A28,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A28,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H28" s="4">
@@ -68280,19 +68976,19 @@
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A28,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A28,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A28,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L28" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A28,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A28,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68303,27 +68999,27 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A29,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A29,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F29+G29+COUNTIFS(交易明細!$B$2:$B$226,$A29,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A29,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A29,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H29" s="4">
@@ -68331,19 +69027,19 @@
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A29,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A29,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A29,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L29" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A29,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A29,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68354,27 +69050,27 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A30,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A30,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F30+G30+COUNTIFS(交易明細!$B$2:$B$226,$A30,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A30,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A30,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H30" s="4">
@@ -68382,19 +69078,19 @@
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A30,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A30,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A30,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L30" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A30,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A30,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68405,27 +69101,27 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A31,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A31,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F31+G31+COUNTIFS(交易明細!$B$2:$B$226,$A31,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A31,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A31,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H31" s="4">
@@ -68433,19 +69129,19 @@
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A31,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A31,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A31,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L31" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A31,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A31,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68456,27 +69152,27 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A32,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A32,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F32+G32+COUNTIFS(交易明細!$B$2:$B$226,$A32,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A32,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A32,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H32" s="4">
@@ -68484,19 +69180,19 @@
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A32,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A32,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A32,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L32" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A32,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A32,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68507,27 +69203,27 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A33,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A33,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F33+G33+COUNTIFS(交易明細!$B$2:$B$226,$A33,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A33,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A33,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H33" s="4">
@@ -68535,19 +69231,19 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A33,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A33,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A33,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L33" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A33,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A33,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68558,27 +69254,27 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A34,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A34,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F34+G34+COUNTIFS(交易明細!$B$2:$B$226,$A34,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A34,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A34,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H34" s="4">
@@ -68586,19 +69282,19 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A34,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A34,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A34,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L34" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A34,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A34,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68609,27 +69305,27 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A35,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A35,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F35+G35+COUNTIFS(交易明細!$B$2:$B$226,$A35,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A35,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A35,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H35" s="4">
@@ -68637,19 +69333,19 @@
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A35,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A35,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A35,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L35" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A35,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A35,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68660,27 +69356,27 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A36,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A36,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F36+G36+COUNTIFS(交易明細!$B$2:$B$226,$A36,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A36,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A36,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H36" s="4">
@@ -68688,19 +69384,19 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A36,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A36,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A36,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L36" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A36,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A36,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68711,27 +69407,27 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A37,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A37,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F37+G37+COUNTIFS(交易明細!$B$2:$B$226,$A37,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A37,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A37,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H37" s="4">
@@ -68739,19 +69435,19 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A37,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A37,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A37,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L37" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A37,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A37,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68762,27 +69458,27 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A38,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A38,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F38+G38+COUNTIFS(交易明細!$B$2:$B$226,$A38,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A38,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A38,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H38" s="4">
@@ -68790,19 +69486,19 @@
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A38,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A38,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A38,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L38" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A38,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A38,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68813,27 +69509,27 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A39,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A39,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F39+G39+COUNTIFS(交易明細!$B$2:$B$226,$A39,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A39,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A39,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H39" s="4">
@@ -68841,19 +69537,19 @@
         <v/>
       </c>
       <c r="I39" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A39,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J39" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A39,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A39,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L39" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A39,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A39,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68864,27 +69560,27 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A40,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A40,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F40+G40+COUNTIFS(交易明細!$B$2:$B$226,$A40,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A40,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A40,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H40" s="4">
@@ -68892,19 +69588,19 @@
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A40,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A40,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A40,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L40" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A40,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A40,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68915,27 +69611,27 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A41,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A41,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F41+G41+COUNTIFS(交易明細!$B$2:$B$226,$A41,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A41,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A41,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -68943,19 +69639,19 @@
         <v/>
       </c>
       <c r="I41" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A41,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J41" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A41,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A41,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L41" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A41,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A41,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -68966,27 +69662,27 @@
         </is>
       </c>
       <c r="B42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A42,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A42,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F42+G42+COUNTIFS(交易明細!$B$2:$B$226,$A42,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A42,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A42,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -68994,19 +69690,19 @@
         <v/>
       </c>
       <c r="I42" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A42,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J42" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A42,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A42,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L42" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A42,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A42,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69017,27 +69713,27 @@
         </is>
       </c>
       <c r="B43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A43,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A43,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F43+G43+COUNTIFS(交易明細!$B$2:$B$226,$A43,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A43,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A43,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -69045,19 +69741,19 @@
         <v/>
       </c>
       <c r="I43" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A43,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J43" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A43,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A43,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L43" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A43,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A43,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69068,27 +69764,27 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A44,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A44,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F44+G44+COUNTIFS(交易明細!$B$2:$B$226,$A44,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A44,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A44,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -69096,19 +69792,19 @@
         <v/>
       </c>
       <c r="I44" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A44,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J44" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A44,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A44,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L44" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A44,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A44,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69119,27 +69815,27 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A45,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A45,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E45" s="2">
-        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F45+G45+COUNTIFS(交易明細!$B$2:$B$226,$A45,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A45,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A45,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -69147,19 +69843,19 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A45,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J45" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A45,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A45,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L45" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A45,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A45,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69170,27 +69866,27 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A46,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A46,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E46" s="2">
-        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F46+G46+COUNTIFS(交易明細!$B$2:$B$226,$A46,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A46,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A46,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -69198,19 +69894,19 @@
         <v/>
       </c>
       <c r="I46" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A46,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J46" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A46,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A46,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L46" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A46,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A46,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69221,27 +69917,27 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A47,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A47,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E47" s="2">
-        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F47+G47+COUNTIFS(交易明細!$B$2:$B$226,$A47,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A47,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A47,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -69249,19 +69945,19 @@
         <v/>
       </c>
       <c r="I47" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A47,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J47" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A47,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A47,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L47" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A47,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A47,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69272,27 +69968,27 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A48,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A48,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E48" s="2">
-        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F48+G48+COUNTIFS(交易明細!$B$2:$B$226,$A48,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A48,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A48,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -69300,19 +69996,19 @@
         <v/>
       </c>
       <c r="I48" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A48,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J48" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A48,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A48,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L48" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A48,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A48,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69323,27 +70019,27 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A49,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A49,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E49" s="2">
-        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F49+G49+COUNTIFS(交易明細!$B$2:$B$226,$A49,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A49,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A49,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -69351,19 +70047,19 @@
         <v/>
       </c>
       <c r="I49" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A49,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J49" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A49,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A49,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L49" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A49,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A49,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69374,27 +70070,27 @@
         </is>
       </c>
       <c r="B50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A50,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A50,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E50" s="2">
-        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F50+G50+COUNTIFS(交易明細!$B$2:$B$226,$A50,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A50,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A50,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H50" s="4">
@@ -69402,19 +70098,19 @@
         <v/>
       </c>
       <c r="I50" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A50,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J50" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A50,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K50" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A50,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L50" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A50,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A50,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69425,27 +70121,27 @@
         </is>
       </c>
       <c r="B51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A51)</f>
         <v/>
       </c>
       <c r="C51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A51,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A51,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E51" s="2">
-        <f>F51+G51+COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F51+G51+COUNTIFS(交易明細!$B$2:$B$226,$A51,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A51,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A51,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H51" s="4">
@@ -69453,19 +70149,19 @@
         <v/>
       </c>
       <c r="I51" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A51,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J51" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A51,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K51" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A51,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L51" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A51,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A51,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69476,27 +70172,27 @@
         </is>
       </c>
       <c r="B52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A52)</f>
         <v/>
       </c>
       <c r="C52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$C$2:$C$224,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A52,交易明細!$C$2:$C$226,"做多")</f>
         <v/>
       </c>
       <c r="D52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$C$2:$C$224,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A52,交易明細!$C$2:$C$226,"做空")</f>
         <v/>
       </c>
       <c r="E52" s="2">
-        <f>F52+G52+COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"時間出場")</f>
+        <f>F52+G52+COUNTIFS(交易明細!$B$2:$B$226,$A52,交易明細!$J$2:$J$226,"時間出場")</f>
         <v/>
       </c>
       <c r="F52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A52,交易明細!$J$2:$J$226,"止盈")</f>
         <v/>
       </c>
       <c r="G52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A52,交易明細!$J$2:$J$226,"止損")</f>
         <v/>
       </c>
       <c r="H52" s="4">
@@ -69504,19 +70200,19 @@
         <v/>
       </c>
       <c r="I52" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A52,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J52" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$224,交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A52,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K52" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$224,交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A52,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L52" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$224,$A52,交易明細!$J$2:$J$224,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$226,$A52,交易明細!$J$2:$J$226,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -69778,11 +70474,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="17" t="n"/>
       <c r="F12" s="17" t="n"/>
@@ -73490,11 +74182,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C218" s="2" t="inlineStr"/>
       <c r="D218" s="2" t="n"/>
       <c r="E218" s="17" t="n"/>
       <c r="F218" s="17" t="n"/>
@@ -74898,7 +75586,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C296" s="2" t="inlineStr"/>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D296" s="2" t="n"/>
       <c r="E296" s="17" t="n"/>
       <c r="F296" s="17" t="n"/>
@@ -76698,7 +77390,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr"/>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="17" t="n"/>
       <c r="F396" s="17" t="n"/>
@@ -77544,11 +78240,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C443" s="2" t="inlineStr"/>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="17" t="n"/>
       <c r="F443" s="17" t="n"/>

--- a/output/dryrun_watch.xlsx
+++ b/output/dryrun_watch.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$450</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$226</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$456</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AC$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -280,7 +280,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$450</f>
+              <f>'資金明細'!$R$2:$R$456</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 15:50（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 21:38（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -795,19 +795,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -815,35 +815,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$226,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$228,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$J$2:$J$226,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$J$2:$J$228,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$J$2:$J$226,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$J$2:$J$228,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$J$2:$J$226,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$J$2:$J$228,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$226,"&lt;&gt;未平倉",交易明細!$L$2:$L$226,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$228,"&lt;&gt;未平倉",交易明細!$L$2:$L$228,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$B$2:$B$226,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做多",交易明細!$B$2:$B$228,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -862,19 +862,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -882,35 +882,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$228,交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$226,"做多",交易明細!$J$2:$J$226,"&lt;&gt;未平倉",交易明細!$L$2:$L$226,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$228,"做多",交易明細!$J$2:$J$228,"&lt;&gt;未平倉",交易明細!$L$2:$L$228,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$B$2:$B$226,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做空",交易明細!$B$2:$B$228,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -929,19 +929,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -949,35 +949,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$228,交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$226,"做空",交易明細!$J$2:$J$226,"&lt;&gt;未平倉",交易明細!$L$2:$L$226,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$228,"做空",交易明細!$J$2:$J$228,"&lt;&gt;未平倉",交易明細!$L$2:$L$228,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1097,73 +1097,73 @@
         <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -1172,21 +1172,21 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -1195,61 +1195,61 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1258,50 +1258,50 @@
         <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -1310,93 +1310,93 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -1407,47 +1407,70 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1513,7 +1536,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R450</f>
+        <f>資金明細!R456</f>
         <v/>
       </c>
     </row>
@@ -1551,7 +1574,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$450)</f>
+        <f>MAX(資金明細!$R$2:$R$456)</f>
         <v/>
       </c>
     </row>
@@ -1570,7 +1593,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$450)</f>
+        <f>MIN(資金明細!$R$2:$R$456)</f>
         <v/>
       </c>
     </row>
@@ -1590,7 +1613,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$450)</f>
+        <f>MIN(資金明細!$X$2:$X$456)</f>
         <v/>
       </c>
     </row>
@@ -1609,7 +1632,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$450,"進場",資金明細!$N$2:$N$450,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$456,"進場",資金明細!$N$2:$N$456,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1628,7 +1651,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$450,"進場",資金明細!$N$2:$N$450,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$456,"進場",資金明細!$N$2:$N$456,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1639,7 +1662,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$450,"出場",資金明細!$N$2:$N$450,"已下單",資金明細!$K$2:$K$450,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$456,"出場",資金明細!$N$2:$N$456,"已下單",資金明細!$K$2:$K$456,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1650,7 +1673,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$226),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$228),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1659,7 +1682,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$450,"出場",資金明細!$N$2:$N$450,"已下單",資金明細!$K$2:$K$450,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$456,"出場",資金明細!$N$2:$N$456,"已下單",資金明細!$K$2:$K$456,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1675,7 +1698,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$450,"出場",資金明細!$N$2:$N$450,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$456,"出場",資金明細!$N$2:$N$456,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1691,7 +1714,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$450)</f>
+        <f>MAX(資金明細!$U$2:$U$456)</f>
         <v/>
       </c>
     </row>
@@ -1707,7 +1730,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$450)</f>
+        <f>MAX(資金明細!$S$2:$S$456)</f>
         <v/>
       </c>
     </row>
@@ -1718,7 +1741,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V450</f>
+        <f>B5*資金明細!V456</f>
         <v/>
       </c>
     </row>
@@ -1729,7 +1752,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N449="已下單",資金明細!O449*交易明細!L225,0)+IF(資金明細!N450="已下單",資金明細!O450*交易明細!L226,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -1740,7 +1763,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$450)</f>
+        <f>MAX(資金明細!$Y$2:$Y$456)</f>
         <v/>
       </c>
     </row>
@@ -1762,7 +1785,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$450,MATCH(1,資金明細!$Z$2:$Z$450,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$456,MATCH(1,資金明細!$Z$2:$Z$456,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1773,7 +1796,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$450,"進場",資金明細!$N$2:$N$450,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$456,"進場",資金明細!$N$2:$N$456,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1838,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z450"/>
+  <dimension ref="A1:Z456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -45133,11 +45156,7 @@
         <v>0.5997349999999999</v>
       </c>
       <c r="J449" s="17" t="n"/>
-      <c r="K449" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K449" s="2" t="n"/>
       <c r="L449" s="5" t="n"/>
       <c r="M449" s="16">
         <f>資金模擬!$B$5*V448</f>
@@ -45227,11 +45246,7 @@
         <v>0.194864</v>
       </c>
       <c r="J450" s="17" t="n"/>
-      <c r="K450" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K450" s="2" t="n"/>
       <c r="L450" s="5" t="n"/>
       <c r="M450" s="16">
         <f>資金模擬!$B$5*V449</f>
@@ -45286,9 +45301,601 @@
         <v/>
       </c>
     </row>
+    <row r="451">
+      <c r="A451" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="B451" s="7" t="n">
+        <v>46280.66666666666</v>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G451" s="17" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="H451" s="17" t="n">
+        <v>0.650239</v>
+      </c>
+      <c r="I451" s="17" t="n">
+        <v>0.5997349999999999</v>
+      </c>
+      <c r="J451" s="17" t="n">
+        <v>0.5997349999999999</v>
+      </c>
+      <c r="K451" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L451" s="5">
+        <f>交易明細!K225</f>
+        <v/>
+      </c>
+      <c r="M451" s="16">
+        <f>M449</f>
+        <v/>
+      </c>
+      <c r="N451" s="2">
+        <f>N449</f>
+        <v/>
+      </c>
+      <c r="O451" s="16">
+        <f>O449</f>
+        <v/>
+      </c>
+      <c r="P451" s="4">
+        <f>交易明細!L225</f>
+        <v/>
+      </c>
+      <c r="Q451" s="10">
+        <f>IF(N451="已下單",O451*P451,0)</f>
+        <v/>
+      </c>
+      <c r="R451" s="10">
+        <f>R450+Q451</f>
+        <v/>
+      </c>
+      <c r="S451" s="16">
+        <f>S450-IF(N451="已下單",M451,0)</f>
+        <v/>
+      </c>
+      <c r="T451" s="16">
+        <f>R451-S451</f>
+        <v/>
+      </c>
+      <c r="U451" s="2">
+        <f>U450-IF(N451="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V451" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R451,0),MAX(V450,FLOOR(MAX(R451,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W451" s="10">
+        <f>MAX(W450,R451)</f>
+        <v/>
+      </c>
+      <c r="X451" s="4">
+        <f>IF(W451&gt;0,R451/W451-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y451" s="16">
+        <f>IF(R451&gt;0,S451*資金模擬!$B$7/R451,0)</f>
+        <v/>
+      </c>
+      <c r="Z451" s="2">
+        <f>IF(OR(Z450=1,R451&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="B452" s="7" t="n">
+        <v>46280.75</v>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>LSK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G452" s="17" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="H452" s="17" t="n">
+        <v>0.377718</v>
+      </c>
+      <c r="I452" s="17" t="n">
+        <v>0.4088700000000001</v>
+      </c>
+      <c r="J452" s="17" t="n"/>
+      <c r="K452" s="2" t="n"/>
+      <c r="L452" s="5" t="n"/>
+      <c r="M452" s="16">
+        <f>資金模擬!$B$5*V451</f>
+        <v/>
+      </c>
+      <c r="N452" s="2">
+        <f>IF(Z451=1,"已停止",IF(T451&gt;=M452,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O452" s="16">
+        <f>IF(N452="已下單",M452*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P452" s="4" t="n"/>
+      <c r="Q452" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R452" s="10">
+        <f>R451+Q452</f>
+        <v/>
+      </c>
+      <c r="S452" s="16">
+        <f>S451+IF(N452="已下單",M452,0)</f>
+        <v/>
+      </c>
+      <c r="T452" s="16">
+        <f>R452-S452</f>
+        <v/>
+      </c>
+      <c r="U452" s="2">
+        <f>U451+IF(N452="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V452" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R452,0),MAX(V451,FLOOR(MAX(R452,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W452" s="10">
+        <f>MAX(W451,R452)</f>
+        <v/>
+      </c>
+      <c r="X452" s="4">
+        <f>IF(W452&gt;0,R452/W452-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y452" s="16">
+        <f>IF(R452&gt;0,S452*資金模擬!$B$7/R452,0)</f>
+        <v/>
+      </c>
+      <c r="Z452" s="2">
+        <f>IF(OR(Z451=1,R452&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n">
+        <v>451</v>
+      </c>
+      <c r="B453" s="7" t="n">
+        <v>46280.79166666666</v>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>LSK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G453" s="17" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="H453" s="17" t="n">
+        <v>0.377718</v>
+      </c>
+      <c r="I453" s="17" t="n">
+        <v>0.4088700000000001</v>
+      </c>
+      <c r="J453" s="17" t="n">
+        <v>0.377718</v>
+      </c>
+      <c r="K453" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L453" s="5">
+        <f>交易明細!K227</f>
+        <v/>
+      </c>
+      <c r="M453" s="16">
+        <f>M452</f>
+        <v/>
+      </c>
+      <c r="N453" s="2">
+        <f>N452</f>
+        <v/>
+      </c>
+      <c r="O453" s="16">
+        <f>O452</f>
+        <v/>
+      </c>
+      <c r="P453" s="4">
+        <f>交易明細!L227</f>
+        <v/>
+      </c>
+      <c r="Q453" s="10">
+        <f>IF(N453="已下單",O453*P453,0)</f>
+        <v/>
+      </c>
+      <c r="R453" s="10">
+        <f>R452+Q453</f>
+        <v/>
+      </c>
+      <c r="S453" s="16">
+        <f>S452-IF(N453="已下單",M453,0)</f>
+        <v/>
+      </c>
+      <c r="T453" s="16">
+        <f>R453-S453</f>
+        <v/>
+      </c>
+      <c r="U453" s="2">
+        <f>U452-IF(N453="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V453" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R453,0),MAX(V452,FLOOR(MAX(R453,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W453" s="10">
+        <f>MAX(W452,R453)</f>
+        <v/>
+      </c>
+      <c r="X453" s="4">
+        <f>IF(W453&gt;0,R453/W453-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y453" s="16">
+        <f>IF(R453&gt;0,S453*資金模擬!$B$7/R453,0)</f>
+        <v/>
+      </c>
+      <c r="Z453" s="2">
+        <f>IF(OR(Z452=1,R453&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="B454" s="7" t="n">
+        <v>46280.79166666666</v>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>CAP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G454" s="17" t="n">
+        <v>0.06137</v>
+      </c>
+      <c r="H454" s="17" t="n">
+        <v>0.0595289</v>
+      </c>
+      <c r="I454" s="17" t="n">
+        <v>0.06443850000000001</v>
+      </c>
+      <c r="J454" s="17" t="n"/>
+      <c r="K454" s="2" t="n"/>
+      <c r="L454" s="5" t="n"/>
+      <c r="M454" s="16">
+        <f>資金模擬!$B$5*V453</f>
+        <v/>
+      </c>
+      <c r="N454" s="2">
+        <f>IF(Z453=1,"已停止",IF(T453&gt;=M454,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O454" s="16">
+        <f>IF(N454="已下單",M454*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P454" s="4" t="n"/>
+      <c r="Q454" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R454" s="10">
+        <f>R453+Q454</f>
+        <v/>
+      </c>
+      <c r="S454" s="16">
+        <f>S453+IF(N454="已下單",M454,0)</f>
+        <v/>
+      </c>
+      <c r="T454" s="16">
+        <f>R454-S454</f>
+        <v/>
+      </c>
+      <c r="U454" s="2">
+        <f>U453+IF(N454="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V454" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R454,0),MAX(V453,FLOOR(MAX(R454,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W454" s="10">
+        <f>MAX(W453,R454)</f>
+        <v/>
+      </c>
+      <c r="X454" s="4">
+        <f>IF(W454&gt;0,R454/W454-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y454" s="16">
+        <f>IF(R454&gt;0,S454*資金模擬!$B$7/R454,0)</f>
+        <v/>
+      </c>
+      <c r="Z454" s="2">
+        <f>IF(OR(Z453=1,R454&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>453</v>
+      </c>
+      <c r="B455" s="7" t="n">
+        <v>46280.875</v>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G455" s="17" t="n">
+        <v>0.20512</v>
+      </c>
+      <c r="H455" s="17" t="n">
+        <v>0.2112736</v>
+      </c>
+      <c r="I455" s="17" t="n">
+        <v>0.194864</v>
+      </c>
+      <c r="J455" s="17" t="n">
+        <v>0.2112736</v>
+      </c>
+      <c r="K455" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L455" s="5">
+        <f>交易明細!K226</f>
+        <v/>
+      </c>
+      <c r="M455" s="16">
+        <f>M450</f>
+        <v/>
+      </c>
+      <c r="N455" s="2">
+        <f>N450</f>
+        <v/>
+      </c>
+      <c r="O455" s="16">
+        <f>O450</f>
+        <v/>
+      </c>
+      <c r="P455" s="4">
+        <f>交易明細!L226</f>
+        <v/>
+      </c>
+      <c r="Q455" s="10">
+        <f>IF(N455="已下單",O455*P455,0)</f>
+        <v/>
+      </c>
+      <c r="R455" s="10">
+        <f>R454+Q455</f>
+        <v/>
+      </c>
+      <c r="S455" s="16">
+        <f>S454-IF(N455="已下單",M455,0)</f>
+        <v/>
+      </c>
+      <c r="T455" s="16">
+        <f>R455-S455</f>
+        <v/>
+      </c>
+      <c r="U455" s="2">
+        <f>U454-IF(N455="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V455" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R455,0),MAX(V454,FLOOR(MAX(R455,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W455" s="10">
+        <f>MAX(W454,R455)</f>
+        <v/>
+      </c>
+      <c r="X455" s="4">
+        <f>IF(W455&gt;0,R455/W455-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y455" s="16">
+        <f>IF(R455&gt;0,S455*資金模擬!$B$7/R455,0)</f>
+        <v/>
+      </c>
+      <c r="Z455" s="2">
+        <f>IF(OR(Z454=1,R455&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n">
+        <v>454</v>
+      </c>
+      <c r="B456" s="7" t="n">
+        <v>46280.875</v>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>CAP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G456" s="17" t="n">
+        <v>0.06137</v>
+      </c>
+      <c r="H456" s="17" t="n">
+        <v>0.0595289</v>
+      </c>
+      <c r="I456" s="17" t="n">
+        <v>0.06443850000000001</v>
+      </c>
+      <c r="J456" s="17" t="n">
+        <v>0.06443850000000001</v>
+      </c>
+      <c r="K456" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L456" s="5">
+        <f>交易明細!K228</f>
+        <v/>
+      </c>
+      <c r="M456" s="16">
+        <f>M454</f>
+        <v/>
+      </c>
+      <c r="N456" s="2">
+        <f>N454</f>
+        <v/>
+      </c>
+      <c r="O456" s="16">
+        <f>O454</f>
+        <v/>
+      </c>
+      <c r="P456" s="4">
+        <f>交易明細!L228</f>
+        <v/>
+      </c>
+      <c r="Q456" s="10">
+        <f>IF(N456="已下單",O456*P456,0)</f>
+        <v/>
+      </c>
+      <c r="R456" s="10">
+        <f>R455+Q456</f>
+        <v/>
+      </c>
+      <c r="S456" s="16">
+        <f>S455-IF(N456="已下單",M456,0)</f>
+        <v/>
+      </c>
+      <c r="T456" s="16">
+        <f>R456-S456</f>
+        <v/>
+      </c>
+      <c r="U456" s="2">
+        <f>U455-IF(N456="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V456" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R456,0),MAX(V455,FLOOR(MAX(R456,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W456" s="10">
+        <f>MAX(W455,R456)</f>
+        <v/>
+      </c>
+      <c r="X456" s="4">
+        <f>IF(W456&gt;0,R456/W456-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y456" s="16">
+        <f>IF(R456&gt;0,S456*資金模擬!$B$7/R456,0)</f>
+        <v/>
+      </c>
+      <c r="Z456" s="2">
+        <f>IF(OR(Z455=1,R456&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z450"/>
-  <conditionalFormatting sqref="K2:K450">
+  <autoFilter ref="A1:Z456"/>
+  <conditionalFormatting sqref="K2:K456">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -45296,7 +45903,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N450">
+  <conditionalFormatting sqref="N2:N456">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -45304,7 +45911,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q450">
+  <conditionalFormatting sqref="Q2:Q456">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -45369,7 +45976,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 15:50（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 21:38（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -45573,7 +46180,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$226),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$228),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -45738,7 +46345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC226"/>
+  <dimension ref="A1:AC228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -67340,14 +67947,14 @@
         <v>0.5997349999999999</v>
       </c>
       <c r="H225" s="7" t="n">
-        <v>46280.625</v>
+        <v>46280.66666666666</v>
       </c>
       <c r="I225" s="17" t="n">
-        <v>0.6066</v>
+        <v>0.5997349999999999</v>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K225" s="5">
@@ -67358,11 +67965,7 @@
         <f>IF(C225="做多",I225/E225-1,1-I225/E225)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M225" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M225" s="2" t="inlineStr"/>
       <c r="N225" s="4" t="n">
         <v>0.03052562846882134</v>
       </c>
@@ -67382,7 +67985,7 @@
         <v>0.01092982734040882</v>
       </c>
       <c r="T225" s="4" t="n">
-        <v>0.04150166323459525</v>
+        <v>0.05</v>
       </c>
       <c r="U225" s="16" t="n">
         <v>0.8348760476846643</v>
@@ -67440,14 +68043,14 @@
         <v>0.194864</v>
       </c>
       <c r="H226" s="7" t="n">
-        <v>46280.625</v>
+        <v>46280.875</v>
       </c>
       <c r="I226" s="17" t="n">
-        <v>0.20194</v>
+        <v>0.2112736</v>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K226" s="5">
@@ -67458,11 +68061,7 @@
         <f>IF(C226="做多",I226/E226-1,1-I226/E226)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M226" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M226" s="2" t="inlineStr"/>
       <c r="N226" s="4" t="n">
         <v>0.03439233484619253</v>
       </c>
@@ -67479,10 +68078,10 @@
         <v>1884084.0024</v>
       </c>
       <c r="S226" s="4" t="n">
-        <v>0.004338923556942209</v>
+        <v>0.03</v>
       </c>
       <c r="T226" s="4" t="n">
-        <v>0.0285686427457098</v>
+        <v>0.04051287051482055</v>
       </c>
       <c r="U226" s="16" t="n">
         <v>0.6198819809527375</v>
@@ -67513,9 +68112,201 @@
         <v/>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>LSK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="n">
+        <v>46280.75</v>
+      </c>
+      <c r="E227" s="17" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="F227" s="17" t="n">
+        <v>0.377718</v>
+      </c>
+      <c r="G227" s="17" t="n">
+        <v>0.4088700000000001</v>
+      </c>
+      <c r="H227" s="7" t="n">
+        <v>46280.79166666666</v>
+      </c>
+      <c r="I227" s="17" t="n">
+        <v>0.377718</v>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K227" s="5">
+        <f>(H227-D227)*24</f>
+        <v/>
+      </c>
+      <c r="L227" s="4">
+        <f>IF(C227="做多",I227/E227-1,1-I227/E227)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="4" t="n">
+        <v>-0.06953405017921133</v>
+      </c>
+      <c r="O227" s="4" t="n">
+        <v>0.1762667332825261</v>
+      </c>
+      <c r="P227" s="4" t="n">
+        <v>-0.03703245749613604</v>
+      </c>
+      <c r="Q227" s="19" t="n">
+        <v>-6448703</v>
+      </c>
+      <c r="R227" s="19" t="n">
+        <v>15364261.8638</v>
+      </c>
+      <c r="S227" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T227" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" s="16" t="n">
+        <v>0.6187481295028492</v>
+      </c>
+      <c r="V227" s="16" t="n">
+        <v>0.9039039039039029</v>
+      </c>
+      <c r="W227" s="4" t="n">
+        <v>0.1875482484508335</v>
+      </c>
+      <c r="X227" s="4" t="n">
+        <v>0.5558850364963503</v>
+      </c>
+      <c r="Y227" s="4" t="n">
+        <v>0.0002338731472049105</v>
+      </c>
+      <c r="Z227" s="4" t="n">
+        <v>0.01463131656237382</v>
+      </c>
+      <c r="AA227" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB227" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC227" s="4">
+        <f>(AB227+2*參數!$B$7)/(AA227+AB227)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>CAP_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="n">
+        <v>46280.79166666666</v>
+      </c>
+      <c r="E228" s="17" t="n">
+        <v>0.06137</v>
+      </c>
+      <c r="F228" s="17" t="n">
+        <v>0.0595289</v>
+      </c>
+      <c r="G228" s="17" t="n">
+        <v>0.06443850000000001</v>
+      </c>
+      <c r="H228" s="7" t="n">
+        <v>46280.875</v>
+      </c>
+      <c r="I228" s="17" t="n">
+        <v>0.06443850000000001</v>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="K228" s="5">
+        <f>(H228-D228)*24</f>
+        <v/>
+      </c>
+      <c r="L228" s="4">
+        <f>IF(C228="做多",I228/E228-1,1-I228/E228)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="4" t="n">
+        <v>-0.06219437652811732</v>
+      </c>
+      <c r="O228" s="4" t="n">
+        <v>0.06406880016718004</v>
+      </c>
+      <c r="P228" s="4" t="n">
+        <v>-0.00808947721450437</v>
+      </c>
+      <c r="Q228" s="19" t="n">
+        <v>-2519277</v>
+      </c>
+      <c r="R228" s="19" t="n">
+        <v>1798381.06354</v>
+      </c>
+      <c r="S228" s="4" t="n">
+        <v>0.002770083102493159</v>
+      </c>
+      <c r="T228" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U228" s="16" t="n">
+        <v>0.7600169040732216</v>
+      </c>
+      <c r="V228" s="16" t="n">
+        <v>0.9199218749999999</v>
+      </c>
+      <c r="W228" s="4" t="n">
+        <v>-0.2375478927203067</v>
+      </c>
+      <c r="X228" s="4" t="n">
+        <v>-0.1192777676454497</v>
+      </c>
+      <c r="Y228" s="4" t="n">
+        <v>-0.0009980921883692151</v>
+      </c>
+      <c r="Z228" s="4" t="n">
+        <v>0.01272818698479727</v>
+      </c>
+      <c r="AA228" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB228" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC228" s="4">
+        <f>(AB228+2*參數!$B$7)/(AA228+AB228)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC226"/>
-  <conditionalFormatting sqref="J2:J226">
+  <autoFilter ref="A1:AC228"/>
+  <conditionalFormatting sqref="J2:J228">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -67536,7 +68327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -67622,27 +68413,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$C$2:$C$226,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A2,交易明細!$C$2:$C$228,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$C$2:$C$226,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A2,交易明細!$C$2:$C$228,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$228,$A2,交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A2,交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A2,交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -67650,19 +68441,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A2,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A2,交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$B$2:$B$228,$A2,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A2,交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A2,交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67673,27 +68464,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$C$2:$C$226,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A3,交易明細!$C$2:$C$228,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$C$2:$C$226,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A3,交易明細!$C$2:$C$228,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$228,$A3,交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A3,交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A3,交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -67701,19 +68492,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A3,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A3,交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$B$2:$B$228,$A3,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A3,交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A3,交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67724,27 +68515,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$C$2:$C$226,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A4,交易明細!$C$2:$C$228,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$C$2:$C$226,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A4,交易明細!$C$2:$C$228,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$228,$A4,交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A4,交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A4,交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -67752,19 +68543,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A4,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A4,交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$B$2:$B$228,$A4,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A4,交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A4,交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67775,27 +68566,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$C$2:$C$226,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A5,交易明細!$C$2:$C$228,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$C$2:$C$226,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A5,交易明細!$C$2:$C$228,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$228,$A5,交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A5,交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A5,交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -67803,19 +68594,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A5,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A5,交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$B$2:$B$228,$A5,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A5,交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A5,交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67826,27 +68617,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$C$2:$C$226,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A6,交易明細!$C$2:$C$228,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$C$2:$C$226,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A6,交易明細!$C$2:$C$228,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$228,$A6,交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A6,交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A6,交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -67854,19 +68645,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A6,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A6,交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$B$2:$B$228,$A6,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A6,交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A6,交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67877,27 +68668,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$C$2:$C$226,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A7,交易明細!$C$2:$C$228,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$C$2:$C$226,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A7,交易明細!$C$2:$C$228,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$228,$A7,交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A7,交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A7,交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -67905,19 +68696,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A7,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A7,交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$B$2:$B$228,$A7,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A7,交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A7,交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67928,27 +68719,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$C$2:$C$226,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A8,交易明細!$C$2:$C$228,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$C$2:$C$226,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A8,交易明細!$C$2:$C$228,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$228,$A8,交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A8,交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A8,交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -67956,19 +68747,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A8,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A8,交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$226,交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$228,交易明細!$B$2:$B$228,$A8,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A8,交易明細!$J$2:$J$226,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A8,交易明細!$J$2:$J$228,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -67979,27 +68770,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$C$2:$C$226,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A9,交易明細!$C$2:$C$228,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$C$2:$C$226,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A9,交易明細!$C$2:$C$228,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$228,$A9,交易明細!$J$2:$J$228,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A9,交易明細!$J$2:$J$228,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$228,$A9,交易明細!$J$2:$J$228,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -68007,19 +68798,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A9,交易明細!$J$2:$J$228,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$226,交易明細!$B$2:$B$226,$A9,交易明細!$J$2:$J$226,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$228,交易明細!$B$2:$B$228,$A9,交易明細!$J$2:$J$228,"&lt;&gt;未平倉")</f